--- a/R/data/quiz_250310.xlsx
+++ b/R/data/quiz_250310.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="277">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -779,6 +779,69 @@
   </si>
   <si>
     <t>전평지</t>
+  </si>
+  <si>
+    <t>8073sun@naver.com</t>
+  </si>
+  <si>
+    <t>이윤선</t>
+  </si>
+  <si>
+    <t>wodyd011324@gmail.com</t>
+  </si>
+  <si>
+    <t>김준형</t>
+  </si>
+  <si>
+    <t>kangsmooth@naver.com</t>
+  </si>
+  <si>
+    <t>강령현</t>
+  </si>
+  <si>
+    <t>hoperoy1213@gmail.com</t>
+  </si>
+  <si>
+    <t>AI로봇융합전공</t>
+  </si>
+  <si>
+    <t>최진호</t>
+  </si>
+  <si>
+    <t>pcy050122@naver.com</t>
+  </si>
+  <si>
+    <t>박채영</t>
+  </si>
+  <si>
+    <t>seoyebbb@gmail.com</t>
+  </si>
+  <si>
+    <t>박서예</t>
+  </si>
+  <si>
+    <t>maria3431@naver.com</t>
+  </si>
+  <si>
+    <t>황지영</t>
+  </si>
+  <si>
+    <t>hyeonji031007@gmail.com</t>
+  </si>
+  <si>
+    <t>우현지</t>
+  </si>
+  <si>
+    <t>bluelemon051106@naver.com</t>
+  </si>
+  <si>
+    <t>신정민</t>
+  </si>
+  <si>
+    <t>jyk3642@naver.com</t>
+  </si>
+  <si>
+    <t>김정연</t>
   </si>
 </sst>
 </file>
@@ -809,7 +872,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border/>
     <border>
       <left style="thin">
@@ -965,25 +1028,11 @@
         <color rgb="FF442F65"/>
       </bottom>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFFFFFF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFFFFFF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1030,9 +1079,6 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -1093,7 +1139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N88" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N98" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -4901,44 +4947,454 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="14">
+      <c r="A88" s="11">
         <v>45727.8825734375</v>
       </c>
-      <c r="B88" s="15" t="s">
+      <c r="B88" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="C88" s="15" t="s">
+      <c r="C88" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="D88" s="15">
+      <c r="D88" s="12">
         <v>2.0241087E7</v>
       </c>
-      <c r="E88" s="15" t="s">
+      <c r="E88" s="12" t="s">
         <v>255</v>
       </c>
-      <c r="F88" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G88" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H88" s="15">
+      <c r="F88" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G88" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H88" s="12">
         <v>2022.0</v>
       </c>
-      <c r="I88" s="15">
-        <v>2020.0</v>
-      </c>
-      <c r="J88" s="15" t="s">
+      <c r="I88" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J88" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="K88" s="15" t="s">
+      <c r="K88" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="L88" s="15" t="s">
+      <c r="L88" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="N88" s="16" t="s">
+      <c r="N88" s="13" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="8">
+        <v>45727.88507077546</v>
+      </c>
+      <c r="B89" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C89" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D89" s="9">
+        <v>2.0217011E7</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H89" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I89" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J89" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K89" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L89" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M89" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="11">
+        <v>45727.89783459491</v>
+      </c>
+      <c r="B90" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D90" s="12">
+        <v>2.0215136E7</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="F90" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G90" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H90" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I90" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J90" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K90" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L90" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M90" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="8">
+        <v>45727.90576612268</v>
+      </c>
+      <c r="B91" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="C91" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D91" s="9">
+        <v>2.0223051E7</v>
+      </c>
+      <c r="E91" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="F91" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G91" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H91" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I91" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J91" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K91" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L91" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N91" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="11">
+        <v>45727.90903185185</v>
+      </c>
+      <c r="B92" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="D92" s="12">
+        <v>2.0246789E7</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="F92" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G92" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H92" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I92" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J92" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K92" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L92" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M92" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8">
+        <v>45727.92954776621</v>
+      </c>
+      <c r="B93" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D93" s="9">
+        <v>2.0243411E7</v>
+      </c>
+      <c r="E93" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="F93" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G93" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H93" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I93" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J93" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K93" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L93" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M93" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="11">
+        <v>45727.93616107639</v>
+      </c>
+      <c r="B94" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D94" s="12">
+        <v>2.0242322E7</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="F94" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G94" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H94" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I94" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J94" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K94" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L94" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M94" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="8">
+        <v>45727.94450972222</v>
+      </c>
+      <c r="B95" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="C95" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D95" s="9">
+        <v>2.0211637E7</v>
+      </c>
+      <c r="E95" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="F95" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G95" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H95" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I95" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J95" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K95" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L95" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N95" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="11">
+        <v>45727.94757311343</v>
+      </c>
+      <c r="B96" s="12" t="s">
+        <v>271</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D96" s="12">
+        <v>2.0242727E7</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="F96" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G96" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H96" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I96" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J96" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K96" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L96" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N96" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8">
+        <v>45727.95005508102</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="C97" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D97" s="9">
+        <v>2.0222615E7</v>
+      </c>
+      <c r="E97" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="F97" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G97" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H97" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I97" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J97" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K97" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L97" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M97" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="14">
+        <v>45727.956041631944</v>
+      </c>
+      <c r="B98" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C98" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D98" s="15">
+        <v>2.022708E7</v>
+      </c>
+      <c r="E98" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="F98" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G98" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H98" s="15">
+        <v>2027.0</v>
+      </c>
+      <c r="I98" s="15">
+        <v>2018.0</v>
+      </c>
+      <c r="J98" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K98" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="L98" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="M98" s="15" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250310.xlsx
+++ b/R/data/quiz_250310.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="297">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -842,6 +842,66 @@
   </si>
   <si>
     <t>김정연</t>
+  </si>
+  <si>
+    <t>cksals9364@naver.com</t>
+  </si>
+  <si>
+    <t>김찬민</t>
+  </si>
+  <si>
+    <t>quf080411@gmail.com</t>
+  </si>
+  <si>
+    <t>김태연</t>
+  </si>
+  <si>
+    <t>renatta@naver.com</t>
+  </si>
+  <si>
+    <t>이예원</t>
+  </si>
+  <si>
+    <t>ggt0826@naver.com</t>
+  </si>
+  <si>
+    <t>김경태</t>
+  </si>
+  <si>
+    <t>dahyeon057@naver.com</t>
+  </si>
+  <si>
+    <t>한다현</t>
+  </si>
+  <si>
+    <t>tmdcks0162@naver.com</t>
+  </si>
+  <si>
+    <t>김승찬</t>
+  </si>
+  <si>
+    <t>20235110@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>소프트웨어학부</t>
+  </si>
+  <si>
+    <t>고유빈</t>
+  </si>
+  <si>
+    <t>huhjunwoo0@gmail.com</t>
+  </si>
+  <si>
+    <t>디지털미디어콘텐츠학부</t>
+  </si>
+  <si>
+    <t>허준우</t>
+  </si>
+  <si>
+    <t>vmin13@naver.com</t>
+  </si>
+  <si>
+    <t>강서연</t>
   </si>
 </sst>
 </file>
@@ -872,7 +932,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border/>
     <border>
       <left style="thin">
@@ -1005,10 +1065,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1016,13 +1076,27 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF442F65"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFF8F9FA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1032,7 +1106,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1079,6 +1153,9 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -1139,7 +1216,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N98" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N107" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -5357,44 +5434,413 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="14">
+      <c r="A98" s="11">
         <v>45727.956041631944</v>
       </c>
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="C98" s="15" t="s">
+      <c r="C98" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="D98" s="15">
+      <c r="D98" s="12">
         <v>2.022708E7</v>
       </c>
-      <c r="E98" s="15" t="s">
+      <c r="E98" s="12" t="s">
         <v>276</v>
       </c>
-      <c r="F98" s="15" t="s">
+      <c r="F98" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G98" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H98" s="15">
+      <c r="G98" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H98" s="12">
         <v>2027.0</v>
       </c>
-      <c r="I98" s="15">
+      <c r="I98" s="12">
         <v>2018.0</v>
       </c>
-      <c r="J98" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="K98" s="15" t="s">
+      <c r="J98" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K98" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="L98" s="15" t="s">
+      <c r="L98" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="M98" s="15" t="s">
+      <c r="M98" s="12" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="8">
+        <v>45727.97656560186</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C99" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="D99" s="9">
+        <v>2.0226726E7</v>
+      </c>
+      <c r="E99" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="F99" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G99" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H99" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I99" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J99" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K99" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L99" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M99" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="11">
+        <v>45727.98094584491</v>
+      </c>
+      <c r="B100" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D100" s="12">
+        <v>2.0246229E7</v>
+      </c>
+      <c r="E100" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="F100" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G100" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H100" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I100" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J100" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K100" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L100" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M100" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="8">
+        <v>45727.99015208334</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="C101" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="D101" s="9">
+        <v>2.0242337E7</v>
+      </c>
+      <c r="E101" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="F101" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G101" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H101" s="9">
+        <v>2027.0</v>
+      </c>
+      <c r="I101" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J101" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K101" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L101" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M101" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="11">
+        <v>45727.993892928236</v>
+      </c>
+      <c r="B102" s="12" t="s">
+        <v>283</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D102" s="12">
+        <v>2.0212703E7</v>
+      </c>
+      <c r="E102" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="F102" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G102" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H102" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I102" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J102" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K102" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L102" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M102" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="8">
+        <v>45727.995004131946</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="C103" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D103" s="9">
+        <v>2.0242853E7</v>
+      </c>
+      <c r="E103" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F103" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G103" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H103" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I103" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J103" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K103" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L103" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N103" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11">
+        <v>45728.01432634259</v>
+      </c>
+      <c r="B104" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D104" s="12">
+        <v>2.0222713E7</v>
+      </c>
+      <c r="E104" s="12" t="s">
+        <v>288</v>
+      </c>
+      <c r="F104" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G104" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H104" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I104" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J104" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K104" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L104" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N104" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="8">
+        <v>45728.04893978009</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C105" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D105" s="9">
+        <v>2.023511E7</v>
+      </c>
+      <c r="E105" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="F105" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G105" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H105" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I105" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J105" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K105" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L105" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N105" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11">
+        <v>45728.05061170139</v>
+      </c>
+      <c r="B106" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>293</v>
+      </c>
+      <c r="D106" s="12">
+        <v>2.0246792E7</v>
+      </c>
+      <c r="E106" s="12" t="s">
+        <v>294</v>
+      </c>
+      <c r="F106" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G106" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H106" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I106" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J106" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K106" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L106" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M106" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="14">
+        <v>45728.10225078704</v>
+      </c>
+      <c r="B107" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="C107" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D107" s="15">
+        <v>2.0242601E7</v>
+      </c>
+      <c r="E107" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="F107" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G107" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H107" s="15">
+        <v>2017.0</v>
+      </c>
+      <c r="I107" s="15">
+        <v>2020.0</v>
+      </c>
+      <c r="J107" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K107" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="L107" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N107" s="16" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250310.xlsx
+++ b/R/data/quiz_250310.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="297">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="379">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -902,6 +902,252 @@
   </si>
   <si>
     <t>강서연</t>
+  </si>
+  <si>
+    <t>jung5jung59708@gmail.com</t>
+  </si>
+  <si>
+    <t>정서현</t>
+  </si>
+  <si>
+    <t>hanyung1236@gmail.com</t>
+  </si>
+  <si>
+    <t>Ai의료융합</t>
+  </si>
+  <si>
+    <t>한영석</t>
+  </si>
+  <si>
+    <t>rmsdud9740@naver.com</t>
+  </si>
+  <si>
+    <t>경영</t>
+  </si>
+  <si>
+    <t>임근영</t>
+  </si>
+  <si>
+    <t>eugenechloek@gmail.com</t>
+  </si>
+  <si>
+    <t>영어영문학과</t>
+  </si>
+  <si>
+    <t>권유진</t>
+  </si>
+  <si>
+    <t>dltmdrb7013@gmail.com</t>
+  </si>
+  <si>
+    <t>인문학부</t>
+  </si>
+  <si>
+    <t>이승규</t>
+  </si>
+  <si>
+    <t>yoonji3795@naver.com</t>
+  </si>
+  <si>
+    <t>미래융합스쿨 융합관광경영전공</t>
+  </si>
+  <si>
+    <t>김윤지</t>
+  </si>
+  <si>
+    <t>hanhh3209@naver.com</t>
+  </si>
+  <si>
+    <t>한혜민</t>
+  </si>
+  <si>
+    <t>dark337006@naver.com</t>
+  </si>
+  <si>
+    <t>언론방송융합미디어전공</t>
+  </si>
+  <si>
+    <t>최봉근</t>
+  </si>
+  <si>
+    <t>lgw200308@gmail.com</t>
+  </si>
+  <si>
+    <t>빅데이터전공</t>
+  </si>
+  <si>
+    <t>이강우</t>
+  </si>
+  <si>
+    <t>ahyun11032@naver.com</t>
+  </si>
+  <si>
+    <t>김아현</t>
+  </si>
+  <si>
+    <t>jmj20061103@gmail.com</t>
+  </si>
+  <si>
+    <t>정민재</t>
+  </si>
+  <si>
+    <t>mireu707@naver.com</t>
+  </si>
+  <si>
+    <t>빅데이터학과</t>
+  </si>
+  <si>
+    <t>김미르</t>
+  </si>
+  <si>
+    <t>younsu0625@naver.com</t>
+  </si>
+  <si>
+    <t>임윤수</t>
+  </si>
+  <si>
+    <t>minbh5642@gmail.com</t>
+  </si>
+  <si>
+    <t>민병현</t>
+  </si>
+  <si>
+    <t>parkchaebin7890@gmail.com</t>
+  </si>
+  <si>
+    <t>디지털미디어콘텐츠 전공</t>
+  </si>
+  <si>
+    <t>qwe1527@naver.com</t>
+  </si>
+  <si>
+    <t>김나은</t>
+  </si>
+  <si>
+    <t>swl0427@naver.com</t>
+  </si>
+  <si>
+    <t>이승우</t>
+  </si>
+  <si>
+    <t>khe1021bb@gmail.com</t>
+  </si>
+  <si>
+    <t>미래융합스쿨 디지털인문예술</t>
+  </si>
+  <si>
+    <t>김하은</t>
+  </si>
+  <si>
+    <t>ssoning0315@naver.com</t>
+  </si>
+  <si>
+    <t>임소연</t>
+  </si>
+  <si>
+    <t>rhkrwnstjd19@gmail.com</t>
+  </si>
+  <si>
+    <t>콘텐츠IT</t>
+  </si>
+  <si>
+    <t>곽준성</t>
+  </si>
+  <si>
+    <t>skaskadl35@naver.com</t>
+  </si>
+  <si>
+    <t>이하민</t>
+  </si>
+  <si>
+    <t>mhk02083@naver.com</t>
+  </si>
+  <si>
+    <t>명희경</t>
+  </si>
+  <si>
+    <t>croony123@naver.com</t>
+  </si>
+  <si>
+    <t>허경무</t>
+  </si>
+  <si>
+    <t>jysjys1006@naver.com</t>
+  </si>
+  <si>
+    <t>지예슬</t>
+  </si>
+  <si>
+    <t>junghanhee777@gmail.com</t>
+  </si>
+  <si>
+    <t>정한희</t>
+  </si>
+  <si>
+    <t>qkrtjsdn0904@naver.com</t>
+  </si>
+  <si>
+    <t>스마트iot</t>
+  </si>
+  <si>
+    <t>박선우</t>
+  </si>
+  <si>
+    <t>leeyjin101010@gmail.com</t>
+  </si>
+  <si>
+    <t>이유진</t>
+  </si>
+  <si>
+    <t>csb5042@hanmail.net</t>
+  </si>
+  <si>
+    <t>최수빈</t>
+  </si>
+  <si>
+    <t>asaint84abc@gmail.com</t>
+  </si>
+  <si>
+    <t>인공지능융합학부</t>
+  </si>
+  <si>
+    <t>최정우</t>
+  </si>
+  <si>
+    <t>limsa3173@gmail.com</t>
+  </si>
+  <si>
+    <t>임승언</t>
+  </si>
+  <si>
+    <t>joonhyukkim13@gmail.com</t>
+  </si>
+  <si>
+    <t>김준혁</t>
+  </si>
+  <si>
+    <t>smfvnfms0615@naver.com</t>
+  </si>
+  <si>
+    <t>국어국문학과</t>
+  </si>
+  <si>
+    <t>김지나</t>
+  </si>
+  <si>
+    <t>min88278610@gmail.com</t>
+  </si>
+  <si>
+    <t>민선주</t>
+  </si>
+  <si>
+    <t>ggffee1129@gmail.com</t>
+  </si>
+  <si>
+    <t>인공지능융합학부(AI의료)</t>
+  </si>
+  <si>
+    <t>송관엽</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1462,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N107" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N141" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -5803,44 +6049,1438 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="14">
+      <c r="A107" s="8">
         <v>45728.10225078704</v>
       </c>
-      <c r="B107" s="15" t="s">
+      <c r="B107" s="9" t="s">
         <v>295</v>
       </c>
-      <c r="C107" s="15" t="s">
+      <c r="C107" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="D107" s="15">
+      <c r="D107" s="9">
         <v>2.0242601E7</v>
       </c>
-      <c r="E107" s="15" t="s">
+      <c r="E107" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="F107" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G107" s="15" t="s">
+      <c r="F107" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G107" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H107" s="15">
-        <v>2017.0</v>
-      </c>
-      <c r="I107" s="15">
-        <v>2020.0</v>
-      </c>
-      <c r="J107" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="K107" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="L107" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N107" s="16" t="s">
+      <c r="H107" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I107" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J107" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K107" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L107" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N107" s="10" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11">
+        <v>45728.331819652776</v>
+      </c>
+      <c r="B108" s="12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D108" s="12">
+        <v>2.0242744E7</v>
+      </c>
+      <c r="E108" s="12" t="s">
+        <v>298</v>
+      </c>
+      <c r="F108" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G108" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H108" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I108" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J108" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K108" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L108" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M108" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="8">
+        <v>45728.34868964121</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C109" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="D109" s="9">
+        <v>2.0226788E7</v>
+      </c>
+      <c r="E109" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="F109" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G109" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H109" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I109" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J109" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K109" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L109" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N109" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11">
+        <v>45728.393996203704</v>
+      </c>
+      <c r="B110" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>303</v>
+      </c>
+      <c r="D110" s="12">
+        <v>2.0243019E7</v>
+      </c>
+      <c r="E110" s="12" t="s">
+        <v>304</v>
+      </c>
+      <c r="F110" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G110" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H110" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I110" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J110" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K110" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L110" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M110" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="8">
+        <v>45728.4966645949</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="C111" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="D111" s="9">
+        <v>2.0221204E7</v>
+      </c>
+      <c r="E111" s="9" t="s">
+        <v>307</v>
+      </c>
+      <c r="F111" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G111" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H111" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I111" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J111" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K111" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L111" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N111" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="11">
+        <v>45728.51330615741</v>
+      </c>
+      <c r="B112" s="12" t="s">
+        <v>308</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="D112" s="12">
+        <v>2.0251066E7</v>
+      </c>
+      <c r="E112" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="F112" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G112" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H112" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I112" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J112" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K112" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L112" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N112" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="8">
+        <v>45728.53187853009</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="D113" s="9">
+        <v>2.0227125E7</v>
+      </c>
+      <c r="E113" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="F113" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G113" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="H113" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I113" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J113" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K113" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L113" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N113" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="11">
+        <v>45728.565723182866</v>
+      </c>
+      <c r="B114" s="12" t="s">
+        <v>314</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D114" s="12">
+        <v>2.0242759E7</v>
+      </c>
+      <c r="E114" s="12" t="s">
+        <v>315</v>
+      </c>
+      <c r="F114" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G114" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H114" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I114" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J114" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K114" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L114" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N114" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="8">
+        <v>45728.593335405094</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C115" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D115" s="9">
+        <v>2.0202581E7</v>
+      </c>
+      <c r="E115" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="F115" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G115" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H115" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I115" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J115" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K115" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L115" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M115" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="11">
+        <v>45728.604960578705</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>319</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="D116" s="12">
+        <v>2.0225208E7</v>
+      </c>
+      <c r="E116" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="F116" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G116" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H116" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I116" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J116" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K116" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L116" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N116" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="8">
+        <v>45728.61109327547</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D117" s="9">
+        <v>2.0243809E7</v>
+      </c>
+      <c r="E117" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="F117" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G117" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H117" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I117" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J117" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K117" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L117" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M117" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="11">
+        <v>45728.637184363426</v>
+      </c>
+      <c r="B118" s="12" t="s">
+        <v>324</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D118" s="12">
+        <v>2.0253246E7</v>
+      </c>
+      <c r="E118" s="12" t="s">
+        <v>325</v>
+      </c>
+      <c r="F118" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G118" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H118" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I118" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J118" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K118" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L118" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M118" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="8">
+        <v>45728.65664998842</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C119" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D119" s="9">
+        <v>2.0195148E7</v>
+      </c>
+      <c r="E119" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="F119" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G119" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H119" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I119" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J119" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K119" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L119" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N119" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="11">
+        <v>45728.680549675926</v>
+      </c>
+      <c r="B120" s="12" t="s">
+        <v>329</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D120" s="12">
+        <v>2.0224139E7</v>
+      </c>
+      <c r="E120" s="12" t="s">
+        <v>330</v>
+      </c>
+      <c r="F120" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="G120" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H120" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I120" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J120" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K120" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L120" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N120" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="8">
+        <v>45728.69191894676</v>
+      </c>
+      <c r="B121" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="C121" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D121" s="9">
+        <v>2.0251036E7</v>
+      </c>
+      <c r="E121" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="F121" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G121" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H121" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I121" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J121" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K121" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L121" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N121" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="11">
+        <v>45728.69311515046</v>
+      </c>
+      <c r="B122" s="12" t="s">
+        <v>333</v>
+      </c>
+      <c r="C122" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="D122" s="12">
+        <v>2.0242524E7</v>
+      </c>
+      <c r="E122" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="F122" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G122" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H122" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I122" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J122" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K122" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L122" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N122" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="8">
+        <v>45728.713069606485</v>
+      </c>
+      <c r="B123" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C123" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D123" s="9">
+        <v>2.0232504E7</v>
+      </c>
+      <c r="E123" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="F123" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G123" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H123" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I123" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J123" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K123" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L123" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N123" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="11">
+        <v>45728.7319040625</v>
+      </c>
+      <c r="B124" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="C124" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D124" s="12">
+        <v>2.0223002E7</v>
+      </c>
+      <c r="E124" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="F124" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G124" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H124" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I124" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J124" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K124" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L124" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M124" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="8">
+        <v>45728.747423761575</v>
+      </c>
+      <c r="B125" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C125" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="D125" s="9">
+        <v>2.024662E7</v>
+      </c>
+      <c r="E125" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="F125" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G125" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H125" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I125" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J125" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K125" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L125" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N125" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="11">
+        <v>45728.76622775463</v>
+      </c>
+      <c r="B126" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="C126" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D126" s="12">
+        <v>2.0212838E7</v>
+      </c>
+      <c r="E126" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="F126" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G126" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H126" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I126" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J126" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K126" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L126" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N126" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="8">
+        <v>45728.78414725694</v>
+      </c>
+      <c r="B127" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="C127" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="D127" s="9">
+        <v>2.0195109E7</v>
+      </c>
+      <c r="E127" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="F127" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G127" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H127" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I127" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J127" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K127" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L127" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M127" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="11">
+        <v>45728.81254811343</v>
+      </c>
+      <c r="B128" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="C128" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D128" s="12">
+        <v>2.0217062E7</v>
+      </c>
+      <c r="E128" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="F128" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G128" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H128" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I128" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J128" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K128" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L128" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M128" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="8">
+        <v>45728.8332530787</v>
+      </c>
+      <c r="B129" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="C129" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D129" s="9">
+        <v>2.0232613E7</v>
+      </c>
+      <c r="E129" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="F129" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G129" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H129" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I129" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J129" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K129" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L129" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M129" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11">
+        <v>45728.836728599534</v>
+      </c>
+      <c r="B130" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="C130" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D130" s="12">
+        <v>2.0225276E7</v>
+      </c>
+      <c r="E130" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="F130" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G130" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H130" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I130" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J130" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K130" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L130" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N130" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="8">
+        <v>45728.83710341435</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>353</v>
+      </c>
+      <c r="C131" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D131" s="9">
+        <v>2.0217073E7</v>
+      </c>
+      <c r="E131" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="F131" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G131" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H131" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I131" s="9">
+        <v>2021.0</v>
+      </c>
+      <c r="J131" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K131" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L131" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N131" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="11">
+        <v>45728.90295998842</v>
+      </c>
+      <c r="B132" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C132" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D132" s="12">
+        <v>2.0242136E7</v>
+      </c>
+      <c r="E132" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="F132" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G132" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H132" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I132" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J132" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K132" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L132" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M132" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="8">
+        <v>45728.910339594906</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C133" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="D133" s="9">
+        <v>2.022712E7</v>
+      </c>
+      <c r="E133" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="F133" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G133" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H133" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I133" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J133" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K133" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L133" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M133" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="11">
+        <v>45728.91069072917</v>
+      </c>
+      <c r="B134" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="C134" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D134" s="12">
+        <v>2.0222132E7</v>
+      </c>
+      <c r="E134" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="F134" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G134" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H134" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I134" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J134" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K134" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L134" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M134" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="8">
+        <v>45728.947866296294</v>
+      </c>
+      <c r="B135" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="C135" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D135" s="9">
+        <v>2.0242849E7</v>
+      </c>
+      <c r="E135" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="F135" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G135" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H135" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I135" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J135" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K135" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L135" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N135" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="11">
+        <v>45728.965238993056</v>
+      </c>
+      <c r="B136" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="D136" s="12">
+        <v>2.0256785E7</v>
+      </c>
+      <c r="E136" s="12" t="s">
+        <v>366</v>
+      </c>
+      <c r="F136" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G136" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H136" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I136" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J136" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K136" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L136" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N136" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="8">
+        <v>45728.96548399306</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="C137" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D137" s="9">
+        <v>2.0226281E7</v>
+      </c>
+      <c r="E137" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="F137" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G137" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H137" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I137" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J137" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K137" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L137" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N137" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="11">
+        <v>45728.99544313658</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D138" s="12">
+        <v>2.0201207E7</v>
+      </c>
+      <c r="E138" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="F138" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G138" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H138" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I138" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J138" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K138" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L138" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N138" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="8">
+        <v>45729.03324859954</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>371</v>
+      </c>
+      <c r="C139" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="D139" s="9">
+        <v>2.0221021E7</v>
+      </c>
+      <c r="E139" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="F139" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G139" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H139" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I139" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J139" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K139" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L139" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N139" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11">
+        <v>45729.05492663194</v>
+      </c>
+      <c r="B140" s="12" t="s">
+        <v>374</v>
+      </c>
+      <c r="C140" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D140" s="12">
+        <v>2.0242615E7</v>
+      </c>
+      <c r="E140" s="12" t="s">
+        <v>375</v>
+      </c>
+      <c r="F140" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G140" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H140" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I140" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J140" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K140" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L140" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N140" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="14">
+        <v>45729.087981805555</v>
+      </c>
+      <c r="B141" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="C141" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="D141" s="15">
+        <v>2.0246737E7</v>
+      </c>
+      <c r="E141" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="F141" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G141" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H141" s="15">
+        <v>2017.0</v>
+      </c>
+      <c r="I141" s="15">
+        <v>2020.0</v>
+      </c>
+      <c r="J141" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K141" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="L141" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N141" s="16" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250310.xlsx
+++ b/R/data/quiz_250310.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="480">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -1148,6 +1148,309 @@
   </si>
   <si>
     <t>송관엽</t>
+  </si>
+  <si>
+    <t>jeonguijin45@gmail.com</t>
+  </si>
+  <si>
+    <t>데이터사이언스학과</t>
+  </si>
+  <si>
+    <t>정의진</t>
+  </si>
+  <si>
+    <t>puy0522@naver.com</t>
+  </si>
+  <si>
+    <t>이혜영</t>
+  </si>
+  <si>
+    <t>sungjun2558@naver.com</t>
+  </si>
+  <si>
+    <t>박성준</t>
+  </si>
+  <si>
+    <t>dn1107123@naver.com</t>
+  </si>
+  <si>
+    <t>김대현</t>
+  </si>
+  <si>
+    <t>sanova369@gmail.com</t>
+  </si>
+  <si>
+    <t>김수진</t>
+  </si>
+  <si>
+    <t>namjihk@gmail.com</t>
+  </si>
+  <si>
+    <t>남지혁</t>
+  </si>
+  <si>
+    <t>dagam331@gmail.com</t>
+  </si>
+  <si>
+    <t>명다감</t>
+  </si>
+  <si>
+    <t>seokzard10@naver.com</t>
+  </si>
+  <si>
+    <t>글로벌비즈니스학과</t>
+  </si>
+  <si>
+    <t>진현석</t>
+  </si>
+  <si>
+    <t>050822ac@gmail.com</t>
+  </si>
+  <si>
+    <t>조연솔</t>
+  </si>
+  <si>
+    <t>yugyuhyeon023@gmail.com</t>
+  </si>
+  <si>
+    <t>자연과학대학 자율전공</t>
+  </si>
+  <si>
+    <t>유규현</t>
+  </si>
+  <si>
+    <t>ous4297@naver.com</t>
+  </si>
+  <si>
+    <t>융합관광경영</t>
+  </si>
+  <si>
+    <t>오윤서</t>
+  </si>
+  <si>
+    <t>hrk5353@naver.com</t>
+  </si>
+  <si>
+    <t>홍리경</t>
+  </si>
+  <si>
+    <t>gkaehdwn68@naver.com</t>
+  </si>
+  <si>
+    <t>함동주</t>
+  </si>
+  <si>
+    <t>dytpq0823@naver.com</t>
+  </si>
+  <si>
+    <t>이한울</t>
+  </si>
+  <si>
+    <t>ncc07291@naver.com</t>
+  </si>
+  <si>
+    <t>신기재</t>
+  </si>
+  <si>
+    <t>lswon9916@naver.com</t>
+  </si>
+  <si>
+    <t>이서원</t>
+  </si>
+  <si>
+    <t>stopji209@naver.com</t>
+  </si>
+  <si>
+    <t>정지윤</t>
+  </si>
+  <si>
+    <t>jyjjyj057@naver.com</t>
+  </si>
+  <si>
+    <t>정예지</t>
+  </si>
+  <si>
+    <t>ksj040202@gmail.com</t>
+  </si>
+  <si>
+    <t>권수정</t>
+  </si>
+  <si>
+    <t>ksy05061010@gmail.com</t>
+  </si>
+  <si>
+    <t>데이터테크전공</t>
+  </si>
+  <si>
+    <t>joony1226@naver.com</t>
+  </si>
+  <si>
+    <t>콘텐츠 it</t>
+  </si>
+  <si>
+    <t>백주현</t>
+  </si>
+  <si>
+    <t>yuvin0612@naver.com</t>
+  </si>
+  <si>
+    <t>장유빈</t>
+  </si>
+  <si>
+    <t>mp0945@naver.com</t>
+  </si>
+  <si>
+    <t>사학과</t>
+  </si>
+  <si>
+    <t>홍민표</t>
+  </si>
+  <si>
+    <t>0812hhh37@gmail.com</t>
+  </si>
+  <si>
+    <t>최아영</t>
+  </si>
+  <si>
+    <t>sswskb71538@naver.com</t>
+  </si>
+  <si>
+    <t>신승우</t>
+  </si>
+  <si>
+    <t>jihyunkim917@gmail.com</t>
+  </si>
+  <si>
+    <t>김지현</t>
+  </si>
+  <si>
+    <t>hb3130@naver.com</t>
+  </si>
+  <si>
+    <t>안효빈</t>
+  </si>
+  <si>
+    <t>chlwhddbs715@gmail.com</t>
+  </si>
+  <si>
+    <t>반도체공학과</t>
+  </si>
+  <si>
+    <t>최종윤</t>
+  </si>
+  <si>
+    <t>shin19980527@gmail.com</t>
+  </si>
+  <si>
+    <t>철학과</t>
+  </si>
+  <si>
+    <t>신재헌</t>
+  </si>
+  <si>
+    <t>dahan1124man@gmail.com</t>
+  </si>
+  <si>
+    <t>빅데이터 학과</t>
+  </si>
+  <si>
+    <t>장한</t>
+  </si>
+  <si>
+    <t>jsy40394725@gmail.com</t>
+  </si>
+  <si>
+    <t>조선영</t>
+  </si>
+  <si>
+    <t>msj5777@naver.com</t>
+  </si>
+  <si>
+    <t>마수정</t>
+  </si>
+  <si>
+    <t>yongjun8844@gmail.com</t>
+  </si>
+  <si>
+    <t>소프트웨어융합(빅데이터)</t>
+  </si>
+  <si>
+    <t>안용준</t>
+  </si>
+  <si>
+    <t>ssm09093@naver.com</t>
+  </si>
+  <si>
+    <t>반도체디스플레이</t>
+  </si>
+  <si>
+    <t>조준범</t>
+  </si>
+  <si>
+    <t>maniaeom@gmail.com</t>
+  </si>
+  <si>
+    <t>청각학전공</t>
+  </si>
+  <si>
+    <t>엄지은</t>
+  </si>
+  <si>
+    <t>geuna7411@gmail.com</t>
+  </si>
+  <si>
+    <t>박근아</t>
+  </si>
+  <si>
+    <t>choije0115@naver.com</t>
+  </si>
+  <si>
+    <t>최정은</t>
+  </si>
+  <si>
+    <t>zxyjh0612@naver.com</t>
+  </si>
+  <si>
+    <t>유재혁</t>
+  </si>
+  <si>
+    <t>kimdw9510@gmail.com</t>
+  </si>
+  <si>
+    <t>김동우</t>
+  </si>
+  <si>
+    <t>3628kyl@naver.com</t>
+  </si>
+  <si>
+    <t>권혜수</t>
+  </si>
+  <si>
+    <t>kigkig495@naver.com</t>
+  </si>
+  <si>
+    <t>콘텐츠it</t>
+  </si>
+  <si>
+    <t>오준혁</t>
+  </si>
+  <si>
+    <t>coreabulls1@gmail.com</t>
+  </si>
+  <si>
+    <t>최성준</t>
+  </si>
+  <si>
+    <t>j92921652@gmail.com</t>
+  </si>
+  <si>
+    <t>정주원</t>
+  </si>
+  <si>
+    <t>ckdnvd!e@kakao.com</t>
+  </si>
+  <si>
+    <t>이시온</t>
   </si>
 </sst>
 </file>
@@ -1462,7 +1765,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N141" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N185" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -7443,43 +7746,1847 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="14">
+      <c r="A141" s="8">
         <v>45729.087981805555</v>
       </c>
-      <c r="B141" s="15" t="s">
+      <c r="B141" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="C141" s="15" t="s">
+      <c r="C141" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="D141" s="15">
+      <c r="D141" s="9">
         <v>2.0246737E7</v>
       </c>
-      <c r="E141" s="15" t="s">
+      <c r="E141" s="9" t="s">
         <v>378</v>
       </c>
-      <c r="F141" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G141" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H141" s="15">
-        <v>2017.0</v>
-      </c>
-      <c r="I141" s="15">
-        <v>2020.0</v>
-      </c>
-      <c r="J141" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="K141" s="15" t="s">
+      <c r="F141" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G141" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H141" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I141" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J141" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K141" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="L141" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N141" s="16" t="s">
+      <c r="L141" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N141" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="11">
+        <v>45729.36367982639</v>
+      </c>
+      <c r="B142" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="C142" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="D142" s="12">
+        <v>2.0243252E7</v>
+      </c>
+      <c r="E142" s="12" t="s">
+        <v>381</v>
+      </c>
+      <c r="F142" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G142" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H142" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I142" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J142" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K142" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L142" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N142" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="8">
+        <v>45729.392381805555</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="C143" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D143" s="9">
+        <v>2.0227028E7</v>
+      </c>
+      <c r="E143" s="9" t="s">
+        <v>383</v>
+      </c>
+      <c r="F143" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G143" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H143" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I143" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J143" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K143" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L143" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N143" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="11">
+        <v>45729.39456105324</v>
+      </c>
+      <c r="B144" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="C144" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D144" s="12">
+        <v>2.021332E7</v>
+      </c>
+      <c r="E144" s="12" t="s">
+        <v>385</v>
+      </c>
+      <c r="F144" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G144" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H144" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I144" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J144" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K144" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L144" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N144" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="8">
+        <v>45729.444654837964</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="C145" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D145" s="9">
+        <v>2.0242918E7</v>
+      </c>
+      <c r="E145" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="F145" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G145" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H145" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I145" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J145" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K145" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L145" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M145" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="11">
+        <v>45729.4465427199</v>
+      </c>
+      <c r="B146" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="C146" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D146" s="12">
+        <v>2.0246915E7</v>
+      </c>
+      <c r="E146" s="12" t="s">
+        <v>389</v>
+      </c>
+      <c r="F146" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G146" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H146" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I146" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J146" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K146" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L146" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N146" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="8">
+        <v>45729.45629780093</v>
+      </c>
+      <c r="B147" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="C147" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D147" s="9">
+        <v>2.0242944E7</v>
+      </c>
+      <c r="E147" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G147" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H147" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I147" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J147" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K147" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L147" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M147" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="11">
+        <v>45729.47303645834</v>
+      </c>
+      <c r="B148" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="C148" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="D148" s="12">
+        <v>2.0226733E7</v>
+      </c>
+      <c r="E148" s="12" t="s">
+        <v>393</v>
+      </c>
+      <c r="F148" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G148" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H148" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I148" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J148" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K148" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L148" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M148" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="8">
+        <v>45729.499945821764</v>
+      </c>
+      <c r="B149" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="C149" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="D149" s="9">
+        <v>2.0246424E7</v>
+      </c>
+      <c r="E149" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="F149" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G149" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H149" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I149" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J149" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K149" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L149" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N149" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="11">
+        <v>45729.579431307866</v>
+      </c>
+      <c r="B150" s="12" t="s">
+        <v>397</v>
+      </c>
+      <c r="C150" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D150" s="12">
+        <v>2.0242748E7</v>
+      </c>
+      <c r="E150" s="12" t="s">
+        <v>398</v>
+      </c>
+      <c r="F150" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G150" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H150" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I150" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J150" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K150" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L150" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M150" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="8">
+        <v>45729.58684429398</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>399</v>
+      </c>
+      <c r="C151" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="D151" s="9">
+        <v>2.0253133E7</v>
+      </c>
+      <c r="E151" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="F151" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G151" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H151" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I151" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J151" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="K151" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L151" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N151" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="11">
+        <v>45729.601671944445</v>
+      </c>
+      <c r="B152" s="12" t="s">
+        <v>402</v>
+      </c>
+      <c r="C152" s="12" t="s">
+        <v>403</v>
+      </c>
+      <c r="D152" s="12">
+        <v>2.0246632E7</v>
+      </c>
+      <c r="E152" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="F152" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G152" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H152" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I152" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J152" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K152" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L152" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M152" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="8">
+        <v>45729.622919456015</v>
+      </c>
+      <c r="B153" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="C153" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D153" s="9">
+        <v>2.0242588E7</v>
+      </c>
+      <c r="E153" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="F153" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G153" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H153" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I153" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J153" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K153" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L153" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N153" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="11">
+        <v>45729.63936939815</v>
+      </c>
+      <c r="B154" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="C154" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D154" s="12">
+        <v>2.0242587E7</v>
+      </c>
+      <c r="E154" s="12" t="s">
+        <v>408</v>
+      </c>
+      <c r="F154" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G154" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H154" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I154" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J154" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K154" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L154" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N154" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="8">
+        <v>45729.64662666667</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D155" s="9">
+        <v>2.0253018E7</v>
+      </c>
+      <c r="E155" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="F155" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G155" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H155" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I155" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J155" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K155" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L155" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M155" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="11">
+        <v>45729.65716243055</v>
+      </c>
+      <c r="B156" s="12" t="s">
+        <v>411</v>
+      </c>
+      <c r="C156" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D156" s="12">
+        <v>2.0192216E7</v>
+      </c>
+      <c r="E156" s="12" t="s">
+        <v>412</v>
+      </c>
+      <c r="F156" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G156" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H156" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I156" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J156" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K156" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L156" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M156" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="8">
+        <v>45729.67466229167</v>
+      </c>
+      <c r="B157" s="9" t="s">
+        <v>413</v>
+      </c>
+      <c r="C157" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D157" s="9">
+        <v>2.0243936E7</v>
+      </c>
+      <c r="E157" s="9" t="s">
+        <v>414</v>
+      </c>
+      <c r="F157" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G157" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H157" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I157" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J157" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K157" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L157" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M157" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="11">
+        <v>45729.69313185185</v>
+      </c>
+      <c r="B158" s="12" t="s">
+        <v>415</v>
+      </c>
+      <c r="C158" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D158" s="12">
+        <v>2.0227074E7</v>
+      </c>
+      <c r="E158" s="12" t="s">
+        <v>416</v>
+      </c>
+      <c r="F158" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G158" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H158" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I158" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J158" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K158" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L158" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M158" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="8">
+        <v>45729.69629788194</v>
+      </c>
+      <c r="B159" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="C159" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D159" s="9">
+        <v>2.0213634E7</v>
+      </c>
+      <c r="E159" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="F159" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G159" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H159" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I159" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J159" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K159" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L159" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N159" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="11">
+        <v>45729.69654846065</v>
+      </c>
+      <c r="B160" s="12" t="s">
+        <v>419</v>
+      </c>
+      <c r="C160" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D160" s="12">
+        <v>2.024621E7</v>
+      </c>
+      <c r="E160" s="12" t="s">
+        <v>420</v>
+      </c>
+      <c r="F160" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G160" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H160" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I160" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J160" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K160" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L160" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N160" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="8">
+        <v>45729.712660590274</v>
+      </c>
+      <c r="B161" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="C161" s="9" t="s">
+        <v>422</v>
+      </c>
+      <c r="D161" s="9">
+        <v>2.0243202E7</v>
+      </c>
+      <c r="E161" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="F161" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G161" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H161" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I161" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J161" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K161" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L161" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M161" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="11">
+        <v>45729.720239409726</v>
+      </c>
+      <c r="B162" s="12" t="s">
+        <v>423</v>
+      </c>
+      <c r="C162" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="D162" s="12">
+        <v>2.0245181E7</v>
+      </c>
+      <c r="E162" s="12" t="s">
+        <v>425</v>
+      </c>
+      <c r="F162" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G162" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H162" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I162" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J162" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K162" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L162" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M162" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="8">
+        <v>45729.72266135417</v>
+      </c>
+      <c r="B163" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="C163" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D163" s="9">
+        <v>2.0203537E7</v>
+      </c>
+      <c r="E163" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="F163" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G163" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H163" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I163" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J163" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K163" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L163" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M163" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="11">
+        <v>45729.76153319444</v>
+      </c>
+      <c r="B164" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="C164" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="D164" s="12">
+        <v>2.0181117E7</v>
+      </c>
+      <c r="E164" s="12" t="s">
+        <v>430</v>
+      </c>
+      <c r="F164" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G164" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H164" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I164" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J164" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K164" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L164" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M164" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="8">
+        <v>45729.76257726851</v>
+      </c>
+      <c r="B165" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="C165" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D165" s="9">
+        <v>2.0243047E7</v>
+      </c>
+      <c r="E165" s="9" t="s">
+        <v>432</v>
+      </c>
+      <c r="F165" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G165" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H165" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I165" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J165" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K165" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L165" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M165" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="11">
+        <v>45729.77363439815</v>
+      </c>
+      <c r="B166" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="C166" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D166" s="12">
+        <v>2.0252122E7</v>
+      </c>
+      <c r="E166" s="12" t="s">
+        <v>434</v>
+      </c>
+      <c r="F166" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G166" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H166" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I166" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J166" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K166" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L166" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M166" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="8">
+        <v>45729.77975559028</v>
+      </c>
+      <c r="B167" s="9" t="s">
+        <v>435</v>
+      </c>
+      <c r="C167" s="9" t="s">
+        <v>309</v>
+      </c>
+      <c r="D167" s="9">
+        <v>2.0241024E7</v>
+      </c>
+      <c r="E167" s="9" t="s">
+        <v>436</v>
+      </c>
+      <c r="F167" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G167" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H167" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I167" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J167" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K167" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L167" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N167" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="11">
+        <v>45729.79442064815</v>
+      </c>
+      <c r="B168" s="12" t="s">
+        <v>437</v>
+      </c>
+      <c r="C168" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D168" s="12">
+        <v>2.0241216E7</v>
+      </c>
+      <c r="E168" s="12" t="s">
+        <v>438</v>
+      </c>
+      <c r="F168" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G168" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H168" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I168" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J168" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K168" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L168" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N168" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="8">
+        <v>45729.797287719906</v>
+      </c>
+      <c r="B169" s="9" t="s">
+        <v>439</v>
+      </c>
+      <c r="C169" s="9" t="s">
+        <v>440</v>
+      </c>
+      <c r="D169" s="9">
+        <v>2.023335E7</v>
+      </c>
+      <c r="E169" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="F169" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G169" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H169" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I169" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J169" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K169" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L169" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N169" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="11">
+        <v>45729.79916689815</v>
+      </c>
+      <c r="B170" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="C170" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="D170" s="12">
+        <v>2.0171054E7</v>
+      </c>
+      <c r="E170" s="12" t="s">
+        <v>444</v>
+      </c>
+      <c r="F170" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G170" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H170" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I170" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J170" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K170" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L170" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M170" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="8">
+        <v>45729.80305444445</v>
+      </c>
+      <c r="B171" s="9" t="s">
+        <v>445</v>
+      </c>
+      <c r="C171" s="9" t="s">
+        <v>446</v>
+      </c>
+      <c r="D171" s="9">
+        <v>2.0225245E7</v>
+      </c>
+      <c r="E171" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="F171" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G171" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H171" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I171" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J171" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K171" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L171" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M171" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="11">
+        <v>45729.81185302083</v>
+      </c>
+      <c r="B172" s="12" t="s">
+        <v>448</v>
+      </c>
+      <c r="C172" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D172" s="12">
+        <v>2.0222634E7</v>
+      </c>
+      <c r="E172" s="12" t="s">
+        <v>449</v>
+      </c>
+      <c r="F172" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G172" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H172" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I172" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J172" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K172" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L172" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N172" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="8">
+        <v>45729.81438782407</v>
+      </c>
+      <c r="B173" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="C173" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D173" s="9">
+        <v>2.023708E7</v>
+      </c>
+      <c r="E173" s="9" t="s">
+        <v>451</v>
+      </c>
+      <c r="F173" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G173" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H173" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I173" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J173" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K173" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L173" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M173" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="11">
+        <v>45729.87222289352</v>
+      </c>
+      <c r="B174" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="C174" s="12" t="s">
+        <v>453</v>
+      </c>
+      <c r="D174" s="12">
+        <v>2.0225188E7</v>
+      </c>
+      <c r="E174" s="12" t="s">
+        <v>454</v>
+      </c>
+      <c r="F174" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G174" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H174" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I174" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J174" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K174" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L174" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N174" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="8">
+        <v>45729.89588841435</v>
+      </c>
+      <c r="B175" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="C175" s="9" t="s">
+        <v>456</v>
+      </c>
+      <c r="D175" s="9">
+        <v>2.0213353E7</v>
+      </c>
+      <c r="E175" s="9" t="s">
+        <v>457</v>
+      </c>
+      <c r="F175" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G175" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H175" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I175" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J175" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K175" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L175" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M175" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="11">
+        <v>45729.93143952546</v>
+      </c>
+      <c r="B176" s="12" t="s">
+        <v>458</v>
+      </c>
+      <c r="C176" s="12" t="s">
+        <v>459</v>
+      </c>
+      <c r="D176" s="12">
+        <v>2.0223933E7</v>
+      </c>
+      <c r="E176" s="12" t="s">
+        <v>460</v>
+      </c>
+      <c r="F176" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G176" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H176" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I176" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J176" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K176" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L176" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M176" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="8">
+        <v>45729.93515532407</v>
+      </c>
+      <c r="B177" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="C177" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D177" s="9">
+        <v>2.024351E7</v>
+      </c>
+      <c r="E177" s="9" t="s">
+        <v>462</v>
+      </c>
+      <c r="F177" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G177" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H177" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I177" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J177" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K177" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L177" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N177" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="11">
+        <v>45729.951329965275</v>
+      </c>
+      <c r="B178" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="C178" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D178" s="12">
+        <v>2.0233543E7</v>
+      </c>
+      <c r="E178" s="12" t="s">
+        <v>464</v>
+      </c>
+      <c r="F178" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G178" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H178" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I178" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J178" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K178" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L178" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M178" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="8">
+        <v>45729.968081493054</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>465</v>
+      </c>
+      <c r="C179" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D179" s="9">
+        <v>2.0222223E7</v>
+      </c>
+      <c r="E179" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="F179" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G179" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H179" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I179" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J179" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="K179" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L179" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N179" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="11">
+        <v>45730.01769443287</v>
+      </c>
+      <c r="B180" s="12" t="s">
+        <v>467</v>
+      </c>
+      <c r="C180" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D180" s="12">
+        <v>2.0242807E7</v>
+      </c>
+      <c r="E180" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="F180" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G180" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H180" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I180" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J180" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K180" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L180" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N180" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="8">
+        <v>45730.02744760417</v>
+      </c>
+      <c r="B181" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="C181" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D181" s="9">
+        <v>2.0242605E7</v>
+      </c>
+      <c r="E181" s="9" t="s">
+        <v>470</v>
+      </c>
+      <c r="F181" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G181" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H181" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I181" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J181" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K181" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L181" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N181" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="11">
+        <v>45730.03097760417</v>
+      </c>
+      <c r="B182" s="12" t="s">
+        <v>471</v>
+      </c>
+      <c r="C182" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="D182" s="12">
+        <v>2.0245205E7</v>
+      </c>
+      <c r="E182" s="12" t="s">
+        <v>473</v>
+      </c>
+      <c r="F182" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G182" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H182" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I182" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J182" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K182" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L182" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M182" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="8">
+        <v>45730.03674856482</v>
+      </c>
+      <c r="B183" s="9" t="s">
+        <v>474</v>
+      </c>
+      <c r="C183" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D183" s="9">
+        <v>2.0242137E7</v>
+      </c>
+      <c r="E183" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="F183" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G183" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H183" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I183" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J183" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K183" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L183" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N183" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="11">
+        <v>45730.12428217592</v>
+      </c>
+      <c r="B184" s="12" t="s">
+        <v>476</v>
+      </c>
+      <c r="C184" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="D184" s="12">
+        <v>2.0243952E7</v>
+      </c>
+      <c r="E184" s="12" t="s">
+        <v>477</v>
+      </c>
+      <c r="F184" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G184" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H184" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I184" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J184" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K184" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L184" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N184" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="14">
+        <v>45730.26984868056</v>
+      </c>
+      <c r="B185" s="15" t="s">
+        <v>478</v>
+      </c>
+      <c r="C185" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D185" s="15">
+        <v>2.0212744E7</v>
+      </c>
+      <c r="E185" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="F185" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="G185" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H185" s="15">
+        <v>2017.0</v>
+      </c>
+      <c r="I185" s="15">
+        <v>2019.0</v>
+      </c>
+      <c r="J185" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K185" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="L185" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="N185" s="16" t="s">
         <v>22</v>
       </c>
     </row>

--- a/R/data/quiz_250310.xlsx
+++ b/R/data/quiz_250310.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2237" uniqueCount="616">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -1451,6 +1451,414 @@
   </si>
   <si>
     <t>이시온</t>
+  </si>
+  <si>
+    <t>kes3384asdasd@naver.com</t>
+  </si>
+  <si>
+    <t>인문학부 사학전공</t>
+  </si>
+  <si>
+    <t>김주은</t>
+  </si>
+  <si>
+    <t>eugenejung0324@gmail.com</t>
+  </si>
+  <si>
+    <t>러시아학과</t>
+  </si>
+  <si>
+    <t>정지호</t>
+  </si>
+  <si>
+    <t>kid050311@naver.com</t>
+  </si>
+  <si>
+    <t>김이담</t>
+  </si>
+  <si>
+    <t>minjj0918@naver.com</t>
+  </si>
+  <si>
+    <t>인공지능융합학부 AI로봇융합전공</t>
+  </si>
+  <si>
+    <t>조석훈</t>
+  </si>
+  <si>
+    <t>hschang0924@gmail.com</t>
+  </si>
+  <si>
+    <t>장현수</t>
+  </si>
+  <si>
+    <t>05hg8239@naver.com</t>
+  </si>
+  <si>
+    <t>조현근</t>
+  </si>
+  <si>
+    <t>choiy617@naver.com</t>
+  </si>
+  <si>
+    <t>최원찬</t>
+  </si>
+  <si>
+    <t>10pjh0420@naver.com</t>
+  </si>
+  <si>
+    <t>박주혁</t>
+  </si>
+  <si>
+    <t>hyunmibob209@gmail.com</t>
+  </si>
+  <si>
+    <t>언론융합미디어(복전 법학과)</t>
+  </si>
+  <si>
+    <t>이현민</t>
+  </si>
+  <si>
+    <t>1991kcal@kakao.com</t>
+  </si>
+  <si>
+    <t>데이터사이언스학부 데이터테크전공</t>
+  </si>
+  <si>
+    <t>원채영</t>
+  </si>
+  <si>
+    <t>psb051014@gmail.com</t>
+  </si>
+  <si>
+    <t>박수빈</t>
+  </si>
+  <si>
+    <t>yeon2760@naver.com</t>
+  </si>
+  <si>
+    <t>강나연</t>
+  </si>
+  <si>
+    <t>wjsskan13@naver.com</t>
+  </si>
+  <si>
+    <t>전나무</t>
+  </si>
+  <si>
+    <t>llyj0202@gmail.com</t>
+  </si>
+  <si>
+    <t>이유정</t>
+  </si>
+  <si>
+    <t>monkey5301@naver.com</t>
+  </si>
+  <si>
+    <t>최원형</t>
+  </si>
+  <si>
+    <t>mins4092@naver.com</t>
+  </si>
+  <si>
+    <t>Ai기술경영융합</t>
+  </si>
+  <si>
+    <t>김민성</t>
+  </si>
+  <si>
+    <t>yourmylife00@naver.com</t>
+  </si>
+  <si>
+    <t>허윤진</t>
+  </si>
+  <si>
+    <t>pyjn1475@naver.com</t>
+  </si>
+  <si>
+    <t>박용준</t>
+  </si>
+  <si>
+    <t>twins.sijin@gmail.com</t>
+  </si>
+  <si>
+    <t>정시진</t>
+  </si>
+  <si>
+    <t>yeeun051212@naver.com</t>
+  </si>
+  <si>
+    <t>진예은</t>
+  </si>
+  <si>
+    <t>jihona1223@naver.com</t>
+  </si>
+  <si>
+    <t>나지호</t>
+  </si>
+  <si>
+    <t>dlxowns1220@naver.com</t>
+  </si>
+  <si>
+    <t>이태준</t>
+  </si>
+  <si>
+    <t>gwkang0330@gmail.com</t>
+  </si>
+  <si>
+    <t>강건우</t>
+  </si>
+  <si>
+    <t>as2020kl@naver.com</t>
+  </si>
+  <si>
+    <t>박수진</t>
+  </si>
+  <si>
+    <t>juduse9@naver.com</t>
+  </si>
+  <si>
+    <t>박시은</t>
+  </si>
+  <si>
+    <t>dhdhdh1010@naver.com</t>
+  </si>
+  <si>
+    <t>김도희</t>
+  </si>
+  <si>
+    <t>kass3210@naver.com</t>
+  </si>
+  <si>
+    <t>박대광</t>
+  </si>
+  <si>
+    <t>chan95713792@gmail.com</t>
+  </si>
+  <si>
+    <t>박찬영</t>
+  </si>
+  <si>
+    <t>psh19851985@gmail.com</t>
+  </si>
+  <si>
+    <t>박성호</t>
+  </si>
+  <si>
+    <t>a1b20802@naver.com</t>
+  </si>
+  <si>
+    <t>이도연</t>
+  </si>
+  <si>
+    <t>a98115988@gmail.com</t>
+  </si>
+  <si>
+    <t>강민구</t>
+  </si>
+  <si>
+    <t>maniddom@gmail.com</t>
+  </si>
+  <si>
+    <t>이민준</t>
+  </si>
+  <si>
+    <t>soyang4040@naver.com</t>
+  </si>
+  <si>
+    <t>김상교</t>
+  </si>
+  <si>
+    <t>kelly9845@naver.com</t>
+  </si>
+  <si>
+    <t>박서연</t>
+  </si>
+  <si>
+    <t>dlwngud77777@naver.com</t>
+  </si>
+  <si>
+    <t>이주형</t>
+  </si>
+  <si>
+    <t>haramie05@naver.com</t>
+  </si>
+  <si>
+    <t>디지털미디어콘텐츠전공</t>
+  </si>
+  <si>
+    <t>김하람</t>
+  </si>
+  <si>
+    <t>wkdguswns16@naver.com</t>
+  </si>
+  <si>
+    <t>장현준</t>
+  </si>
+  <si>
+    <t>kimdongkyun1108@gmail.com</t>
+  </si>
+  <si>
+    <t>김동균</t>
+  </si>
+  <si>
+    <t>skh4896@gmail.com</t>
+  </si>
+  <si>
+    <t>박재민</t>
+  </si>
+  <si>
+    <t>spino0908@naver.com</t>
+  </si>
+  <si>
+    <t>구현우</t>
+  </si>
+  <si>
+    <t>mj09045@naver.com</t>
+  </si>
+  <si>
+    <t>김민재</t>
+  </si>
+  <si>
+    <t>거의 중요하지 않다</t>
+  </si>
+  <si>
+    <t>bestkrh@naver.com</t>
+  </si>
+  <si>
+    <t>김래현</t>
+  </si>
+  <si>
+    <t>host051006@gmail.com</t>
+  </si>
+  <si>
+    <t>윤아영</t>
+  </si>
+  <si>
+    <t>sob3099@gmail.com</t>
+  </si>
+  <si>
+    <t>송종현</t>
+  </si>
+  <si>
+    <t>kmkben@naver.com</t>
+  </si>
+  <si>
+    <t>소프트웨어학과/빅데이터</t>
+  </si>
+  <si>
+    <t>김민규</t>
+  </si>
+  <si>
+    <t>wookyung7536@naver.com</t>
+  </si>
+  <si>
+    <t>양우경</t>
+  </si>
+  <si>
+    <t>kek2300@naver.com</t>
+  </si>
+  <si>
+    <t>박진현</t>
+  </si>
+  <si>
+    <t>cyw20242581@gmail.com</t>
+  </si>
+  <si>
+    <t>언론방송융합미디어</t>
+  </si>
+  <si>
+    <t>최영우</t>
+  </si>
+  <si>
+    <t>misobell520@naver.com</t>
+  </si>
+  <si>
+    <t>이현희</t>
+  </si>
+  <si>
+    <t>kuvin0808@naver.com</t>
+  </si>
+  <si>
+    <t>이규빈</t>
+  </si>
+  <si>
+    <t>pyo9630@gmail.com</t>
+  </si>
+  <si>
+    <t>이충영</t>
+  </si>
+  <si>
+    <t>gka4057@naver.com</t>
+  </si>
+  <si>
+    <t>함효린</t>
+  </si>
+  <si>
+    <t>jiwon020522@naver.com</t>
+  </si>
+  <si>
+    <t>박지원</t>
+  </si>
+  <si>
+    <t>rudtlr419@naver.com</t>
+  </si>
+  <si>
+    <t>장경식</t>
+  </si>
+  <si>
+    <t>rlacksrud12@naver.com</t>
+  </si>
+  <si>
+    <t>김찬경</t>
+  </si>
+  <si>
+    <t>skdda1073@naver.com</t>
+  </si>
+  <si>
+    <t>고경완</t>
+  </si>
+  <si>
+    <t>gmls3318@naver.com</t>
+  </si>
+  <si>
+    <t>변희연</t>
+  </si>
+  <si>
+    <t>seahorse93076714@gmail.com</t>
+  </si>
+  <si>
+    <t>이지원</t>
+  </si>
+  <si>
+    <t>kimjnuadad@naver.com</t>
+  </si>
+  <si>
+    <t>김도연</t>
+  </si>
+  <si>
+    <t>wnsduq285@gmail.com</t>
+  </si>
+  <si>
+    <t>박준엽</t>
+  </si>
+  <si>
+    <t>yangkyung04@naver.com</t>
+  </si>
+  <si>
+    <t>양경호</t>
+  </si>
+  <si>
+    <t>kmj2542233@naver.com</t>
+  </si>
+  <si>
+    <t>김민지</t>
+  </si>
+  <si>
+    <t>kwan0172@gmail.com</t>
+  </si>
+  <si>
+    <t>김관형</t>
   </si>
 </sst>
 </file>
@@ -1481,7 +1889,7 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="12">
     <border/>
     <border>
       <left style="thin">
@@ -1614,10 +2022,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1625,27 +2033,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF8F9FA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF442F65"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFF8F9FA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF442F65"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFF8F9FA"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -1655,7 +2049,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1702,9 +2096,6 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="12" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
@@ -1765,7 +2156,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N185" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N248" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -9550,43 +9941,2626 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="14">
+      <c r="A185" s="8">
         <v>45730.26984868056</v>
       </c>
-      <c r="B185" s="15" t="s">
+      <c r="B185" s="9" t="s">
         <v>478</v>
       </c>
-      <c r="C185" s="15" t="s">
+      <c r="C185" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="D185" s="15">
+      <c r="D185" s="9">
         <v>2.0212744E7</v>
       </c>
-      <c r="E185" s="15" t="s">
+      <c r="E185" s="9" t="s">
         <v>479</v>
       </c>
-      <c r="F185" s="15" t="s">
+      <c r="F185" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G185" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H185" s="15">
-        <v>2017.0</v>
-      </c>
-      <c r="I185" s="15">
+      <c r="G185" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H185" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I185" s="9">
         <v>2019.0</v>
       </c>
-      <c r="J185" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="K185" s="15" t="s">
+      <c r="J185" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K185" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="L185" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="N185" s="16" t="s">
+      <c r="L185" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N185" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="11">
+        <v>45730.39729116898</v>
+      </c>
+      <c r="B186" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="C186" s="12" t="s">
+        <v>481</v>
+      </c>
+      <c r="D186" s="12">
+        <v>2.0241022E7</v>
+      </c>
+      <c r="E186" s="12" t="s">
+        <v>482</v>
+      </c>
+      <c r="F186" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G186" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H186" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I186" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J186" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K186" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L186" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M186" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="8">
+        <v>45730.432286967596</v>
+      </c>
+      <c r="B187" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C187" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="D187" s="9">
+        <v>2.0231725E7</v>
+      </c>
+      <c r="E187" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="F187" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G187" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H187" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I187" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J187" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K187" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L187" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N187" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="11">
+        <v>45730.45570695602</v>
+      </c>
+      <c r="B188" s="12" t="s">
+        <v>486</v>
+      </c>
+      <c r="C188" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D188" s="12">
+        <v>2.0246916E7</v>
+      </c>
+      <c r="E188" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="F188" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G188" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H188" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I188" s="12">
+        <v>2021.0</v>
+      </c>
+      <c r="J188" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K188" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L188" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N188" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="8">
+        <v>45730.474726712964</v>
+      </c>
+      <c r="B189" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="C189" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="D189" s="9">
+        <v>2.0246777E7</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>490</v>
+      </c>
+      <c r="F189" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G189" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H189" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I189" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J189" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K189" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L189" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N189" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="11">
+        <v>45730.52888028935</v>
+      </c>
+      <c r="B190" s="12" t="s">
+        <v>491</v>
+      </c>
+      <c r="C190" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D190" s="12">
+        <v>2.0242431E7</v>
+      </c>
+      <c r="E190" s="12" t="s">
+        <v>492</v>
+      </c>
+      <c r="F190" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G190" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H190" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I190" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J190" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K190" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L190" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M190" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="8">
+        <v>45730.5397672338</v>
+      </c>
+      <c r="B191" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="C191" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D191" s="9">
+        <v>2.0242438E7</v>
+      </c>
+      <c r="E191" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="F191" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G191" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H191" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I191" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J191" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K191" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L191" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N191" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="11">
+        <v>45730.550829583335</v>
+      </c>
+      <c r="B192" s="12" t="s">
+        <v>495</v>
+      </c>
+      <c r="C192" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="D192" s="12">
+        <v>2.0231097E7</v>
+      </c>
+      <c r="E192" s="12" t="s">
+        <v>496</v>
+      </c>
+      <c r="F192" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G192" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H192" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I192" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J192" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K192" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L192" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M192" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="8">
+        <v>45730.56150894676</v>
+      </c>
+      <c r="B193" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="C193" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D193" s="9">
+        <v>2.0223517E7</v>
+      </c>
+      <c r="E193" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="F193" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G193" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H193" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I193" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J193" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K193" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L193" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M193" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="11">
+        <v>45730.6283616088</v>
+      </c>
+      <c r="B194" s="12" t="s">
+        <v>499</v>
+      </c>
+      <c r="C194" s="12" t="s">
+        <v>500</v>
+      </c>
+      <c r="D194" s="12">
+        <v>2.0241725E7</v>
+      </c>
+      <c r="E194" s="12" t="s">
+        <v>501</v>
+      </c>
+      <c r="F194" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G194" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H194" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I194" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J194" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K194" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L194" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N194" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="8">
+        <v>45730.63010833334</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>502</v>
+      </c>
+      <c r="C195" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="D195" s="9">
+        <v>2.0243233E7</v>
+      </c>
+      <c r="E195" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="F195" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G195" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H195" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I195" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J195" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K195" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L195" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M195" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="11">
+        <v>45730.63043950232</v>
+      </c>
+      <c r="B196" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="C196" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D196" s="12">
+        <v>2.0243713E7</v>
+      </c>
+      <c r="E196" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="F196" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G196" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H196" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I196" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J196" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K196" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L196" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N196" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="8">
+        <v>45730.65439318287</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="C197" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D197" s="9">
+        <v>2.0233901E7</v>
+      </c>
+      <c r="E197" s="9" t="s">
+        <v>508</v>
+      </c>
+      <c r="F197" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G197" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H197" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I197" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J197" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K197" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L197" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M197" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="11">
+        <v>45730.65722318287</v>
+      </c>
+      <c r="B198" s="12" t="s">
+        <v>509</v>
+      </c>
+      <c r="C198" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D198" s="12">
+        <v>2.0242432E7</v>
+      </c>
+      <c r="E198" s="12" t="s">
+        <v>510</v>
+      </c>
+      <c r="F198" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G198" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H198" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I198" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J198" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K198" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L198" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N198" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="8">
+        <v>45730.70683594907</v>
+      </c>
+      <c r="B199" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="C199" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D199" s="9">
+        <v>2.0227071E7</v>
+      </c>
+      <c r="E199" s="9" t="s">
+        <v>512</v>
+      </c>
+      <c r="F199" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G199" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H199" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I199" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J199" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K199" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L199" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M199" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="11">
+        <v>45730.756049131945</v>
+      </c>
+      <c r="B200" s="12" t="s">
+        <v>513</v>
+      </c>
+      <c r="C200" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D200" s="12">
+        <v>2.0203735E7</v>
+      </c>
+      <c r="E200" s="12" t="s">
+        <v>514</v>
+      </c>
+      <c r="F200" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G200" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H200" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I200" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J200" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K200" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L200" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M200" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="8">
+        <v>45730.76766952546</v>
+      </c>
+      <c r="B201" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="C201" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="D201" s="9">
+        <v>2.0226711E7</v>
+      </c>
+      <c r="E201" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="F201" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G201" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H201" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I201" s="9">
+        <v>2021.0</v>
+      </c>
+      <c r="J201" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K201" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L201" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N201" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="11">
+        <v>45730.78573621528</v>
+      </c>
+      <c r="B202" s="12" t="s">
+        <v>518</v>
+      </c>
+      <c r="C202" s="12" t="s">
+        <v>443</v>
+      </c>
+      <c r="D202" s="12">
+        <v>2.0221111E7</v>
+      </c>
+      <c r="E202" s="12" t="s">
+        <v>519</v>
+      </c>
+      <c r="F202" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G202" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H202" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I202" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J202" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K202" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L202" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N202" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="8">
+        <v>45730.810834351854</v>
+      </c>
+      <c r="B203" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="C203" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D203" s="9">
+        <v>2.0201044E7</v>
+      </c>
+      <c r="E203" s="9" t="s">
+        <v>521</v>
+      </c>
+      <c r="F203" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G203" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H203" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I203" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J203" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K203" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L203" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M203" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="11">
+        <v>45730.821793449075</v>
+      </c>
+      <c r="B204" s="12" t="s">
+        <v>522</v>
+      </c>
+      <c r="C204" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D204" s="12">
+        <v>2.0221534E7</v>
+      </c>
+      <c r="E204" s="12" t="s">
+        <v>523</v>
+      </c>
+      <c r="F204" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G204" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H204" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I204" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J204" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K204" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L204" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N204" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="8">
+        <v>45730.88194063657</v>
+      </c>
+      <c r="B205" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="C205" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D205" s="9">
+        <v>2.0243845E7</v>
+      </c>
+      <c r="E205" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="F205" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G205" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H205" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I205" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J205" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K205" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L205" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N205" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="11">
+        <v>45730.9475628588</v>
+      </c>
+      <c r="B206" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="C206" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D206" s="12">
+        <v>2.0222318E7</v>
+      </c>
+      <c r="E206" s="12" t="s">
+        <v>527</v>
+      </c>
+      <c r="F206" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G206" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H206" s="12">
+        <v>2027.0</v>
+      </c>
+      <c r="I206" s="12">
+        <v>2021.0</v>
+      </c>
+      <c r="J206" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K206" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L206" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M206" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="8">
+        <v>45730.947579803236</v>
+      </c>
+      <c r="B207" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="C207" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D207" s="9">
+        <v>2.0223023E7</v>
+      </c>
+      <c r="E207" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="F207" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G207" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H207" s="9">
+        <v>2027.0</v>
+      </c>
+      <c r="I207" s="9">
+        <v>2021.0</v>
+      </c>
+      <c r="J207" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K207" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L207" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N207" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="11">
+        <v>45730.976591666666</v>
+      </c>
+      <c r="B208" s="12" t="s">
+        <v>530</v>
+      </c>
+      <c r="C208" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="D208" s="12">
+        <v>2.0235101E7</v>
+      </c>
+      <c r="E208" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="F208" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G208" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H208" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I208" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J208" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K208" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L208" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N208" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="8">
+        <v>45730.99154511574</v>
+      </c>
+      <c r="B209" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="C209" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D209" s="9">
+        <v>2.0212952E7</v>
+      </c>
+      <c r="E209" s="9" t="s">
+        <v>533</v>
+      </c>
+      <c r="F209" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G209" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H209" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I209" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J209" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K209" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L209" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M209" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="11">
+        <v>45730.99264163194</v>
+      </c>
+      <c r="B210" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="C210" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D210" s="12">
+        <v>2.0246237E7</v>
+      </c>
+      <c r="E210" s="12" t="s">
+        <v>535</v>
+      </c>
+      <c r="F210" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G210" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H210" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I210" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J210" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K210" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L210" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M210" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="8">
+        <v>45731.01766078704</v>
+      </c>
+      <c r="B211" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="C211" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D211" s="9">
+        <v>2.0242208E7</v>
+      </c>
+      <c r="E211" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="F211" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G211" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H211" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I211" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J211" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K211" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L211" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N211" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="11">
+        <v>45731.02350166667</v>
+      </c>
+      <c r="B212" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="C212" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D212" s="12">
+        <v>2.0212721E7</v>
+      </c>
+      <c r="E212" s="12" t="s">
+        <v>539</v>
+      </c>
+      <c r="F212" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G212" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H212" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I212" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J212" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K212" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L212" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M212" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="8">
+        <v>45731.07114450232</v>
+      </c>
+      <c r="B213" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="C213" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D213" s="9">
+        <v>2.0242964E7</v>
+      </c>
+      <c r="E213" s="9" t="s">
+        <v>541</v>
+      </c>
+      <c r="F213" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G213" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H213" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I213" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J213" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K213" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L213" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N213" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="11">
+        <v>45731.41159737269</v>
+      </c>
+      <c r="B214" s="12" t="s">
+        <v>542</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D214" s="12">
+        <v>2.0215156E7</v>
+      </c>
+      <c r="E214" s="12" t="s">
+        <v>543</v>
+      </c>
+      <c r="F214" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G214" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H214" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I214" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J214" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K214" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L214" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N214" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="8">
+        <v>45731.452807037036</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="C215" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="D215" s="9">
+        <v>2.0245216E7</v>
+      </c>
+      <c r="E215" s="9" t="s">
+        <v>545</v>
+      </c>
+      <c r="F215" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G215" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H215" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I215" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J215" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K215" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L215" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N215" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="11">
+        <v>45731.530208553246</v>
+      </c>
+      <c r="B216" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="C216" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D216" s="12">
+        <v>2.0222901E7</v>
+      </c>
+      <c r="E216" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="F216" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G216" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H216" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I216" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J216" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K216" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L216" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N216" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="8">
+        <v>45731.55531490741</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="C217" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D217" s="9">
+        <v>2.0225213E7</v>
+      </c>
+      <c r="E217" s="9" t="s">
+        <v>549</v>
+      </c>
+      <c r="F217" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G217" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H217" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I217" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J217" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K217" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L217" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M217" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="11">
+        <v>45731.56757165509</v>
+      </c>
+      <c r="B218" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="C218" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D218" s="12">
+        <v>2.021271E7</v>
+      </c>
+      <c r="E218" s="12" t="s">
+        <v>551</v>
+      </c>
+      <c r="F218" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G218" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H218" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I218" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J218" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K218" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L218" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M218" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="8">
+        <v>45731.624744444445</v>
+      </c>
+      <c r="B219" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="C219" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D219" s="9">
+        <v>2.0223515E7</v>
+      </c>
+      <c r="E219" s="9" t="s">
+        <v>553</v>
+      </c>
+      <c r="F219" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G219" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H219" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I219" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J219" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K219" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L219" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N219" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="11">
+        <v>45731.63182314815</v>
+      </c>
+      <c r="B220" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="C220" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D220" s="12">
+        <v>2.0194143E7</v>
+      </c>
+      <c r="E220" s="12" t="s">
+        <v>555</v>
+      </c>
+      <c r="F220" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G220" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H220" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I220" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J220" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K220" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L220" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M220" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="8">
+        <v>45731.63310644676</v>
+      </c>
+      <c r="B221" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="C221" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="D221" s="9">
+        <v>2.0242519E7</v>
+      </c>
+      <c r="E221" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="F221" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G221" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H221" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I221" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J221" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K221" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L221" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N221" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="11">
+        <v>45731.64020069444</v>
+      </c>
+      <c r="B222" s="12" t="s">
+        <v>559</v>
+      </c>
+      <c r="C222" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D222" s="12">
+        <v>2.0213033E7</v>
+      </c>
+      <c r="E222" s="12" t="s">
+        <v>560</v>
+      </c>
+      <c r="F222" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G222" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H222" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I222" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J222" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K222" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L222" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N222" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="8">
+        <v>45731.65520892361</v>
+      </c>
+      <c r="B223" s="9" t="s">
+        <v>561</v>
+      </c>
+      <c r="C223" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D223" s="9">
+        <v>2.023512E7</v>
+      </c>
+      <c r="E223" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="F223" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G223" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H223" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I223" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J223" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K223" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L223" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M223" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="11">
+        <v>45731.67663765047</v>
+      </c>
+      <c r="B224" s="12" t="s">
+        <v>563</v>
+      </c>
+      <c r="C224" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="D224" s="12">
+        <v>2.0226743E7</v>
+      </c>
+      <c r="E224" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="F224" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G224" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H224" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I224" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J224" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K224" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L224" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M224" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="8">
+        <v>45731.725625543986</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>565</v>
+      </c>
+      <c r="C225" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="D225" s="9">
+        <v>2.0211005E7</v>
+      </c>
+      <c r="E225" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="F225" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G225" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H225" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I225" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J225" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K225" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L225" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M225" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="11">
+        <v>45731.75728071759</v>
+      </c>
+      <c r="B226" s="12" t="s">
+        <v>567</v>
+      </c>
+      <c r="C226" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D226" s="12">
+        <v>2.0202917E7</v>
+      </c>
+      <c r="E226" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="F226" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G226" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="H226" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I226" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J226" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K226" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L226" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N226" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="8">
+        <v>45731.76013659722</v>
+      </c>
+      <c r="B227" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="C227" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D227" s="9">
+        <v>2.0252916E7</v>
+      </c>
+      <c r="E227" s="9" t="s">
+        <v>571</v>
+      </c>
+      <c r="F227" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G227" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H227" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I227" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J227" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K227" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L227" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N227" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="11">
+        <v>45731.76020163194</v>
+      </c>
+      <c r="B228" s="12" t="s">
+        <v>572</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D228" s="12">
+        <v>2.0246929E7</v>
+      </c>
+      <c r="E228" s="12" t="s">
+        <v>573</v>
+      </c>
+      <c r="F228" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G228" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H228" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I228" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J228" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K228" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L228" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N228" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="8">
+        <v>45731.77399324074</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="C229" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="D229" s="9">
+        <v>2.0231049E7</v>
+      </c>
+      <c r="E229" s="9" t="s">
+        <v>575</v>
+      </c>
+      <c r="F229" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G229" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H229" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I229" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J229" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K229" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L229" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M229" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="11">
+        <v>45731.7800645949</v>
+      </c>
+      <c r="B230" s="12" t="s">
+        <v>576</v>
+      </c>
+      <c r="C230" s="12" t="s">
+        <v>577</v>
+      </c>
+      <c r="D230" s="12">
+        <v>2.020513E7</v>
+      </c>
+      <c r="E230" s="12" t="s">
+        <v>578</v>
+      </c>
+      <c r="F230" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G230" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H230" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I230" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J230" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K230" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L230" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M230" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="8">
+        <v>45731.789129259254</v>
+      </c>
+      <c r="B231" s="9" t="s">
+        <v>579</v>
+      </c>
+      <c r="C231" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D231" s="9">
+        <v>2.0212223E7</v>
+      </c>
+      <c r="E231" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="F231" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G231" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H231" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I231" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J231" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K231" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L231" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M231" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="11">
+        <v>45731.79608907407</v>
+      </c>
+      <c r="B232" s="12" t="s">
+        <v>581</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="D232" s="12">
+        <v>2.0203619E7</v>
+      </c>
+      <c r="E232" s="12" t="s">
+        <v>582</v>
+      </c>
+      <c r="F232" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G232" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H232" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I232" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J232" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K232" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L232" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N232" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="8">
+        <v>45731.8125205324</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>583</v>
+      </c>
+      <c r="C233" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="D233" s="9">
+        <v>2.0242581E7</v>
+      </c>
+      <c r="E233" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="F233" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G233" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H233" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I233" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J233" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="K233" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L233" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M233" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="11">
+        <v>45731.833720787035</v>
+      </c>
+      <c r="B234" s="12" t="s">
+        <v>586</v>
+      </c>
+      <c r="C234" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="D234" s="12">
+        <v>2.0242564E7</v>
+      </c>
+      <c r="E234" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="F234" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G234" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H234" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I234" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J234" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K234" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L234" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M234" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="8">
+        <v>45731.8351175</v>
+      </c>
+      <c r="B235" s="9" t="s">
+        <v>588</v>
+      </c>
+      <c r="C235" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D235" s="9">
+        <v>2.0233418E7</v>
+      </c>
+      <c r="E235" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="F235" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G235" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H235" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I235" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J235" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K235" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L235" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M235" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="11">
+        <v>45731.83774560185</v>
+      </c>
+      <c r="B236" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="C236" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D236" s="12">
+        <v>2.0222427E7</v>
+      </c>
+      <c r="E236" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="F236" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G236" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H236" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I236" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J236" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K236" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L236" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M236" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="8">
+        <v>45731.84523741898</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>592</v>
+      </c>
+      <c r="C237" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D237" s="9">
+        <v>2.0243848E7</v>
+      </c>
+      <c r="E237" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="F237" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G237" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H237" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I237" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J237" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K237" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L237" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N237" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="11">
+        <v>45731.84951690972</v>
+      </c>
+      <c r="B238" s="12" t="s">
+        <v>594</v>
+      </c>
+      <c r="C238" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D238" s="12">
+        <v>2.021707E7</v>
+      </c>
+      <c r="E238" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="F238" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G238" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H238" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I238" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J238" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K238" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L238" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M238" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="8">
+        <v>45731.89802846065</v>
+      </c>
+      <c r="B239" s="9" t="s">
+        <v>596</v>
+      </c>
+      <c r="C239" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D239" s="9">
+        <v>2.0242741E7</v>
+      </c>
+      <c r="E239" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="F239" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G239" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H239" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I239" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J239" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K239" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L239" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M239" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="11">
+        <v>45731.90061597222</v>
+      </c>
+      <c r="B240" s="12" t="s">
+        <v>598</v>
+      </c>
+      <c r="C240" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D240" s="12">
+        <v>2.0202934E7</v>
+      </c>
+      <c r="E240" s="12" t="s">
+        <v>599</v>
+      </c>
+      <c r="F240" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G240" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H240" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I240" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J240" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K240" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L240" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N240" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="8">
+        <v>45731.90588680556</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>600</v>
+      </c>
+      <c r="C241" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="D241" s="9">
+        <v>2.0226702E7</v>
+      </c>
+      <c r="E241" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="F241" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G241" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H241" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I241" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J241" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K241" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L241" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M241" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="11">
+        <v>45731.915525185184</v>
+      </c>
+      <c r="B242" s="12" t="s">
+        <v>602</v>
+      </c>
+      <c r="C242" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D242" s="12">
+        <v>2.0237008E7</v>
+      </c>
+      <c r="E242" s="12" t="s">
+        <v>603</v>
+      </c>
+      <c r="F242" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G242" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H242" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I242" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J242" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K242" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L242" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N242" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="8">
+        <v>45731.92057203704</v>
+      </c>
+      <c r="B243" s="9" t="s">
+        <v>604</v>
+      </c>
+      <c r="C243" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="D243" s="9">
+        <v>2.0241229E7</v>
+      </c>
+      <c r="E243" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="F243" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G243" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H243" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I243" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J243" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K243" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L243" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M243" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="11">
+        <v>45731.93087224537</v>
+      </c>
+      <c r="B244" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="C244" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D244" s="12">
+        <v>2.0241201E7</v>
+      </c>
+      <c r="E244" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="F244" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G244" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H244" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I244" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J244" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K244" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L244" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N244" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="8">
+        <v>45731.94410537037</v>
+      </c>
+      <c r="B245" s="9" t="s">
+        <v>608</v>
+      </c>
+      <c r="C245" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D245" s="9">
+        <v>2.0227096E7</v>
+      </c>
+      <c r="E245" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="F245" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G245" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H245" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I245" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J245" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K245" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L245" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N245" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="11">
+        <v>45731.949097986115</v>
+      </c>
+      <c r="B246" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="C246" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D246" s="12">
+        <v>2.024372E7</v>
+      </c>
+      <c r="E246" s="12" t="s">
+        <v>611</v>
+      </c>
+      <c r="F246" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G246" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H246" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I246" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J246" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K246" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L246" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N246" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="8">
+        <v>45731.96279914352</v>
+      </c>
+      <c r="B247" s="9" t="s">
+        <v>612</v>
+      </c>
+      <c r="C247" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D247" s="9">
+        <v>2.025271E7</v>
+      </c>
+      <c r="E247" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="F247" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G247" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H247" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I247" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J247" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K247" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L247" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M247" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="14">
+        <v>45731.97248777778</v>
+      </c>
+      <c r="B248" s="15" t="s">
+        <v>614</v>
+      </c>
+      <c r="C248" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D248" s="15">
+        <v>2.021291E7</v>
+      </c>
+      <c r="E248" s="15" t="s">
+        <v>615</v>
+      </c>
+      <c r="F248" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G248" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H248" s="15">
+        <v>2017.0</v>
+      </c>
+      <c r="I248" s="15">
+        <v>2020.0</v>
+      </c>
+      <c r="J248" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K248" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="L248" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="M248" s="15" t="s">
         <v>22</v>
       </c>
     </row>

--- a/R/data/quiz_250310.xlsx
+++ b/R/data/quiz_250310.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2237" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3263" uniqueCount="860">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -1859,6 +1859,738 @@
   </si>
   <si>
     <t>김관형</t>
+  </si>
+  <si>
+    <t>2005jkjk@naver.com</t>
+  </si>
+  <si>
+    <t>글로벌비즈니스전공</t>
+  </si>
+  <si>
+    <t>최나윤</t>
+  </si>
+  <si>
+    <t>lee.jaehyeok0903@gmail.com</t>
+  </si>
+  <si>
+    <t>이재혁</t>
+  </si>
+  <si>
+    <t>qusdnwls12@gmail.com</t>
+  </si>
+  <si>
+    <t>변우진</t>
+  </si>
+  <si>
+    <t>ayourg@naver.com</t>
+  </si>
+  <si>
+    <t>사회복지학전공</t>
+  </si>
+  <si>
+    <t>신아영</t>
+  </si>
+  <si>
+    <t>haeyoon205@gmail.com</t>
+  </si>
+  <si>
+    <t>철학전공</t>
+  </si>
+  <si>
+    <t>정해윤</t>
+  </si>
+  <si>
+    <t>coolalex127@gmail.com</t>
+  </si>
+  <si>
+    <t>양윤모</t>
+  </si>
+  <si>
+    <t>aannddyy350@gmail.com</t>
+  </si>
+  <si>
+    <t>이승환</t>
+  </si>
+  <si>
+    <t>20223505@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>생명과학</t>
+  </si>
+  <si>
+    <t>권준성</t>
+  </si>
+  <si>
+    <t>hours00@naver.com</t>
+  </si>
+  <si>
+    <t>우수민</t>
+  </si>
+  <si>
+    <t>llimjh123@naver.com</t>
+  </si>
+  <si>
+    <t>임준완</t>
+  </si>
+  <si>
+    <t>xeoxeoy@naver.com</t>
+  </si>
+  <si>
+    <t>임서영</t>
+  </si>
+  <si>
+    <t>yeolpk0930@naver.com</t>
+  </si>
+  <si>
+    <t>박동빈</t>
+  </si>
+  <si>
+    <t>hallymjhj@gmail.com</t>
+  </si>
+  <si>
+    <t>장혁진</t>
+  </si>
+  <si>
+    <t>bakhanseong11@gmail.com</t>
+  </si>
+  <si>
+    <t>박한성</t>
+  </si>
+  <si>
+    <t>nahm63@naver.com</t>
+  </si>
+  <si>
+    <t>인문학부 철학전공</t>
+  </si>
+  <si>
+    <t>김남엽</t>
+  </si>
+  <si>
+    <t>nkav1234@naver.com</t>
+  </si>
+  <si>
+    <t>박종민</t>
+  </si>
+  <si>
+    <t>ychoe119@gmail.com</t>
+  </si>
+  <si>
+    <t>최윤서</t>
+  </si>
+  <si>
+    <t>gyuha8489@gmail.com</t>
+  </si>
+  <si>
+    <t>김유하</t>
+  </si>
+  <si>
+    <t>brianbrian317@daum.net</t>
+  </si>
+  <si>
+    <t>김보성</t>
+  </si>
+  <si>
+    <t>qqeeww9090@gmail.com</t>
+  </si>
+  <si>
+    <t>경규남</t>
+  </si>
+  <si>
+    <t>pio__@naver.com</t>
+  </si>
+  <si>
+    <t>디지털미디어콘텐츠학과</t>
+  </si>
+  <si>
+    <t>김남영</t>
+  </si>
+  <si>
+    <t>csu1102@naver.com</t>
+  </si>
+  <si>
+    <t>조성운</t>
+  </si>
+  <si>
+    <t>woojoong0221@gmail.com</t>
+  </si>
+  <si>
+    <t>디지털인문예술</t>
+  </si>
+  <si>
+    <t>김우중</t>
+  </si>
+  <si>
+    <t>leesojin0000@naver.com</t>
+  </si>
+  <si>
+    <t>이소진</t>
+  </si>
+  <si>
+    <t>justin99961@gmail.com</t>
+  </si>
+  <si>
+    <t>조연서</t>
+  </si>
+  <si>
+    <t>hansuhyun0809@naver.com</t>
+  </si>
+  <si>
+    <t>한수현</t>
+  </si>
+  <si>
+    <t>cksgh582@gmail.com</t>
+  </si>
+  <si>
+    <t>체유학과</t>
+  </si>
+  <si>
+    <t>박찬호</t>
+  </si>
+  <si>
+    <t>ksyprosch11@gmail.com</t>
+  </si>
+  <si>
+    <t>김서연</t>
+  </si>
+  <si>
+    <t>ysj030412@gmail.com</t>
+  </si>
+  <si>
+    <t>윤성중</t>
+  </si>
+  <si>
+    <t>capjjjmj@naver.com</t>
+  </si>
+  <si>
+    <t>전민정</t>
+  </si>
+  <si>
+    <t>ngjh1026@gmail.com</t>
+  </si>
+  <si>
+    <t>한림대학교</t>
+  </si>
+  <si>
+    <t>남궁정현</t>
+  </si>
+  <si>
+    <t>a53309705@gmail.com</t>
+  </si>
+  <si>
+    <t>반도체 디스플레이</t>
+  </si>
+  <si>
+    <t>박상훈</t>
+  </si>
+  <si>
+    <t>yangsj0626@gmail.com</t>
+  </si>
+  <si>
+    <t>양선준</t>
+  </si>
+  <si>
+    <t>jenny_0603@naver.com</t>
+  </si>
+  <si>
+    <t>이지수</t>
+  </si>
+  <si>
+    <t>iamhdm@naver.com</t>
+  </si>
+  <si>
+    <t>황동민</t>
+  </si>
+  <si>
+    <t>kdh000224@naver.com</t>
+  </si>
+  <si>
+    <t>김동현</t>
+  </si>
+  <si>
+    <t>20202514@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>김윤아</t>
+  </si>
+  <si>
+    <t>woonusannus@gmail.com</t>
+  </si>
+  <si>
+    <t>박현우</t>
+  </si>
+  <si>
+    <t>0205ysm@naver.com</t>
+  </si>
+  <si>
+    <t>유승민</t>
+  </si>
+  <si>
+    <t>castle@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>배은성</t>
+  </si>
+  <si>
+    <t>dlalswn221@naver.com</t>
+  </si>
+  <si>
+    <t>이민주</t>
+  </si>
+  <si>
+    <t>lhp050705@gmail.com</t>
+  </si>
+  <si>
+    <t>청각학부</t>
+  </si>
+  <si>
+    <t>이현표</t>
+  </si>
+  <si>
+    <t>kiss040924@gmail.com</t>
+  </si>
+  <si>
+    <t>김무원</t>
+  </si>
+  <si>
+    <t>jun050510@naver.com</t>
+  </si>
+  <si>
+    <t>유한준</t>
+  </si>
+  <si>
+    <t>lee_tmdgus@naver.com</t>
+  </si>
+  <si>
+    <t>이승현</t>
+  </si>
+  <si>
+    <t>zosel1595@naver.com</t>
+  </si>
+  <si>
+    <t>최성민</t>
+  </si>
+  <si>
+    <t>song_050929@naver.com</t>
+  </si>
+  <si>
+    <t>송은채</t>
+  </si>
+  <si>
+    <t>yookh114@gmail.com</t>
+  </si>
+  <si>
+    <t>유강현</t>
+  </si>
+  <si>
+    <t>jackkhc02@naver.com</t>
+  </si>
+  <si>
+    <t>김세윤</t>
+  </si>
+  <si>
+    <t>dlwldn010108@naver.com</t>
+  </si>
+  <si>
+    <t>이지우</t>
+  </si>
+  <si>
+    <t>guschdl0313@gmail.com</t>
+  </si>
+  <si>
+    <t>최현종</t>
+  </si>
+  <si>
+    <t>0821choi@gmail.com</t>
+  </si>
+  <si>
+    <t>반도체•디스플레이스쿨</t>
+  </si>
+  <si>
+    <t>최시온</t>
+  </si>
+  <si>
+    <t>echanwoo48@gmail.com</t>
+  </si>
+  <si>
+    <t>이찬우</t>
+  </si>
+  <si>
+    <t>solyooncho@gmail.com</t>
+  </si>
+  <si>
+    <t>조윤솔</t>
+  </si>
+  <si>
+    <t>iyw120@naver.com</t>
+  </si>
+  <si>
+    <t>박규빈</t>
+  </si>
+  <si>
+    <t>ssw29772977@gmail.com</t>
+  </si>
+  <si>
+    <t>성승원</t>
+  </si>
+  <si>
+    <t>lminseok1228@gmail.com</t>
+  </si>
+  <si>
+    <t>이민석</t>
+  </si>
+  <si>
+    <t>h20202591@glab.hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>홍기민</t>
+  </si>
+  <si>
+    <t>jaho73220@gmail.com</t>
+  </si>
+  <si>
+    <t>이재호</t>
+  </si>
+  <si>
+    <t>8676sua@gmail.com</t>
+  </si>
+  <si>
+    <t>조수아</t>
+  </si>
+  <si>
+    <t>djun321@naver.com</t>
+  </si>
+  <si>
+    <t>황동준</t>
+  </si>
+  <si>
+    <t>whdlstjd02@gmail.com</t>
+  </si>
+  <si>
+    <t>조인성</t>
+  </si>
+  <si>
+    <t>kms706375@gmail.com</t>
+  </si>
+  <si>
+    <t>김민수</t>
+  </si>
+  <si>
+    <t>a95123236@gmail.com</t>
+  </si>
+  <si>
+    <t>임진우</t>
+  </si>
+  <si>
+    <t>yelin0612@naver.com</t>
+  </si>
+  <si>
+    <t>권예린</t>
+  </si>
+  <si>
+    <t>nick6723@naver.com</t>
+  </si>
+  <si>
+    <t>의약신소재공학과 미래융합스쿨</t>
+  </si>
+  <si>
+    <t>유준상</t>
+  </si>
+  <si>
+    <t>sop1210805@gmail.com</t>
+  </si>
+  <si>
+    <t>이정진</t>
+  </si>
+  <si>
+    <t>tegentoppa0641@gmail.com</t>
+  </si>
+  <si>
+    <t>이정민</t>
+  </si>
+  <si>
+    <t>ae11021111@gmail.com</t>
+  </si>
+  <si>
+    <t>정대현</t>
+  </si>
+  <si>
+    <t>mikyoung327586@gmail.com</t>
+  </si>
+  <si>
+    <t>박찬희</t>
+  </si>
+  <si>
+    <t>jeffdong05112@naver.com</t>
+  </si>
+  <si>
+    <t>융합신소재공학부</t>
+  </si>
+  <si>
+    <t>서동찬</t>
+  </si>
+  <si>
+    <t>seodonghyeong7330@gmail.com</t>
+  </si>
+  <si>
+    <t>서동형</t>
+  </si>
+  <si>
+    <t>tkdahr022@naver.com</t>
+  </si>
+  <si>
+    <t>길상목</t>
+  </si>
+  <si>
+    <t>yuri060314@naver.com</t>
+  </si>
+  <si>
+    <t>정유리</t>
+  </si>
+  <si>
+    <t>seoyeon9446@naver.com</t>
+  </si>
+  <si>
+    <t>조서연</t>
+  </si>
+  <si>
+    <t>2005tree@gmail.com</t>
+  </si>
+  <si>
+    <t>신영욱</t>
+  </si>
+  <si>
+    <t>2013bin@naver.com</t>
+  </si>
+  <si>
+    <t>박유빈</t>
+  </si>
+  <si>
+    <t>pyr0528@naver.com</t>
+  </si>
+  <si>
+    <t>박예린</t>
+  </si>
+  <si>
+    <t>hull7614@gmail.com</t>
+  </si>
+  <si>
+    <t>남궁효경</t>
+  </si>
+  <si>
+    <t>black319shadow@gamil.con</t>
+  </si>
+  <si>
+    <t>김솔</t>
+  </si>
+  <si>
+    <t>hyunjoon0504@gmail.com</t>
+  </si>
+  <si>
+    <t>소프트웨어</t>
+  </si>
+  <si>
+    <t>최현준</t>
+  </si>
+  <si>
+    <t>20226614@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>김태현</t>
+  </si>
+  <si>
+    <t>frogisvi@gmail.com</t>
+  </si>
+  <si>
+    <t>권세희</t>
+  </si>
+  <si>
+    <t>deoduck877@naver.com</t>
+  </si>
+  <si>
+    <t>김동규</t>
+  </si>
+  <si>
+    <t>ahgjark11@naver.com</t>
+  </si>
+  <si>
+    <t>김동률</t>
+  </si>
+  <si>
+    <t>dltldms0908@naver.com</t>
+  </si>
+  <si>
+    <t>이시은</t>
+  </si>
+  <si>
+    <t>cws0241@naver.com</t>
+  </si>
+  <si>
+    <t>최우성</t>
+  </si>
+  <si>
+    <t>rjh9567@naver.com</t>
+  </si>
+  <si>
+    <t>언론방송융합미디어 전공</t>
+  </si>
+  <si>
+    <t>유채하</t>
+  </si>
+  <si>
+    <t>a.to.the.z.1087@gmail.com</t>
+  </si>
+  <si>
+    <t>김지혜</t>
+  </si>
+  <si>
+    <t>sjo47926@gmail.com</t>
+  </si>
+  <si>
+    <t>조서현</t>
+  </si>
+  <si>
+    <t>koyoonki1@gmail.com</t>
+  </si>
+  <si>
+    <t>고윤기</t>
+  </si>
+  <si>
+    <t>hyunjinfc2015@gmail.com</t>
+  </si>
+  <si>
+    <t>김현진</t>
+  </si>
+  <si>
+    <t>wldn2756@naver.com</t>
+  </si>
+  <si>
+    <t>박지우</t>
+  </si>
+  <si>
+    <t>manjo1234@naver.com</t>
+  </si>
+  <si>
+    <t>김민주</t>
+  </si>
+  <si>
+    <t>namu6186@naver.com</t>
+  </si>
+  <si>
+    <t>minser9265@gmail.com</t>
+  </si>
+  <si>
+    <t>정민서</t>
+  </si>
+  <si>
+    <t>aod1574@naver.com</t>
+  </si>
+  <si>
+    <t>맹은지</t>
+  </si>
+  <si>
+    <t>zesprie@naver.com</t>
+  </si>
+  <si>
+    <t>강미소</t>
+  </si>
+  <si>
+    <t>seounguk08@gmail.com</t>
+  </si>
+  <si>
+    <t>김승욱</t>
+  </si>
+  <si>
+    <t>cara0070322@gmail.com</t>
+  </si>
+  <si>
+    <t>신성민</t>
+  </si>
+  <si>
+    <t>rms2004gml@naver.com</t>
+  </si>
+  <si>
+    <t>장근희</t>
+  </si>
+  <si>
+    <t>20242236@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>정용원</t>
+  </si>
+  <si>
+    <t>dbgusdk0323@gmail.com</t>
+  </si>
+  <si>
+    <t>유현진</t>
+  </si>
+  <si>
+    <t>seoulsion123@gmail.com</t>
+  </si>
+  <si>
+    <t>tjdbs_s@naver.com</t>
+  </si>
+  <si>
+    <t>의약신소재전공</t>
+  </si>
+  <si>
+    <t>최서윤</t>
+  </si>
+  <si>
+    <t>scw0651@gmail.com</t>
+  </si>
+  <si>
+    <t>서창우</t>
+  </si>
+  <si>
+    <t>ehclfjqm@naver.com</t>
+  </si>
+  <si>
+    <t>변수현</t>
+  </si>
+  <si>
+    <t>rlaqufl1234@naver.com</t>
+  </si>
+  <si>
+    <t>김벼리</t>
+  </si>
+  <si>
+    <t>hongbeens@gmail.com</t>
+  </si>
+  <si>
+    <t>데이터사이언스</t>
+  </si>
+  <si>
+    <t>조홍빈</t>
+  </si>
+  <si>
+    <t>astpqls3541@naver.com</t>
+  </si>
+  <si>
+    <t>이세빈</t>
+  </si>
+  <si>
+    <t>20215177@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>신승훈</t>
+  </si>
+  <si>
+    <t>hyuki0514@naver.com</t>
+  </si>
+  <si>
+    <t>정준혁</t>
+  </si>
+  <si>
+    <t>scb0897@naver.com</t>
+  </si>
+  <si>
+    <t>신채빈</t>
+  </si>
+  <si>
+    <t>yewon0311_@naver.com</t>
+  </si>
+  <si>
+    <t>김예원</t>
   </si>
 </sst>
 </file>
@@ -2156,7 +2888,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N248" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N362" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -12524,44 +13256,4718 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="14">
+      <c r="A248" s="11">
         <v>45731.97248777778</v>
       </c>
-      <c r="B248" s="15" t="s">
+      <c r="B248" s="12" t="s">
         <v>614</v>
       </c>
-      <c r="C248" s="15" t="s">
+      <c r="C248" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="D248" s="15">
+      <c r="D248" s="12">
         <v>2.021291E7</v>
       </c>
-      <c r="E248" s="15" t="s">
+      <c r="E248" s="12" t="s">
         <v>615</v>
       </c>
-      <c r="F248" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G248" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H248" s="15">
-        <v>2017.0</v>
-      </c>
-      <c r="I248" s="15">
-        <v>2020.0</v>
-      </c>
-      <c r="J248" s="15" t="s">
+      <c r="F248" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G248" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H248" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I248" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J248" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="K248" s="15" t="s">
+      <c r="K248" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="L248" s="15" t="s">
+      <c r="L248" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="M248" s="15" t="s">
+      <c r="M248" s="12" t="s">
         <v>22</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="8">
+        <v>45731.99596943287</v>
+      </c>
+      <c r="B249" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="C249" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="D249" s="9">
+        <v>2.0246426E7</v>
+      </c>
+      <c r="E249" s="9" t="s">
+        <v>618</v>
+      </c>
+      <c r="F249" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G249" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H249" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I249" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J249" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K249" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L249" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N249" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="11">
+        <v>45732.00554662037</v>
+      </c>
+      <c r="B250" s="12" t="s">
+        <v>619</v>
+      </c>
+      <c r="C250" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D250" s="12">
+        <v>2.024394E7</v>
+      </c>
+      <c r="E250" s="12" t="s">
+        <v>620</v>
+      </c>
+      <c r="F250" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G250" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H250" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I250" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J250" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K250" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L250" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N250" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="8">
+        <v>45732.01163671297</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>621</v>
+      </c>
+      <c r="C251" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D251" s="9">
+        <v>2.0172727E7</v>
+      </c>
+      <c r="E251" s="9" t="s">
+        <v>622</v>
+      </c>
+      <c r="F251" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G251" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H251" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I251" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J251" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K251" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L251" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N251" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="11">
+        <v>45732.02509221065</v>
+      </c>
+      <c r="B252" s="12" t="s">
+        <v>623</v>
+      </c>
+      <c r="C252" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="D252" s="12">
+        <v>2.0242329E7</v>
+      </c>
+      <c r="E252" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="F252" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G252" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H252" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I252" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J252" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K252" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L252" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M252" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="8">
+        <v>45732.02633822917</v>
+      </c>
+      <c r="B253" s="9" t="s">
+        <v>626</v>
+      </c>
+      <c r="C253" s="9" t="s">
+        <v>627</v>
+      </c>
+      <c r="D253" s="9">
+        <v>2.0241093E7</v>
+      </c>
+      <c r="E253" s="9" t="s">
+        <v>628</v>
+      </c>
+      <c r="F253" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G253" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H253" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I253" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J253" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K253" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L253" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N253" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="11">
+        <v>45732.03101304398</v>
+      </c>
+      <c r="B254" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="C254" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D254" s="12">
+        <v>2.02052E7</v>
+      </c>
+      <c r="E254" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="F254" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G254" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H254" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I254" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J254" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K254" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L254" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N254" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="8">
+        <v>45732.03675983797</v>
+      </c>
+      <c r="B255" s="9" t="s">
+        <v>631</v>
+      </c>
+      <c r="C255" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D255" s="9">
+        <v>2.0223004E7</v>
+      </c>
+      <c r="E255" s="9" t="s">
+        <v>632</v>
+      </c>
+      <c r="F255" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G255" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H255" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I255" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J255" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K255" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L255" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M255" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="11">
+        <v>45732.03750877315</v>
+      </c>
+      <c r="B256" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="C256" s="12" t="s">
+        <v>634</v>
+      </c>
+      <c r="D256" s="12">
+        <v>2.0223505E7</v>
+      </c>
+      <c r="E256" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="F256" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G256" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H256" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I256" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J256" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K256" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L256" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M256" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="8">
+        <v>45732.04869028935</v>
+      </c>
+      <c r="B257" s="9" t="s">
+        <v>636</v>
+      </c>
+      <c r="C257" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D257" s="9">
+        <v>2.0246257E7</v>
+      </c>
+      <c r="E257" s="9" t="s">
+        <v>637</v>
+      </c>
+      <c r="F257" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G257" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H257" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I257" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J257" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K257" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L257" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M257" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="11">
+        <v>45732.05108181713</v>
+      </c>
+      <c r="B258" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="C258" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="D258" s="12">
+        <v>2.0225239E7</v>
+      </c>
+      <c r="E258" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="F258" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G258" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H258" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I258" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J258" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K258" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L258" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N258" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="8">
+        <v>45732.0680100926</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>640</v>
+      </c>
+      <c r="C259" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D259" s="9">
+        <v>2.0252569E7</v>
+      </c>
+      <c r="E259" s="9" t="s">
+        <v>641</v>
+      </c>
+      <c r="F259" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G259" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H259" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I259" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J259" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K259" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L259" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M259" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="11">
+        <v>45732.30669922454</v>
+      </c>
+      <c r="B260" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="C260" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D260" s="12">
+        <v>2.0222716E7</v>
+      </c>
+      <c r="E260" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="F260" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G260" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H260" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I260" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J260" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K260" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L260" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M260" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="8">
+        <v>45732.35748460648</v>
+      </c>
+      <c r="B261" s="9" t="s">
+        <v>644</v>
+      </c>
+      <c r="C261" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D261" s="9">
+        <v>2.024257E7</v>
+      </c>
+      <c r="E261" s="9" t="s">
+        <v>645</v>
+      </c>
+      <c r="F261" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G261" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H261" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I261" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J261" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K261" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L261" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N261" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="11">
+        <v>45732.39020230324</v>
+      </c>
+      <c r="B262" s="12" t="s">
+        <v>646</v>
+      </c>
+      <c r="C262" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D262" s="12">
+        <v>2.0216409E7</v>
+      </c>
+      <c r="E262" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="F262" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G262" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H262" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I262" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J262" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K262" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L262" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M262" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="8">
+        <v>45732.3968312963</v>
+      </c>
+      <c r="B263" s="9" t="s">
+        <v>648</v>
+      </c>
+      <c r="C263" s="9" t="s">
+        <v>649</v>
+      </c>
+      <c r="D263" s="9">
+        <v>2.0241006E7</v>
+      </c>
+      <c r="E263" s="9" t="s">
+        <v>650</v>
+      </c>
+      <c r="F263" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G263" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H263" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I263" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J263" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K263" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L263" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M263" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="11">
+        <v>45732.41340675926</v>
+      </c>
+      <c r="B264" s="12" t="s">
+        <v>651</v>
+      </c>
+      <c r="C264" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D264" s="12">
+        <v>2.0224116E7</v>
+      </c>
+      <c r="E264" s="12" t="s">
+        <v>652</v>
+      </c>
+      <c r="F264" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G264" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H264" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I264" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J264" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K264" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L264" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N264" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="8">
+        <v>45732.425346018514</v>
+      </c>
+      <c r="B265" s="9" t="s">
+        <v>653</v>
+      </c>
+      <c r="C265" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="D265" s="9">
+        <v>2.0246428E7</v>
+      </c>
+      <c r="E265" s="9" t="s">
+        <v>654</v>
+      </c>
+      <c r="F265" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G265" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H265" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I265" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J265" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K265" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L265" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M265" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="11">
+        <v>45732.44928523148</v>
+      </c>
+      <c r="B266" s="12" t="s">
+        <v>655</v>
+      </c>
+      <c r="C266" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D266" s="12">
+        <v>2.024102E7</v>
+      </c>
+      <c r="E266" s="12" t="s">
+        <v>656</v>
+      </c>
+      <c r="F266" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G266" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H266" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I266" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J266" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K266" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L266" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M266" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="8">
+        <v>45732.47196480324</v>
+      </c>
+      <c r="B267" s="9" t="s">
+        <v>657</v>
+      </c>
+      <c r="C267" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D267" s="9">
+        <v>2.0243209E7</v>
+      </c>
+      <c r="E267" s="9" t="s">
+        <v>658</v>
+      </c>
+      <c r="F267" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G267" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H267" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I267" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J267" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K267" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L267" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N267" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="11">
+        <v>45732.48472354167</v>
+      </c>
+      <c r="B268" s="12" t="s">
+        <v>659</v>
+      </c>
+      <c r="C268" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D268" s="12">
+        <v>2.0223302E7</v>
+      </c>
+      <c r="E268" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="F268" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G268" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H268" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I268" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J268" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K268" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L268" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N268" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="8">
+        <v>45732.491715833334</v>
+      </c>
+      <c r="B269" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="C269" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="D269" s="9">
+        <v>2.0227145E7</v>
+      </c>
+      <c r="E269" s="9" t="s">
+        <v>663</v>
+      </c>
+      <c r="F269" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G269" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H269" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I269" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J269" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K269" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L269" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N269" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="11">
+        <v>45732.50961248843</v>
+      </c>
+      <c r="B270" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="C270" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D270" s="12">
+        <v>2.0223044E7</v>
+      </c>
+      <c r="E270" s="12" t="s">
+        <v>665</v>
+      </c>
+      <c r="F270" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G270" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H270" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I270" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J270" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K270" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L270" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N270" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="8">
+        <v>45732.520032534725</v>
+      </c>
+      <c r="B271" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="C271" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="D271" s="9">
+        <v>2.0246617E7</v>
+      </c>
+      <c r="E271" s="9" t="s">
+        <v>668</v>
+      </c>
+      <c r="F271" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G271" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H271" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I271" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J271" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K271" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L271" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M271" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="11">
+        <v>45732.52334601852</v>
+      </c>
+      <c r="B272" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="C272" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D272" s="12">
+        <v>2.0242553E7</v>
+      </c>
+      <c r="E272" s="12" t="s">
+        <v>670</v>
+      </c>
+      <c r="F272" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G272" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H272" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I272" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J272" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K272" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L272" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N272" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="8">
+        <v>45732.53081614584</v>
+      </c>
+      <c r="B273" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="C273" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D273" s="9">
+        <v>2.0196285E7</v>
+      </c>
+      <c r="E273" s="9" t="s">
+        <v>672</v>
+      </c>
+      <c r="F273" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G273" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H273" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I273" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J273" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K273" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L273" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M273" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="11">
+        <v>45732.53150545139</v>
+      </c>
+      <c r="B274" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="C274" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="D274" s="12">
+        <v>2.0241109E7</v>
+      </c>
+      <c r="E274" s="12" t="s">
+        <v>674</v>
+      </c>
+      <c r="F274" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G274" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H274" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I274" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J274" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K274" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L274" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M274" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="8">
+        <v>45732.53521555556</v>
+      </c>
+      <c r="B275" s="9" t="s">
+        <v>675</v>
+      </c>
+      <c r="C275" s="9" t="s">
+        <v>676</v>
+      </c>
+      <c r="D275" s="9">
+        <v>2.0204124E7</v>
+      </c>
+      <c r="E275" s="9" t="s">
+        <v>677</v>
+      </c>
+      <c r="F275" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G275" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H275" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I275" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J275" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="K275" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L275" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M275" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="11">
+        <v>45732.5404393287</v>
+      </c>
+      <c r="B276" s="12" t="s">
+        <v>678</v>
+      </c>
+      <c r="C276" s="12" t="s">
+        <v>472</v>
+      </c>
+      <c r="D276" s="12">
+        <v>2.0245129E7</v>
+      </c>
+      <c r="E276" s="12" t="s">
+        <v>679</v>
+      </c>
+      <c r="F276" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G276" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H276" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I276" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J276" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K276" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L276" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N276" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="8">
+        <v>45732.54193365741</v>
+      </c>
+      <c r="B277" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="C277" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D277" s="9">
+        <v>2.0223331E7</v>
+      </c>
+      <c r="E277" s="9" t="s">
+        <v>681</v>
+      </c>
+      <c r="F277" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G277" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H277" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I277" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J277" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K277" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L277" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M277" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="11">
+        <v>45732.550535532406</v>
+      </c>
+      <c r="B278" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="C278" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="D278" s="12">
+        <v>2.0241085E7</v>
+      </c>
+      <c r="E278" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="F278" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G278" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H278" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I278" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J278" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K278" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L278" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N278" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="8">
+        <v>45732.556902094904</v>
+      </c>
+      <c r="B279" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="C279" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="D279" s="9">
+        <v>2.0232813E7</v>
+      </c>
+      <c r="E279" s="9" t="s">
+        <v>686</v>
+      </c>
+      <c r="F279" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G279" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H279" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I279" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J279" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K279" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L279" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M279" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="11">
+        <v>45732.57908438657</v>
+      </c>
+      <c r="B280" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="C280" s="12" t="s">
+        <v>688</v>
+      </c>
+      <c r="D280" s="12">
+        <v>2.0243317E7</v>
+      </c>
+      <c r="E280" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="F280" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G280" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H280" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I280" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J280" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K280" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L280" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M280" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="8">
+        <v>45732.59300149306</v>
+      </c>
+      <c r="B281" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D281" s="9">
+        <v>2.0222222E7</v>
+      </c>
+      <c r="E281" s="9" t="s">
+        <v>691</v>
+      </c>
+      <c r="F281" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G281" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H281" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I281" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J281" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K281" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L281" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M281" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="11">
+        <v>45732.59645700231</v>
+      </c>
+      <c r="B282" s="12" t="s">
+        <v>692</v>
+      </c>
+      <c r="C282" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D282" s="12">
+        <v>2.021302E7</v>
+      </c>
+      <c r="E282" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="F282" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G282" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H282" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I282" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J282" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K282" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L282" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N282" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="8">
+        <v>45732.61370840278</v>
+      </c>
+      <c r="B283" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="C283" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D283" s="9">
+        <v>2.0225279E7</v>
+      </c>
+      <c r="E283" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="F283" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G283" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H283" s="9">
+        <v>2027.0</v>
+      </c>
+      <c r="I283" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J283" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K283" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L283" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N283" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="11">
+        <v>45732.62242885417</v>
+      </c>
+      <c r="B284" s="12" t="s">
+        <v>696</v>
+      </c>
+      <c r="C284" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D284" s="12">
+        <v>2.0202913E7</v>
+      </c>
+      <c r="E284" s="12" t="s">
+        <v>697</v>
+      </c>
+      <c r="F284" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G284" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H284" s="12">
+        <v>2027.0</v>
+      </c>
+      <c r="I284" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J284" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K284" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L284" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N284" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="8">
+        <v>45732.63388263889</v>
+      </c>
+      <c r="B285" s="9" t="s">
+        <v>698</v>
+      </c>
+      <c r="C285" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D285" s="9">
+        <v>2.0202514E7</v>
+      </c>
+      <c r="E285" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="F285" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G285" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H285" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I285" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J285" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K285" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L285" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M285" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="11">
+        <v>45732.63854114583</v>
+      </c>
+      <c r="B286" s="12" t="s">
+        <v>700</v>
+      </c>
+      <c r="C286" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D286" s="12">
+        <v>2.0221222E7</v>
+      </c>
+      <c r="E286" s="12" t="s">
+        <v>701</v>
+      </c>
+      <c r="F286" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G286" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H286" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I286" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J286" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K286" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L286" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M286" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="8">
+        <v>45732.64696243056</v>
+      </c>
+      <c r="B287" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="C287" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="D287" s="9">
+        <v>2.0223329E7</v>
+      </c>
+      <c r="E287" s="9" t="s">
+        <v>703</v>
+      </c>
+      <c r="F287" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G287" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H287" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I287" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J287" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K287" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L287" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M287" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="11">
+        <v>45732.64696888889</v>
+      </c>
+      <c r="B288" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="C288" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D288" s="12">
+        <v>2.0222962E7</v>
+      </c>
+      <c r="E288" s="12" t="s">
+        <v>705</v>
+      </c>
+      <c r="F288" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G288" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H288" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I288" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J288" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K288" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L288" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M288" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="8">
+        <v>45732.64810239583</v>
+      </c>
+      <c r="B289" s="9" t="s">
+        <v>706</v>
+      </c>
+      <c r="C289" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="D289" s="9">
+        <v>2.0241066E7</v>
+      </c>
+      <c r="E289" s="9" t="s">
+        <v>707</v>
+      </c>
+      <c r="F289" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G289" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H289" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I289" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J289" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K289" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L289" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N289" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="11">
+        <v>45732.66139204861</v>
+      </c>
+      <c r="B290" s="12" t="s">
+        <v>708</v>
+      </c>
+      <c r="C290" s="12" t="s">
+        <v>709</v>
+      </c>
+      <c r="D290" s="12">
+        <v>2.0243942E7</v>
+      </c>
+      <c r="E290" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="F290" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G290" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H290" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I290" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J290" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K290" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L290" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N290" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="8">
+        <v>45732.68558247686</v>
+      </c>
+      <c r="B291" s="9" t="s">
+        <v>711</v>
+      </c>
+      <c r="C291" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="D291" s="9">
+        <v>2.023101E7</v>
+      </c>
+      <c r="E291" s="9" t="s">
+        <v>712</v>
+      </c>
+      <c r="F291" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G291" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H291" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I291" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J291" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K291" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L291" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M291" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="11">
+        <v>45732.68841806713</v>
+      </c>
+      <c r="B292" s="12" t="s">
+        <v>713</v>
+      </c>
+      <c r="C292" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D292" s="12">
+        <v>2.0241528E7</v>
+      </c>
+      <c r="E292" s="12" t="s">
+        <v>714</v>
+      </c>
+      <c r="F292" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G292" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H292" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I292" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J292" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K292" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L292" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M292" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="8">
+        <v>45732.693982303244</v>
+      </c>
+      <c r="B293" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="C293" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D293" s="9">
+        <v>2.0245223E7</v>
+      </c>
+      <c r="E293" s="9" t="s">
+        <v>716</v>
+      </c>
+      <c r="F293" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G293" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H293" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I293" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J293" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K293" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L293" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M293" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="11">
+        <v>45732.704900185185</v>
+      </c>
+      <c r="B294" s="12" t="s">
+        <v>717</v>
+      </c>
+      <c r="C294" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D294" s="12">
+        <v>2.022326E7</v>
+      </c>
+      <c r="E294" s="12" t="s">
+        <v>718</v>
+      </c>
+      <c r="F294" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G294" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H294" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I294" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J294" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K294" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L294" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M294" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="8">
+        <v>45732.714274618054</v>
+      </c>
+      <c r="B295" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="C295" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="D295" s="9">
+        <v>2.0241049E7</v>
+      </c>
+      <c r="E295" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="F295" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G295" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H295" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I295" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J295" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K295" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L295" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M295" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="11">
+        <v>45732.72248488426</v>
+      </c>
+      <c r="B296" s="12" t="s">
+        <v>721</v>
+      </c>
+      <c r="C296" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D296" s="12">
+        <v>2.0245209E7</v>
+      </c>
+      <c r="E296" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="F296" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G296" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H296" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I296" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J296" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K296" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L296" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M296" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="8">
+        <v>45732.73122462963</v>
+      </c>
+      <c r="B297" s="9" t="s">
+        <v>723</v>
+      </c>
+      <c r="C297" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="D297" s="9">
+        <v>2.0211021E7</v>
+      </c>
+      <c r="E297" s="9" t="s">
+        <v>724</v>
+      </c>
+      <c r="F297" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G297" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H297" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I297" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J297" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K297" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L297" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M297" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="11">
+        <v>45732.73413028935</v>
+      </c>
+      <c r="B298" s="12" t="s">
+        <v>725</v>
+      </c>
+      <c r="C298" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="D298" s="12">
+        <v>2.0226769E7</v>
+      </c>
+      <c r="E298" s="12" t="s">
+        <v>726</v>
+      </c>
+      <c r="F298" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G298" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H298" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I298" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J298" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K298" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L298" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M298" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="8">
+        <v>45732.73983976852</v>
+      </c>
+      <c r="B299" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="C299" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D299" s="9">
+        <v>2.0225272E7</v>
+      </c>
+      <c r="E299" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="F299" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G299" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H299" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I299" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J299" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K299" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L299" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N299" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="11">
+        <v>45732.746437141206</v>
+      </c>
+      <c r="B300" s="12" t="s">
+        <v>729</v>
+      </c>
+      <c r="C300" s="12" t="s">
+        <v>730</v>
+      </c>
+      <c r="D300" s="12">
+        <v>2.0243364E7</v>
+      </c>
+      <c r="E300" s="12" t="s">
+        <v>731</v>
+      </c>
+      <c r="F300" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G300" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H300" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I300" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J300" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K300" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L300" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N300" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="8">
+        <v>45732.7627097338</v>
+      </c>
+      <c r="B301" s="9" t="s">
+        <v>732</v>
+      </c>
+      <c r="C301" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D301" s="9">
+        <v>2.0224134E7</v>
+      </c>
+      <c r="E301" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="F301" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G301" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H301" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I301" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J301" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K301" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L301" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N301" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="11">
+        <v>45732.76743738426</v>
+      </c>
+      <c r="B302" s="12" t="s">
+        <v>734</v>
+      </c>
+      <c r="C302" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D302" s="12">
+        <v>2.0243035E7</v>
+      </c>
+      <c r="E302" s="12" t="s">
+        <v>735</v>
+      </c>
+      <c r="F302" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G302" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H302" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I302" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J302" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K302" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L302" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N302" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="8">
+        <v>45732.77010980324</v>
+      </c>
+      <c r="B303" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="C303" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D303" s="9">
+        <v>2.0242953E7</v>
+      </c>
+      <c r="E303" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="F303" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G303" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H303" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I303" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J303" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K303" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L303" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N303" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="11">
+        <v>45732.7715853125</v>
+      </c>
+      <c r="B304" s="12" t="s">
+        <v>738</v>
+      </c>
+      <c r="C304" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D304" s="12">
+        <v>2.0246627E7</v>
+      </c>
+      <c r="E304" s="12" t="s">
+        <v>739</v>
+      </c>
+      <c r="F304" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G304" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H304" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I304" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J304" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K304" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L304" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M304" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="8">
+        <v>45732.77778399306</v>
+      </c>
+      <c r="B305" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="C305" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D305" s="9">
+        <v>2.0245219E7</v>
+      </c>
+      <c r="E305" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="F305" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G305" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H305" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I305" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J305" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K305" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L305" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N305" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="11">
+        <v>45732.80292758102</v>
+      </c>
+      <c r="B306" s="12" t="s">
+        <v>742</v>
+      </c>
+      <c r="C306" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="D306" s="12">
+        <v>2.0202591E7</v>
+      </c>
+      <c r="E306" s="12" t="s">
+        <v>743</v>
+      </c>
+      <c r="F306" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G306" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H306" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I306" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J306" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K306" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L306" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N306" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="8">
+        <v>45732.81257385417</v>
+      </c>
+      <c r="B307" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="C307" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D307" s="9">
+        <v>2.0221532E7</v>
+      </c>
+      <c r="E307" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="F307" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G307" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H307" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I307" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J307" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K307" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L307" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N307" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="11">
+        <v>45732.82198258102</v>
+      </c>
+      <c r="B308" s="12" t="s">
+        <v>746</v>
+      </c>
+      <c r="C308" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D308" s="12">
+        <v>2.0246285E7</v>
+      </c>
+      <c r="E308" s="12" t="s">
+        <v>747</v>
+      </c>
+      <c r="F308" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G308" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H308" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I308" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J308" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K308" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L308" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M308" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="8">
+        <v>45732.82296922454</v>
+      </c>
+      <c r="B309" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="C309" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D309" s="9">
+        <v>2.0183016E7</v>
+      </c>
+      <c r="E309" s="9" t="s">
+        <v>749</v>
+      </c>
+      <c r="F309" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G309" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H309" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I309" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J309" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K309" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L309" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N309" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="11">
+        <v>45732.82482422453</v>
+      </c>
+      <c r="B310" s="12" t="s">
+        <v>750</v>
+      </c>
+      <c r="C310" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D310" s="12">
+        <v>2.020343E7</v>
+      </c>
+      <c r="E310" s="12" t="s">
+        <v>751</v>
+      </c>
+      <c r="F310" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G310" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H310" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I310" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J310" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K310" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L310" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M310" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="8">
+        <v>45732.82676783565</v>
+      </c>
+      <c r="B311" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="C311" s="9" t="s">
+        <v>443</v>
+      </c>
+      <c r="D311" s="9">
+        <v>2.0241011E7</v>
+      </c>
+      <c r="E311" s="9" t="s">
+        <v>753</v>
+      </c>
+      <c r="F311" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G311" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H311" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I311" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J311" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K311" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L311" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N311" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="11">
+        <v>45732.8284972338</v>
+      </c>
+      <c r="B312" s="12" t="s">
+        <v>754</v>
+      </c>
+      <c r="C312" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D312" s="12">
+        <v>2.0243022E7</v>
+      </c>
+      <c r="E312" s="12" t="s">
+        <v>755</v>
+      </c>
+      <c r="F312" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G312" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H312" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I312" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J312" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K312" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L312" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M312" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="8">
+        <v>45732.82862299768</v>
+      </c>
+      <c r="B313" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="C313" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D313" s="9">
+        <v>2.0213905E7</v>
+      </c>
+      <c r="E313" s="9" t="s">
+        <v>757</v>
+      </c>
+      <c r="F313" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G313" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H313" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I313" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J313" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K313" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L313" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M313" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="11">
+        <v>45732.830386574075</v>
+      </c>
+      <c r="B314" s="12" t="s">
+        <v>758</v>
+      </c>
+      <c r="C314" s="12" t="s">
+        <v>759</v>
+      </c>
+      <c r="D314" s="12">
+        <v>2.0216626E7</v>
+      </c>
+      <c r="E314" s="12" t="s">
+        <v>760</v>
+      </c>
+      <c r="F314" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G314" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H314" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I314" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J314" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K314" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L314" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N314" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="8">
+        <v>45732.833324872685</v>
+      </c>
+      <c r="B315" s="9" t="s">
+        <v>761</v>
+      </c>
+      <c r="C315" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D315" s="9">
+        <v>2.0243729E7</v>
+      </c>
+      <c r="E315" s="9" t="s">
+        <v>762</v>
+      </c>
+      <c r="F315" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G315" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H315" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I315" s="9">
+        <v>2021.0</v>
+      </c>
+      <c r="J315" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K315" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L315" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N315" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="11">
+        <v>45732.834193414354</v>
+      </c>
+      <c r="B316" s="12" t="s">
+        <v>763</v>
+      </c>
+      <c r="C316" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D316" s="12">
+        <v>2.0241629E7</v>
+      </c>
+      <c r="E316" s="12" t="s">
+        <v>764</v>
+      </c>
+      <c r="F316" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G316" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H316" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I316" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J316" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K316" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L316" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N316" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="8">
+        <v>45732.84158570602</v>
+      </c>
+      <c r="B317" s="9" t="s">
+        <v>765</v>
+      </c>
+      <c r="C317" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="D317" s="9">
+        <v>2.0243348E7</v>
+      </c>
+      <c r="E317" s="9" t="s">
+        <v>766</v>
+      </c>
+      <c r="F317" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G317" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="H317" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I317" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J317" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K317" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L317" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M317" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="11">
+        <v>45732.84227857639</v>
+      </c>
+      <c r="B318" s="12" t="s">
+        <v>767</v>
+      </c>
+      <c r="C318" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D318" s="12">
+        <v>2.0242523E7</v>
+      </c>
+      <c r="E318" s="12" t="s">
+        <v>768</v>
+      </c>
+      <c r="F318" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G318" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H318" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I318" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J318" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K318" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L318" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M318" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="8">
+        <v>45732.854039513884</v>
+      </c>
+      <c r="B319" s="9" t="s">
+        <v>769</v>
+      </c>
+      <c r="C319" s="9" t="s">
+        <v>770</v>
+      </c>
+      <c r="D319" s="9">
+        <v>2.0241716E7</v>
+      </c>
+      <c r="E319" s="9" t="s">
+        <v>771</v>
+      </c>
+      <c r="F319" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G319" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H319" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I319" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J319" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K319" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L319" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M319" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="11">
+        <v>45732.854471875005</v>
+      </c>
+      <c r="B320" s="12" t="s">
+        <v>772</v>
+      </c>
+      <c r="C320" s="12" t="s">
+        <v>327</v>
+      </c>
+      <c r="D320" s="12">
+        <v>2.0245182E7</v>
+      </c>
+      <c r="E320" s="12" t="s">
+        <v>773</v>
+      </c>
+      <c r="F320" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G320" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H320" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I320" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J320" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K320" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L320" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M320" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="8">
+        <v>45732.866046111114</v>
+      </c>
+      <c r="B321" s="9" t="s">
+        <v>774</v>
+      </c>
+      <c r="C321" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D321" s="9">
+        <v>2.0217124E7</v>
+      </c>
+      <c r="E321" s="9" t="s">
+        <v>775</v>
+      </c>
+      <c r="F321" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G321" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H321" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I321" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J321" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K321" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L321" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M321" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="11">
+        <v>45732.86686414352</v>
+      </c>
+      <c r="B322" s="12" t="s">
+        <v>776</v>
+      </c>
+      <c r="C322" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D322" s="12">
+        <v>2.0253725E7</v>
+      </c>
+      <c r="E322" s="12" t="s">
+        <v>777</v>
+      </c>
+      <c r="F322" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G322" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H322" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I322" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J322" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K322" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L322" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M322" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="8">
+        <v>45732.87257898148</v>
+      </c>
+      <c r="B323" s="9" t="s">
+        <v>778</v>
+      </c>
+      <c r="C323" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D323" s="9">
+        <v>2.021304E7</v>
+      </c>
+      <c r="E323" s="9" t="s">
+        <v>779</v>
+      </c>
+      <c r="F323" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G323" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H323" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I323" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J323" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K323" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L323" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N323" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="11">
+        <v>45732.872781990736</v>
+      </c>
+      <c r="B324" s="12" t="s">
+        <v>780</v>
+      </c>
+      <c r="C324" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D324" s="12">
+        <v>2.024625E7</v>
+      </c>
+      <c r="E324" s="12" t="s">
+        <v>781</v>
+      </c>
+      <c r="F324" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G324" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H324" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I324" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J324" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K324" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L324" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M324" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="8">
+        <v>45732.877952106486</v>
+      </c>
+      <c r="B325" s="9" t="s">
+        <v>782</v>
+      </c>
+      <c r="C325" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D325" s="9">
+        <v>2.020412E7</v>
+      </c>
+      <c r="E325" s="9" t="s">
+        <v>783</v>
+      </c>
+      <c r="F325" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G325" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H325" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I325" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J325" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K325" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L325" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N325" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="11">
+        <v>45732.88307888889</v>
+      </c>
+      <c r="B326" s="12" t="s">
+        <v>784</v>
+      </c>
+      <c r="C326" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D326" s="12">
+        <v>2.0227057E7</v>
+      </c>
+      <c r="E326" s="12" t="s">
+        <v>785</v>
+      </c>
+      <c r="F326" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G326" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H326" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I326" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J326" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K326" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L326" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N326" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="8">
+        <v>45732.88952271991</v>
+      </c>
+      <c r="B327" s="9" t="s">
+        <v>786</v>
+      </c>
+      <c r="C327" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D327" s="9">
+        <v>2.0242218E7</v>
+      </c>
+      <c r="E327" s="9" t="s">
+        <v>787</v>
+      </c>
+      <c r="F327" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G327" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H327" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I327" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J327" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K327" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L327" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N327" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="11">
+        <v>45732.89277315972</v>
+      </c>
+      <c r="B328" s="12" t="s">
+        <v>788</v>
+      </c>
+      <c r="C328" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D328" s="12">
+        <v>2.0241514E7</v>
+      </c>
+      <c r="E328" s="12" t="s">
+        <v>789</v>
+      </c>
+      <c r="F328" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G328" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H328" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I328" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J328" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K328" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L328" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N328" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="8">
+        <v>45732.89559939815</v>
+      </c>
+      <c r="B329" s="9" t="s">
+        <v>790</v>
+      </c>
+      <c r="C329" s="9" t="s">
+        <v>791</v>
+      </c>
+      <c r="D329" s="9">
+        <v>2.0255271E7</v>
+      </c>
+      <c r="E329" s="9" t="s">
+        <v>792</v>
+      </c>
+      <c r="F329" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G329" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H329" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I329" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J329" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K329" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L329" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N329" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="11">
+        <v>45732.90550521991</v>
+      </c>
+      <c r="B330" s="12" t="s">
+        <v>793</v>
+      </c>
+      <c r="C330" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D330" s="12">
+        <v>2.0226614E7</v>
+      </c>
+      <c r="E330" s="12" t="s">
+        <v>794</v>
+      </c>
+      <c r="F330" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G330" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H330" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I330" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J330" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K330" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L330" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M330" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="8">
+        <v>45732.912442789355</v>
+      </c>
+      <c r="B331" s="9" t="s">
+        <v>795</v>
+      </c>
+      <c r="C331" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D331" s="9">
+        <v>2.024511E7</v>
+      </c>
+      <c r="E331" s="9" t="s">
+        <v>796</v>
+      </c>
+      <c r="F331" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G331" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H331" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I331" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J331" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K331" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L331" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M331" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="11">
+        <v>45732.91299462963</v>
+      </c>
+      <c r="B332" s="12" t="s">
+        <v>797</v>
+      </c>
+      <c r="C332" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D332" s="12">
+        <v>2.0195122E7</v>
+      </c>
+      <c r="E332" s="12" t="s">
+        <v>798</v>
+      </c>
+      <c r="F332" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G332" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H332" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I332" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J332" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K332" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L332" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M332" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="8">
+        <v>45732.917958125</v>
+      </c>
+      <c r="B333" s="9" t="s">
+        <v>799</v>
+      </c>
+      <c r="C333" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D333" s="9">
+        <v>2.0221507E7</v>
+      </c>
+      <c r="E333" s="9" t="s">
+        <v>800</v>
+      </c>
+      <c r="F333" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G333" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H333" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I333" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J333" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K333" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L333" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N333" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="11">
+        <v>45732.91837342593</v>
+      </c>
+      <c r="B334" s="12" t="s">
+        <v>801</v>
+      </c>
+      <c r="C334" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="D334" s="12">
+        <v>2.0231068E7</v>
+      </c>
+      <c r="E334" s="12" t="s">
+        <v>802</v>
+      </c>
+      <c r="F334" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G334" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H334" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I334" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J334" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K334" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L334" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N334" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="8">
+        <v>45732.92746327547</v>
+      </c>
+      <c r="B335" s="9" t="s">
+        <v>803</v>
+      </c>
+      <c r="C335" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D335" s="9">
+        <v>2.0214151E7</v>
+      </c>
+      <c r="E335" s="9" t="s">
+        <v>804</v>
+      </c>
+      <c r="F335" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G335" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H335" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I335" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J335" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="K335" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L335" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N335" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="11">
+        <v>45732.929475173616</v>
+      </c>
+      <c r="B336" s="12" t="s">
+        <v>805</v>
+      </c>
+      <c r="C336" s="12" t="s">
+        <v>806</v>
+      </c>
+      <c r="D336" s="12">
+        <v>2.0241063E7</v>
+      </c>
+      <c r="E336" s="12" t="s">
+        <v>807</v>
+      </c>
+      <c r="F336" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G336" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H336" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I336" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J336" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K336" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L336" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N336" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="8">
+        <v>45732.93063256945</v>
+      </c>
+      <c r="B337" s="9" t="s">
+        <v>808</v>
+      </c>
+      <c r="C337" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D337" s="9">
+        <v>2.0242713E7</v>
+      </c>
+      <c r="E337" s="9" t="s">
+        <v>809</v>
+      </c>
+      <c r="F337" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G337" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H337" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I337" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J337" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K337" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L337" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M337" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="11">
+        <v>45732.94579616898</v>
+      </c>
+      <c r="B338" s="12" t="s">
+        <v>810</v>
+      </c>
+      <c r="C338" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D338" s="12">
+        <v>2.0243842E7</v>
+      </c>
+      <c r="E338" s="12" t="s">
+        <v>811</v>
+      </c>
+      <c r="F338" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G338" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H338" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I338" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J338" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K338" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L338" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M338" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="8">
+        <v>45732.960267800925</v>
+      </c>
+      <c r="B339" s="9" t="s">
+        <v>812</v>
+      </c>
+      <c r="C339" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D339" s="9">
+        <v>2.0192201E7</v>
+      </c>
+      <c r="E339" s="9" t="s">
+        <v>813</v>
+      </c>
+      <c r="F339" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G339" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H339" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I339" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J339" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K339" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L339" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N339" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="11">
+        <v>45732.96592515046</v>
+      </c>
+      <c r="B340" s="12" t="s">
+        <v>814</v>
+      </c>
+      <c r="C340" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="D340" s="12">
+        <v>2.0241028E7</v>
+      </c>
+      <c r="E340" s="12" t="s">
+        <v>815</v>
+      </c>
+      <c r="F340" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G340" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H340" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I340" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J340" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K340" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L340" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M340" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="8">
+        <v>45732.97300366898</v>
+      </c>
+      <c r="B341" s="9" t="s">
+        <v>816</v>
+      </c>
+      <c r="C341" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D341" s="9">
+        <v>2.0221038E7</v>
+      </c>
+      <c r="E341" s="9" t="s">
+        <v>817</v>
+      </c>
+      <c r="F341" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G341" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H341" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I341" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J341" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K341" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L341" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M341" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="11">
+        <v>45732.987161157405</v>
+      </c>
+      <c r="B342" s="12" t="s">
+        <v>818</v>
+      </c>
+      <c r="C342" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="D342" s="12">
+        <v>2.0246912E7</v>
+      </c>
+      <c r="E342" s="12" t="s">
+        <v>819</v>
+      </c>
+      <c r="F342" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G342" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H342" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I342" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J342" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K342" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L342" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M342" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="8">
+        <v>45732.99445329861</v>
+      </c>
+      <c r="B343" s="9" t="s">
+        <v>820</v>
+      </c>
+      <c r="C343" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D343" s="9">
+        <v>2.0221506E7</v>
+      </c>
+      <c r="E343" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="F343" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G343" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H343" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I343" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J343" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K343" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L343" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M343" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="11">
+        <v>45733.01058829861</v>
+      </c>
+      <c r="B344" s="12" t="s">
+        <v>821</v>
+      </c>
+      <c r="C344" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D344" s="12">
+        <v>2.0252433E7</v>
+      </c>
+      <c r="E344" s="12" t="s">
+        <v>822</v>
+      </c>
+      <c r="F344" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G344" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H344" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I344" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J344" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K344" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L344" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M344" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="8">
+        <v>45733.11982773148</v>
+      </c>
+      <c r="B345" s="9" t="s">
+        <v>823</v>
+      </c>
+      <c r="C345" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D345" s="9">
+        <v>2.0232949E7</v>
+      </c>
+      <c r="E345" s="9" t="s">
+        <v>824</v>
+      </c>
+      <c r="F345" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G345" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H345" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I345" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J345" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K345" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L345" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M345" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="11">
+        <v>45733.41204210648</v>
+      </c>
+      <c r="B346" s="12" t="s">
+        <v>825</v>
+      </c>
+      <c r="C346" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D346" s="12">
+        <v>2.0182101E7</v>
+      </c>
+      <c r="E346" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="F346" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G346" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H346" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I346" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J346" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K346" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L346" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N346" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="8">
+        <v>45733.462341192135</v>
+      </c>
+      <c r="B347" s="9" t="s">
+        <v>827</v>
+      </c>
+      <c r="C347" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D347" s="9">
+        <v>2.0213507E7</v>
+      </c>
+      <c r="E347" s="9" t="s">
+        <v>828</v>
+      </c>
+      <c r="F347" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G347" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H347" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I347" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J347" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K347" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L347" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N347" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="11">
+        <v>45733.47131498843</v>
+      </c>
+      <c r="B348" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="C348" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="D348" s="12">
+        <v>2.024674E7</v>
+      </c>
+      <c r="E348" s="12" t="s">
+        <v>830</v>
+      </c>
+      <c r="F348" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G348" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H348" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I348" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J348" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K348" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L348" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M348" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="8">
+        <v>45733.506501192125</v>
+      </c>
+      <c r="B349" s="9" t="s">
+        <v>831</v>
+      </c>
+      <c r="C349" s="9" t="s">
+        <v>617</v>
+      </c>
+      <c r="D349" s="9">
+        <v>2.0246417E7</v>
+      </c>
+      <c r="E349" s="9" t="s">
+        <v>832</v>
+      </c>
+      <c r="F349" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G349" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H349" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I349" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J349" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K349" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L349" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M349" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="11">
+        <v>45733.51715186343</v>
+      </c>
+      <c r="B350" s="12" t="s">
+        <v>833</v>
+      </c>
+      <c r="C350" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D350" s="12">
+        <v>2.0242236E7</v>
+      </c>
+      <c r="E350" s="12" t="s">
+        <v>834</v>
+      </c>
+      <c r="F350" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G350" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H350" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I350" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J350" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K350" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L350" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M350" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="8">
+        <v>45733.51871487268</v>
+      </c>
+      <c r="B351" s="9" t="s">
+        <v>835</v>
+      </c>
+      <c r="C351" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D351" s="9">
+        <v>2.0246261E7</v>
+      </c>
+      <c r="E351" s="9" t="s">
+        <v>836</v>
+      </c>
+      <c r="F351" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G351" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H351" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I351" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J351" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K351" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L351" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N351" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="11">
+        <v>45733.56176861111</v>
+      </c>
+      <c r="B352" s="12" t="s">
+        <v>837</v>
+      </c>
+      <c r="C352" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="D352" s="12">
+        <v>2.023173E7</v>
+      </c>
+      <c r="E352" s="12" t="s">
+        <v>731</v>
+      </c>
+      <c r="F352" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G352" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H352" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I352" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J352" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K352" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L352" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N352" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="8">
+        <v>45733.6589194213</v>
+      </c>
+      <c r="B353" s="9" t="s">
+        <v>838</v>
+      </c>
+      <c r="C353" s="9" t="s">
+        <v>839</v>
+      </c>
+      <c r="D353" s="9">
+        <v>2.0246644E7</v>
+      </c>
+      <c r="E353" s="9" t="s">
+        <v>840</v>
+      </c>
+      <c r="F353" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G353" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H353" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I353" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J353" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K353" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L353" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N353" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="11">
+        <v>45733.66478225694</v>
+      </c>
+      <c r="B354" s="12" t="s">
+        <v>841</v>
+      </c>
+      <c r="C354" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="D354" s="12">
+        <v>2.0193224E7</v>
+      </c>
+      <c r="E354" s="12" t="s">
+        <v>842</v>
+      </c>
+      <c r="F354" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G354" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H354" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I354" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J354" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K354" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L354" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N354" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="8">
+        <v>45733.667152326394</v>
+      </c>
+      <c r="B355" s="9" t="s">
+        <v>843</v>
+      </c>
+      <c r="C355" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D355" s="9">
+        <v>2.0223821E7</v>
+      </c>
+      <c r="E355" s="9" t="s">
+        <v>844</v>
+      </c>
+      <c r="F355" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G355" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H355" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I355" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J355" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K355" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L355" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M355" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="11">
+        <v>45733.6928921412</v>
+      </c>
+      <c r="B356" s="12" t="s">
+        <v>845</v>
+      </c>
+      <c r="C356" s="12" t="s">
+        <v>662</v>
+      </c>
+      <c r="D356" s="12">
+        <v>2.0212918E7</v>
+      </c>
+      <c r="E356" s="12" t="s">
+        <v>846</v>
+      </c>
+      <c r="F356" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G356" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H356" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I356" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J356" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K356" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L356" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N356" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="8">
+        <v>45733.771795671295</v>
+      </c>
+      <c r="B357" s="9" t="s">
+        <v>847</v>
+      </c>
+      <c r="C357" s="9" t="s">
+        <v>848</v>
+      </c>
+      <c r="D357" s="9">
+        <v>2.0243255E7</v>
+      </c>
+      <c r="E357" s="9" t="s">
+        <v>849</v>
+      </c>
+      <c r="F357" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G357" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H357" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I357" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J357" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K357" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L357" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M357" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="11">
+        <v>45733.817323020834</v>
+      </c>
+      <c r="B358" s="12" t="s">
+        <v>850</v>
+      </c>
+      <c r="C358" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D358" s="12">
+        <v>2.0226628E7</v>
+      </c>
+      <c r="E358" s="12" t="s">
+        <v>851</v>
+      </c>
+      <c r="F358" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G358" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H358" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I358" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J358" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K358" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L358" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M358" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="8">
+        <v>45733.8617718287</v>
+      </c>
+      <c r="B359" s="9" t="s">
+        <v>852</v>
+      </c>
+      <c r="C359" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="D359" s="9">
+        <v>2.0215177E7</v>
+      </c>
+      <c r="E359" s="9" t="s">
+        <v>853</v>
+      </c>
+      <c r="F359" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G359" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H359" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I359" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J359" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K359" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L359" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M359" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="11">
+        <v>45733.86361512731</v>
+      </c>
+      <c r="B360" s="12" t="s">
+        <v>854</v>
+      </c>
+      <c r="C360" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D360" s="12">
+        <v>2.0192231E7</v>
+      </c>
+      <c r="E360" s="12" t="s">
+        <v>855</v>
+      </c>
+      <c r="F360" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G360" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H360" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I360" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J360" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K360" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L360" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M360" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="8">
+        <v>45733.87217869213</v>
+      </c>
+      <c r="B361" s="9" t="s">
+        <v>856</v>
+      </c>
+      <c r="C361" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D361" s="9">
+        <v>2.0243521E7</v>
+      </c>
+      <c r="E361" s="9" t="s">
+        <v>857</v>
+      </c>
+      <c r="F361" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G361" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H361" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I361" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J361" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K361" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L361" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N361" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="14">
+        <v>45733.90943809028</v>
+      </c>
+      <c r="B362" s="15" t="s">
+        <v>858</v>
+      </c>
+      <c r="C362" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="D362" s="15">
+        <v>2.0221706E7</v>
+      </c>
+      <c r="E362" s="15" t="s">
+        <v>859</v>
+      </c>
+      <c r="F362" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G362" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H362" s="15">
+        <v>2017.0</v>
+      </c>
+      <c r="I362" s="15">
+        <v>2020.0</v>
+      </c>
+      <c r="J362" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K362" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="L362" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="M362" s="15" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250310.xlsx
+++ b/R/data/quiz_250310.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3263" uniqueCount="860">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3389" uniqueCount="891">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -2591,6 +2591,99 @@
   </si>
   <si>
     <t>김예원</t>
+  </si>
+  <si>
+    <t>ekzkdi12@naver.com</t>
+  </si>
+  <si>
+    <t>박정민</t>
+  </si>
+  <si>
+    <t>ysw201200@gmail.com</t>
+  </si>
+  <si>
+    <t>이윤서</t>
+  </si>
+  <si>
+    <t>fireanger0@gmail.com</t>
+  </si>
+  <si>
+    <t>AI로봇융합</t>
+  </si>
+  <si>
+    <t>양조은</t>
+  </si>
+  <si>
+    <t>tjwldus5810@naver.com</t>
+  </si>
+  <si>
+    <t>서지연</t>
+  </si>
+  <si>
+    <t>seoyeonjang0418@naver.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">영어영문학과 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">장서연 </t>
+  </si>
+  <si>
+    <t>nody0402@naver.com</t>
+  </si>
+  <si>
+    <t>소프트웨어 융합대학 빅데이터전공</t>
+  </si>
+  <si>
+    <t>박준우</t>
+  </si>
+  <si>
+    <t>derechos2405@gmail.com</t>
+  </si>
+  <si>
+    <t>김성훈</t>
+  </si>
+  <si>
+    <t>ahj050411@naver.com</t>
+  </si>
+  <si>
+    <t>안현주</t>
+  </si>
+  <si>
+    <t>jinhoney05@naver.com</t>
+  </si>
+  <si>
+    <t>이진헌</t>
+  </si>
+  <si>
+    <t>hby9364@naver.com</t>
+  </si>
+  <si>
+    <t>황보연</t>
+  </si>
+  <si>
+    <t>dbsrhkdid5@naver.com</t>
+  </si>
+  <si>
+    <t>박태양</t>
+  </si>
+  <si>
+    <t>kuen0508217@naver.com</t>
+  </si>
+  <si>
+    <t>권가영</t>
+  </si>
+  <si>
+    <t>qmpzalwn2001@gmail.com</t>
+  </si>
+  <si>
+    <t>오유택</t>
+  </si>
+  <si>
+    <t>wlgprnjs98@gmail.com</t>
+  </si>
+  <si>
+    <t>권지혜</t>
   </si>
 </sst>
 </file>
@@ -2888,7 +2981,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N362" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N376" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -17930,44 +18023,618 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="14">
+      <c r="A362" s="11">
         <v>45733.90943809028</v>
       </c>
-      <c r="B362" s="15" t="s">
+      <c r="B362" s="12" t="s">
         <v>858</v>
       </c>
-      <c r="C362" s="15" t="s">
+      <c r="C362" s="12" t="s">
         <v>557</v>
       </c>
-      <c r="D362" s="15">
+      <c r="D362" s="12">
         <v>2.0221706E7</v>
       </c>
-      <c r="E362" s="15" t="s">
+      <c r="E362" s="12" t="s">
         <v>859</v>
       </c>
-      <c r="F362" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="G362" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H362" s="15">
-        <v>2017.0</v>
-      </c>
-      <c r="I362" s="15">
-        <v>2020.0</v>
-      </c>
-      <c r="J362" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="K362" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="L362" s="15" t="s">
+      <c r="F362" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G362" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H362" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I362" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J362" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K362" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L362" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="M362" s="15" t="s">
-        <v>32</v>
+      <c r="M362" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="8">
+        <v>45733.916603715275</v>
+      </c>
+      <c r="B363" s="9" t="s">
+        <v>860</v>
+      </c>
+      <c r="C363" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D363" s="9">
+        <v>2.024296E7</v>
+      </c>
+      <c r="E363" s="9" t="s">
+        <v>861</v>
+      </c>
+      <c r="F363" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G363" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H363" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I363" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J363" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K363" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L363" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M363" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="11">
+        <v>45733.972905787035</v>
+      </c>
+      <c r="B364" s="12" t="s">
+        <v>862</v>
+      </c>
+      <c r="C364" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D364" s="12">
+        <v>2.0212556E7</v>
+      </c>
+      <c r="E364" s="12" t="s">
+        <v>863</v>
+      </c>
+      <c r="F364" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G364" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H364" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I364" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J364" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K364" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L364" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N364" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="8">
+        <v>45734.02042903935</v>
+      </c>
+      <c r="B365" s="9" t="s">
+        <v>864</v>
+      </c>
+      <c r="C365" s="9" t="s">
+        <v>865</v>
+      </c>
+      <c r="D365" s="9">
+        <v>2.0246475E7</v>
+      </c>
+      <c r="E365" s="9" t="s">
+        <v>866</v>
+      </c>
+      <c r="F365" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G365" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H365" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I365" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J365" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K365" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L365" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N365" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="11">
+        <v>45734.04713707176</v>
+      </c>
+      <c r="B366" s="12" t="s">
+        <v>867</v>
+      </c>
+      <c r="C366" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D366" s="12">
+        <v>2.0242328E7</v>
+      </c>
+      <c r="E366" s="12" t="s">
+        <v>868</v>
+      </c>
+      <c r="F366" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G366" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H366" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I366" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J366" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K366" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L366" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N366" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="8">
+        <v>45734.064854861106</v>
+      </c>
+      <c r="B367" s="9" t="s">
+        <v>869</v>
+      </c>
+      <c r="C367" s="9" t="s">
+        <v>870</v>
+      </c>
+      <c r="D367" s="9">
+        <v>2.0241232E7</v>
+      </c>
+      <c r="E367" s="9" t="s">
+        <v>871</v>
+      </c>
+      <c r="F367" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G367" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H367" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I367" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J367" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K367" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L367" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M367" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="11">
+        <v>45734.57387653935</v>
+      </c>
+      <c r="B368" s="12" t="s">
+        <v>872</v>
+      </c>
+      <c r="C368" s="12" t="s">
+        <v>873</v>
+      </c>
+      <c r="D368" s="12">
+        <v>2.0225163E7</v>
+      </c>
+      <c r="E368" s="12" t="s">
+        <v>874</v>
+      </c>
+      <c r="F368" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G368" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H368" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I368" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J368" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K368" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L368" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N368" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="8">
+        <v>45734.62540725694</v>
+      </c>
+      <c r="B369" s="9" t="s">
+        <v>875</v>
+      </c>
+      <c r="C369" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D369" s="9">
+        <v>2.024622E7</v>
+      </c>
+      <c r="E369" s="9" t="s">
+        <v>876</v>
+      </c>
+      <c r="F369" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G369" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H369" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I369" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J369" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K369" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L369" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M369" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="11">
+        <v>45734.65708010417</v>
+      </c>
+      <c r="B370" s="12" t="s">
+        <v>877</v>
+      </c>
+      <c r="C370" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D370" s="12">
+        <v>2.0243719E7</v>
+      </c>
+      <c r="E370" s="12" t="s">
+        <v>878</v>
+      </c>
+      <c r="F370" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G370" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H370" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I370" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J370" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K370" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L370" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N370" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="8">
+        <v>45734.771842222224</v>
+      </c>
+      <c r="B371" s="9" t="s">
+        <v>879</v>
+      </c>
+      <c r="C371" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D371" s="9">
+        <v>2.0253241E7</v>
+      </c>
+      <c r="E371" s="9" t="s">
+        <v>880</v>
+      </c>
+      <c r="F371" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G371" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H371" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I371" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J371" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K371" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L371" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M371" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="11">
+        <v>45734.79591715278</v>
+      </c>
+      <c r="B372" s="12" t="s">
+        <v>881</v>
+      </c>
+      <c r="C372" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D372" s="12">
+        <v>2.0254146E7</v>
+      </c>
+      <c r="E372" s="12" t="s">
+        <v>882</v>
+      </c>
+      <c r="F372" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G372" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H372" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I372" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J372" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K372" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L372" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M372" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="8">
+        <v>45734.805028946765</v>
+      </c>
+      <c r="B373" s="9" t="s">
+        <v>883</v>
+      </c>
+      <c r="C373" s="9" t="s">
+        <v>320</v>
+      </c>
+      <c r="D373" s="9">
+        <v>2.0195174E7</v>
+      </c>
+      <c r="E373" s="9" t="s">
+        <v>884</v>
+      </c>
+      <c r="F373" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G373" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H373" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I373" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J373" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K373" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L373" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M373" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="11">
+        <v>45734.81971871528</v>
+      </c>
+      <c r="B374" s="12" t="s">
+        <v>885</v>
+      </c>
+      <c r="C374" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D374" s="12">
+        <v>2.0242909E7</v>
+      </c>
+      <c r="E374" s="12" t="s">
+        <v>886</v>
+      </c>
+      <c r="F374" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G374" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H374" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I374" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J374" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K374" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L374" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N374" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="8">
+        <v>45734.84318722222</v>
+      </c>
+      <c r="B375" s="9" t="s">
+        <v>887</v>
+      </c>
+      <c r="C375" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D375" s="9">
+        <v>2.0246413E7</v>
+      </c>
+      <c r="E375" s="9" t="s">
+        <v>888</v>
+      </c>
+      <c r="F375" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G375" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H375" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I375" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J375" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K375" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L375" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M375" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="14">
+        <v>45734.90119138889</v>
+      </c>
+      <c r="B376" s="15" t="s">
+        <v>889</v>
+      </c>
+      <c r="C376" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D376" s="15">
+        <v>2.0246211E7</v>
+      </c>
+      <c r="E376" s="15" t="s">
+        <v>890</v>
+      </c>
+      <c r="F376" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G376" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="H376" s="15">
+        <v>2012.0</v>
+      </c>
+      <c r="I376" s="15">
+        <v>2018.0</v>
+      </c>
+      <c r="J376" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="K376" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="L376" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="M376" s="15" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/R/data/quiz_250310.xlsx
+++ b/R/data/quiz_250310.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3389" uniqueCount="891">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5090" uniqueCount="1279">
   <si>
     <t>타임스탬프</t>
   </si>
@@ -2684,6 +2684,1170 @@
   </si>
   <si>
     <t>권지혜</t>
+  </si>
+  <si>
+    <t>dnjstkd458@naver.com</t>
+  </si>
+  <si>
+    <t>이원상</t>
+  </si>
+  <si>
+    <t>autumngo77@gmail.com</t>
+  </si>
+  <si>
+    <t>고나영</t>
+  </si>
+  <si>
+    <t>cksal0415@gmail.com</t>
+  </si>
+  <si>
+    <t>홍찬미</t>
+  </si>
+  <si>
+    <t>01bell@naver.com</t>
+  </si>
+  <si>
+    <t>바이오메디컬</t>
+  </si>
+  <si>
+    <t>김민채</t>
+  </si>
+  <si>
+    <t>seojingwon8@gmail.com</t>
+  </si>
+  <si>
+    <t>권서진</t>
+  </si>
+  <si>
+    <t>kimtaehee34@naver.com</t>
+  </si>
+  <si>
+    <t>김태희</t>
+  </si>
+  <si>
+    <t>yourim1207@naver.com</t>
+  </si>
+  <si>
+    <t>오유림</t>
+  </si>
+  <si>
+    <t>20242640@hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>황가현</t>
+  </si>
+  <si>
+    <t>kimin18_@naver.com</t>
+  </si>
+  <si>
+    <t>김민정</t>
+  </si>
+  <si>
+    <t>juni060919@naver.com</t>
+  </si>
+  <si>
+    <t>언어청각학부</t>
+  </si>
+  <si>
+    <t>이주은</t>
+  </si>
+  <si>
+    <t>h20241217@glab.hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>원예진</t>
+  </si>
+  <si>
+    <t>lamsys@naver.com</t>
+  </si>
+  <si>
+    <t>정시효</t>
+  </si>
+  <si>
+    <t>h20241202@glab.hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>영어영문과</t>
+  </si>
+  <si>
+    <t>ehdcks3444@naver.com</t>
+  </si>
+  <si>
+    <t>AI기술경영융합전공</t>
+  </si>
+  <si>
+    <t>김동찬</t>
+  </si>
+  <si>
+    <t>dongyeon7220@gmail.com</t>
+  </si>
+  <si>
+    <t>김동연</t>
+  </si>
+  <si>
+    <t>goseokran051021@gmail.com</t>
+  </si>
+  <si>
+    <t>고석란</t>
+  </si>
+  <si>
+    <t>eunseo041320@naver.com</t>
+  </si>
+  <si>
+    <t>이은서</t>
+  </si>
+  <si>
+    <t>taekwonlmj@gmail.com</t>
+  </si>
+  <si>
+    <t>이미주</t>
+  </si>
+  <si>
+    <t>yyeon0425@gmail.com</t>
+  </si>
+  <si>
+    <t>김연우</t>
+  </si>
+  <si>
+    <t>taehoon9466@gmail.com</t>
+  </si>
+  <si>
+    <t>반도체-디스플레이스쿨</t>
+  </si>
+  <si>
+    <t>염태훈</t>
+  </si>
+  <si>
+    <t>junsung872@gmail.com</t>
+  </si>
+  <si>
+    <t>윤준성</t>
+  </si>
+  <si>
+    <t>yuchan0829@naver.com</t>
+  </si>
+  <si>
+    <t>정유찬</t>
+  </si>
+  <si>
+    <t>romma37@naver.com</t>
+  </si>
+  <si>
+    <t>이새롬</t>
+  </si>
+  <si>
+    <t>htkhwan@naver.com</t>
+  </si>
+  <si>
+    <t>김성민</t>
+  </si>
+  <si>
+    <t>linaeun2004@naver.com</t>
+  </si>
+  <si>
+    <t>shinhyeonho79@gmail.com</t>
+  </si>
+  <si>
+    <t>반도체 디스플레이스쿨</t>
+  </si>
+  <si>
+    <t>신현호</t>
+  </si>
+  <si>
+    <t>minnzz118@gmail.com</t>
+  </si>
+  <si>
+    <t>서민지</t>
+  </si>
+  <si>
+    <t>wkdrmsgur12345678@gmail.com</t>
+  </si>
+  <si>
+    <t>스마트IoT</t>
+  </si>
+  <si>
+    <t>장근혁</t>
+  </si>
+  <si>
+    <t>moonsy06@naver.com</t>
+  </si>
+  <si>
+    <t>문소연</t>
+  </si>
+  <si>
+    <t>wbslqj0240@naver.com</t>
+  </si>
+  <si>
+    <t>박도은</t>
+  </si>
+  <si>
+    <t>baekwondong@naver.com</t>
+  </si>
+  <si>
+    <t>백원동</t>
+  </si>
+  <si>
+    <t>ksyoun1214@gmail.com</t>
+  </si>
+  <si>
+    <t>김승연</t>
+  </si>
+  <si>
+    <t>kimgg0324@naver.com</t>
+  </si>
+  <si>
+    <t>김기건</t>
+  </si>
+  <si>
+    <t>won00814@naver.com</t>
+  </si>
+  <si>
+    <t>이혜원</t>
+  </si>
+  <si>
+    <t>hmsimlk@naver.com</t>
+  </si>
+  <si>
+    <t>홍수민</t>
+  </si>
+  <si>
+    <t>subin051001@naver.com</t>
+  </si>
+  <si>
+    <t>송수빈</t>
+  </si>
+  <si>
+    <t>ssm04072@gmail.com</t>
+  </si>
+  <si>
+    <t>김소정</t>
+  </si>
+  <si>
+    <t>her0507050@gmail.com</t>
+  </si>
+  <si>
+    <t>유지훈</t>
+  </si>
+  <si>
+    <t>ksl100101@gmail.com</t>
+  </si>
+  <si>
+    <t>김사랑</t>
+  </si>
+  <si>
+    <t>ckgustjr0705@gmail.com</t>
+  </si>
+  <si>
+    <t>차현석</t>
+  </si>
+  <si>
+    <t>bella0729@naver.com</t>
+  </si>
+  <si>
+    <t>김해원</t>
+  </si>
+  <si>
+    <t>hyeri051119@naver.com</t>
+  </si>
+  <si>
+    <t>서혜리</t>
+  </si>
+  <si>
+    <t>jbh7574@naver.com</t>
+  </si>
+  <si>
+    <t>전병훈</t>
+  </si>
+  <si>
+    <t>kses12058@gnail.com</t>
+  </si>
+  <si>
+    <t>김도현</t>
+  </si>
+  <si>
+    <t>gin050302@naver.com</t>
+  </si>
+  <si>
+    <t>김현정</t>
+  </si>
+  <si>
+    <t>opopkang0528@gmail.com</t>
+  </si>
+  <si>
+    <t>강현지</t>
+  </si>
+  <si>
+    <t>kim9301204@gmail.com</t>
+  </si>
+  <si>
+    <t>소대현</t>
+  </si>
+  <si>
+    <t>hwangdaeun09@gmail.com</t>
+  </si>
+  <si>
+    <t>황다은</t>
+  </si>
+  <si>
+    <t>gbsgbsgbs01@gmail.com</t>
+  </si>
+  <si>
+    <t>정경환</t>
+  </si>
+  <si>
+    <t>chlehdgk0404@naver.com</t>
+  </si>
+  <si>
+    <t>최동하</t>
+  </si>
+  <si>
+    <t>hyp050515@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">경영학과 </t>
+  </si>
+  <si>
+    <t>박혜인</t>
+  </si>
+  <si>
+    <t>qga0303@naver.com</t>
+  </si>
+  <si>
+    <t>박하민</t>
+  </si>
+  <si>
+    <t>kyjgirin@naver.com</t>
+  </si>
+  <si>
+    <t>의약신소재</t>
+  </si>
+  <si>
+    <t>권예주</t>
+  </si>
+  <si>
+    <t>yooyoungjune@naver.com</t>
+  </si>
+  <si>
+    <t>유영준</t>
+  </si>
+  <si>
+    <t>wjdgksdla@naver.com</t>
+  </si>
+  <si>
+    <t>이정한</t>
+  </si>
+  <si>
+    <t>khmexol140805@gmail.com</t>
+  </si>
+  <si>
+    <t>융합관광경영전공</t>
+  </si>
+  <si>
+    <t>권현민</t>
+  </si>
+  <si>
+    <t>hl24gh0308@gmail.com</t>
+  </si>
+  <si>
+    <t>김지웅</t>
+  </si>
+  <si>
+    <t>kkddyy329@gmail.com</t>
+  </si>
+  <si>
+    <t>데이터사이언스 학부 데이터테크전공</t>
+  </si>
+  <si>
+    <t>thd2270@gmail.com</t>
+  </si>
+  <si>
+    <t>강예송</t>
+  </si>
+  <si>
+    <t>qkrwogus030103@naver.com</t>
+  </si>
+  <si>
+    <t>박재현</t>
+  </si>
+  <si>
+    <t>ratso6113@gmail.com</t>
+  </si>
+  <si>
+    <t>이소연</t>
+  </si>
+  <si>
+    <t>juliaj03@naver.com</t>
+  </si>
+  <si>
+    <t>정한결</t>
+  </si>
+  <si>
+    <t>kec0705@naver.com</t>
+  </si>
+  <si>
+    <t>인공지능융합학부- AI의료</t>
+  </si>
+  <si>
+    <t>이은영</t>
+  </si>
+  <si>
+    <t>kohhyunseo1018@naver.com</t>
+  </si>
+  <si>
+    <t>고현서</t>
+  </si>
+  <si>
+    <t>jaewon102703@gmail.com</t>
+  </si>
+  <si>
+    <t>김재원</t>
+  </si>
+  <si>
+    <t>hanmaim89@gmail.com</t>
+  </si>
+  <si>
+    <t>juho0519@naver.com</t>
+  </si>
+  <si>
+    <t>주호연</t>
+  </si>
+  <si>
+    <t>english3849@naver.com</t>
+  </si>
+  <si>
+    <t>장서린</t>
+  </si>
+  <si>
+    <t>qweryoon0415@gmail.com</t>
+  </si>
+  <si>
+    <t>tyn47760@naver.com</t>
+  </si>
+  <si>
+    <t>권태연</t>
+  </si>
+  <si>
+    <t>s82852747@gmail.com</t>
+  </si>
+  <si>
+    <t>서재영</t>
+  </si>
+  <si>
+    <t>sue92563897@gmail.com</t>
+  </si>
+  <si>
+    <t>김세연</t>
+  </si>
+  <si>
+    <t>jmk104904@gmail.com</t>
+  </si>
+  <si>
+    <t>정민기</t>
+  </si>
+  <si>
+    <t>chrisjuice@naver.com</t>
+  </si>
+  <si>
+    <t>한수민</t>
+  </si>
+  <si>
+    <t>teasu0219@naver.com</t>
+  </si>
+  <si>
+    <t>김태수</t>
+  </si>
+  <si>
+    <t>kimsm3236@gmail.com</t>
+  </si>
+  <si>
+    <t>김민영</t>
+  </si>
+  <si>
+    <t>dmsak0708@naver.com</t>
+  </si>
+  <si>
+    <t>최은임</t>
+  </si>
+  <si>
+    <t>abck0612@naver.com</t>
+  </si>
+  <si>
+    <t>서예림</t>
+  </si>
+  <si>
+    <t>haenlove1021@naver.com</t>
+  </si>
+  <si>
+    <t>janghs476@gmail.com</t>
+  </si>
+  <si>
+    <t>장현서</t>
+  </si>
+  <si>
+    <t>cheolhyun1234@naver.com</t>
+  </si>
+  <si>
+    <t>박철현</t>
+  </si>
+  <si>
+    <t>seo020815@naver.com</t>
+  </si>
+  <si>
+    <t>정보과학대/빅데이터전공</t>
+  </si>
+  <si>
+    <t>hoe978034@gmail.com</t>
+  </si>
+  <si>
+    <t>이호은</t>
+  </si>
+  <si>
+    <t>rlawhdgus1212@gmail.com</t>
+  </si>
+  <si>
+    <t>김종현</t>
+  </si>
+  <si>
+    <t>zouyuanyuan0101@gmail.com</t>
+  </si>
+  <si>
+    <t>문화산업</t>
+  </si>
+  <si>
+    <t>ZOU YUANYUAN</t>
+  </si>
+  <si>
+    <t>in4394@naver.com</t>
+  </si>
+  <si>
+    <t>김혜인</t>
+  </si>
+  <si>
+    <t>000727yjh@naver.com</t>
+  </si>
+  <si>
+    <t>윤종현</t>
+  </si>
+  <si>
+    <t>monica.oh0609@gmail.com</t>
+  </si>
+  <si>
+    <t>오민선</t>
+  </si>
+  <si>
+    <t>hyehwi0807@naver.com</t>
+  </si>
+  <si>
+    <t>김혜빈</t>
+  </si>
+  <si>
+    <t>bellita0321@naver.com</t>
+  </si>
+  <si>
+    <t>손가연</t>
+  </si>
+  <si>
+    <t>bong8hee@gmail.com</t>
+  </si>
+  <si>
+    <t>강태웅</t>
+  </si>
+  <si>
+    <t>jiwon041202@naver.com</t>
+  </si>
+  <si>
+    <t>윤지원</t>
+  </si>
+  <si>
+    <t>kseoj123@naver.com</t>
+  </si>
+  <si>
+    <t>김서진</t>
+  </si>
+  <si>
+    <t>eshan0401@gmail.com</t>
+  </si>
+  <si>
+    <t>디지털미디어컨텐츠 학과</t>
+  </si>
+  <si>
+    <t>한은성</t>
+  </si>
+  <si>
+    <t>hyub1509@naver.com</t>
+  </si>
+  <si>
+    <t>이준협</t>
+  </si>
+  <si>
+    <t>kheom2002@gmail.com</t>
+  </si>
+  <si>
+    <t>엄규현</t>
+  </si>
+  <si>
+    <t>bjfcu7@gmail.com</t>
+  </si>
+  <si>
+    <t>김채연</t>
+  </si>
+  <si>
+    <t>amazing7124@naver.com</t>
+  </si>
+  <si>
+    <t>서준호</t>
+  </si>
+  <si>
+    <t>yeonseo9033@gmail.com</t>
+  </si>
+  <si>
+    <t>고연서</t>
+  </si>
+  <si>
+    <t>yky9430@naver.com</t>
+  </si>
+  <si>
+    <t>유가영</t>
+  </si>
+  <si>
+    <t>kar0173@naver.com</t>
+  </si>
+  <si>
+    <t>최승민</t>
+  </si>
+  <si>
+    <t>jongyeogc126@gmail.com</t>
+  </si>
+  <si>
+    <t>최종혁</t>
+  </si>
+  <si>
+    <t>kim9876584@gmail.com</t>
+  </si>
+  <si>
+    <t>김성욱</t>
+  </si>
+  <si>
+    <t>dldmstj1027@gmail.com</t>
+  </si>
+  <si>
+    <t>kijoopark12@gmail.com</t>
+  </si>
+  <si>
+    <t>박기주</t>
+  </si>
+  <si>
+    <t>god303086@gmail.com</t>
+  </si>
+  <si>
+    <t>남궁연희</t>
+  </si>
+  <si>
+    <t>qkrwndus1117@naver.com</t>
+  </si>
+  <si>
+    <t>박주연</t>
+  </si>
+  <si>
+    <t>xogns7149@naver.com</t>
+  </si>
+  <si>
+    <t>김태욱</t>
+  </si>
+  <si>
+    <t>h20241235@glab.hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>정채원</t>
+  </si>
+  <si>
+    <t>kim1123693@gmail.com</t>
+  </si>
+  <si>
+    <t>김희수</t>
+  </si>
+  <si>
+    <t>gagahyun335@naver.com</t>
+  </si>
+  <si>
+    <t>이가현</t>
+  </si>
+  <si>
+    <t>dhhhxh273@naver.com</t>
+  </si>
+  <si>
+    <t>최서정</t>
+  </si>
+  <si>
+    <t>juseung1449@gmail.com</t>
+  </si>
+  <si>
+    <t>이주승</t>
+  </si>
+  <si>
+    <t>dami1232@naver.com</t>
+  </si>
+  <si>
+    <t>김경재</t>
+  </si>
+  <si>
+    <t>wjdtjdbs8926@naver.com</t>
+  </si>
+  <si>
+    <t>정서윤</t>
+  </si>
+  <si>
+    <t>juicee220@gmail.com</t>
+  </si>
+  <si>
+    <t>최주아</t>
+  </si>
+  <si>
+    <t>jjongwoo0628@naver.com</t>
+  </si>
+  <si>
+    <t>윤종우</t>
+  </si>
+  <si>
+    <t>gnsh2005@naver.com</t>
+  </si>
+  <si>
+    <t>이지나</t>
+  </si>
+  <si>
+    <t>soeun7443@naver.com</t>
+  </si>
+  <si>
+    <t>박소은</t>
+  </si>
+  <si>
+    <t>alex1874@naver.com</t>
+  </si>
+  <si>
+    <t>데이터테크 전공</t>
+  </si>
+  <si>
+    <t>김진수</t>
+  </si>
+  <si>
+    <t>hclee2891@naver.com</t>
+  </si>
+  <si>
+    <t>이학찬</t>
+  </si>
+  <si>
+    <t>h20241226@glab.hallym.ac.kr</t>
+  </si>
+  <si>
+    <t>이주연</t>
+  </si>
+  <si>
+    <t>sminji674@gmail.com</t>
+  </si>
+  <si>
+    <t>송민지</t>
+  </si>
+  <si>
+    <t>hjykmj0916@gmail.com</t>
+  </si>
+  <si>
+    <t>김유경</t>
+  </si>
+  <si>
+    <t>storybjy11@naver.com</t>
+  </si>
+  <si>
+    <t>박기원</t>
+  </si>
+  <si>
+    <t>ahyeon8650@naver.com</t>
+  </si>
+  <si>
+    <t>서아현</t>
+  </si>
+  <si>
+    <t>lim48664401@gmail.com</t>
+  </si>
+  <si>
+    <t>임동욱</t>
+  </si>
+  <si>
+    <t>es187019@gmail.com</t>
+  </si>
+  <si>
+    <t>김현빈</t>
+  </si>
+  <si>
+    <t>choiseoungbin@gmail.com</t>
+  </si>
+  <si>
+    <t>최승빈</t>
+  </si>
+  <si>
+    <t>dldudals0413@naver.com</t>
+  </si>
+  <si>
+    <t>이영민</t>
+  </si>
+  <si>
+    <t>jhbbjshb-djnd@naver.com</t>
+  </si>
+  <si>
+    <t>성지민</t>
+  </si>
+  <si>
+    <t>juheepoiu@gmail.com</t>
+  </si>
+  <si>
+    <t>임주희</t>
+  </si>
+  <si>
+    <t>rhdbswn01@naver.com</t>
+  </si>
+  <si>
+    <t>언론방송융합미디어학과</t>
+  </si>
+  <si>
+    <t>고윤주</t>
+  </si>
+  <si>
+    <t>jahee0114@gmail.com</t>
+  </si>
+  <si>
+    <t>최재희</t>
+  </si>
+  <si>
+    <t>tkdgnl0206@gmail.com</t>
+  </si>
+  <si>
+    <t>이상휘</t>
+  </si>
+  <si>
+    <t>cny120333@naver.com</t>
+  </si>
+  <si>
+    <t>최나연</t>
+  </si>
+  <si>
+    <t>qazxdrf12@naver.com</t>
+  </si>
+  <si>
+    <t>박호연</t>
+  </si>
+  <si>
+    <t>seojungbin050928@naver.com</t>
+  </si>
+  <si>
+    <t>서정빈</t>
+  </si>
+  <si>
+    <t>g01086348696@gmail.com</t>
+  </si>
+  <si>
+    <t>박선근</t>
+  </si>
+  <si>
+    <t>heey7754@naver.com</t>
+  </si>
+  <si>
+    <t>이희연</t>
+  </si>
+  <si>
+    <t>skgurwls0416@gmail.com</t>
+  </si>
+  <si>
+    <t>나혁진</t>
+  </si>
+  <si>
+    <t>woojinkim0518@naver.com</t>
+  </si>
+  <si>
+    <t>김우진</t>
+  </si>
+  <si>
+    <t>hjuu1238@gmail.com</t>
+  </si>
+  <si>
+    <t>조재하</t>
+  </si>
+  <si>
+    <t>pgueue110@gmail.com</t>
+  </si>
+  <si>
+    <t>정다영</t>
+  </si>
+  <si>
+    <t>a01033294075@gmail.com</t>
+  </si>
+  <si>
+    <t>임혜원</t>
+  </si>
+  <si>
+    <t>leeds44@naver.com</t>
+  </si>
+  <si>
+    <t>빅데이터과</t>
+  </si>
+  <si>
+    <t>이동수</t>
+  </si>
+  <si>
+    <t>dltjdgns040528@naver.com</t>
+  </si>
+  <si>
+    <t>이성훈</t>
+  </si>
+  <si>
+    <t>kosac99-@naver.com</t>
+  </si>
+  <si>
+    <t>김성희</t>
+  </si>
+  <si>
+    <t>alexwoojin17@gmail.com</t>
+  </si>
+  <si>
+    <t>차우진</t>
+  </si>
+  <si>
+    <t>siyeon050217@gmail.com</t>
+  </si>
+  <si>
+    <t>이시연</t>
+  </si>
+  <si>
+    <t>imjustdaeunnn@gmail.com</t>
+  </si>
+  <si>
+    <t>정다은</t>
+  </si>
+  <si>
+    <t>jae2001830@gmail.com</t>
+  </si>
+  <si>
+    <t>이재홍</t>
+  </si>
+  <si>
+    <t>jwseok0218@naver.com</t>
+  </si>
+  <si>
+    <t>조우석</t>
+  </si>
+  <si>
+    <t>ujinhong11@gmail.com</t>
+  </si>
+  <si>
+    <t>홍우진</t>
+  </si>
+  <si>
+    <t>nmi123nmi0212@gmail.com</t>
+  </si>
+  <si>
+    <t>노현주</t>
+  </si>
+  <si>
+    <t>lcs7714567@gmail.com</t>
+  </si>
+  <si>
+    <t>jhwoo0513@naver.com</t>
+  </si>
+  <si>
+    <t>사학전공</t>
+  </si>
+  <si>
+    <t>우재홍</t>
+  </si>
+  <si>
+    <t>ehrud6450@naver.con</t>
+  </si>
+  <si>
+    <t>황도경</t>
+  </si>
+  <si>
+    <t>ekksx@naver.com</t>
+  </si>
+  <si>
+    <t>ohyegon050824@gmail.com</t>
+  </si>
+  <si>
+    <t>오예건</t>
+  </si>
+  <si>
+    <t>lunarena0719@naver.com</t>
+  </si>
+  <si>
+    <t>채은서</t>
+  </si>
+  <si>
+    <t>tj5854566@naver.com</t>
+  </si>
+  <si>
+    <t>박서희</t>
+  </si>
+  <si>
+    <t>boeun050214@naver.com</t>
+  </si>
+  <si>
+    <t>이보은</t>
+  </si>
+  <si>
+    <t>wlrhtm@naver.com</t>
+  </si>
+  <si>
+    <t>배승제</t>
+  </si>
+  <si>
+    <t>lym051211-@naver.com</t>
+  </si>
+  <si>
+    <t>이예빈</t>
+  </si>
+  <si>
+    <t>hansoomin1108@gmail.com</t>
+  </si>
+  <si>
+    <t>디지털금융정보과</t>
+  </si>
+  <si>
+    <t>성수민</t>
+  </si>
+  <si>
+    <t>swh12q@gmail.com</t>
+  </si>
+  <si>
+    <t>권지영</t>
+  </si>
+  <si>
+    <t>gmltjd050406@gmail.com</t>
+  </si>
+  <si>
+    <t>김희성</t>
+  </si>
+  <si>
+    <t>chlwodlf9557@naver.com</t>
+  </si>
+  <si>
+    <t>최재일</t>
+  </si>
+  <si>
+    <t>dollee78@naver.com</t>
+  </si>
+  <si>
+    <t>이재민</t>
+  </si>
+  <si>
+    <t>danieloh1216@gmail.com</t>
+  </si>
+  <si>
+    <t>오주람</t>
+  </si>
+  <si>
+    <t>cntmddl1@naver.com</t>
+  </si>
+  <si>
+    <t>국어국문학전공</t>
+  </si>
+  <si>
+    <t>추승이</t>
+  </si>
+  <si>
+    <t>kimminjung6615@hanmail.net</t>
+  </si>
+  <si>
+    <t>pohang0209@gmail.com</t>
+  </si>
+  <si>
+    <t>이성희</t>
+  </si>
+  <si>
+    <t>crescent0221@naver.com</t>
+  </si>
+  <si>
+    <t>일본</t>
+  </si>
+  <si>
+    <t>오상현</t>
+  </si>
+  <si>
+    <t>idhyunmook@gmail.com</t>
+  </si>
+  <si>
+    <t>강현묵</t>
+  </si>
+  <si>
+    <t>fnaf0039@gmail.com</t>
+  </si>
+  <si>
+    <t>박건도</t>
+  </si>
+  <si>
+    <t>a01020945272@gmail.com</t>
+  </si>
+  <si>
+    <t>tldkwhgsl@gmail.com</t>
+  </si>
+  <si>
+    <t>최다온</t>
+  </si>
+  <si>
+    <t>bluelion-gbn9981@naver.com</t>
+  </si>
+  <si>
+    <t>구보늬</t>
+  </si>
+  <si>
+    <t>skrud030405@naver.com</t>
+  </si>
+  <si>
+    <t>김나경</t>
+  </si>
+  <si>
+    <t>minseo1416@naver.com</t>
+  </si>
+  <si>
+    <t>권민서</t>
+  </si>
+  <si>
+    <t>selliakim@gmail.com</t>
+  </si>
+  <si>
+    <t>김수아</t>
+  </si>
+  <si>
+    <t>ssg663927@gmail.com</t>
+  </si>
+  <si>
+    <t>신성결</t>
+  </si>
+  <si>
+    <t>guswjd052428@naver.com</t>
+  </si>
+  <si>
+    <t>전현정</t>
+  </si>
+  <si>
+    <t>yu760923@naver.com</t>
+  </si>
+  <si>
+    <t>노윤희</t>
+  </si>
+  <si>
+    <t>dlwntkd3526@naver.com</t>
+  </si>
+  <si>
+    <t>이주상</t>
+  </si>
+  <si>
+    <t>minchan6020@gmail.com</t>
+  </si>
+  <si>
+    <t>김민찬</t>
+  </si>
+  <si>
+    <t>bsj021105@naver.com</t>
+  </si>
+  <si>
+    <t>백수정</t>
   </si>
 </sst>
 </file>
@@ -2847,10 +4011,10 @@
         <color rgb="FF442F65"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -2858,13 +4022,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF8F9FA"/>
       </top>
       <bottom style="thin">
         <color rgb="FF442F65"/>
@@ -2981,7 +4145,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N376" displayName="Form_Responses1" name="Form_Responses1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N565" displayName="Form_Responses1" name="Form_Responses1" id="1">
   <tableColumns count="14">
     <tableColumn name="타임스탬프" id="1"/>
     <tableColumn name="이메일 주소" id="2"/>
@@ -18597,44 +19761,7793 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="14">
+      <c r="A376" s="11">
         <v>45734.90119138889</v>
       </c>
-      <c r="B376" s="15" t="s">
+      <c r="B376" s="12" t="s">
         <v>889</v>
       </c>
-      <c r="C376" s="15" t="s">
+      <c r="C376" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D376" s="15">
+      <c r="D376" s="12">
         <v>2.0246211E7</v>
       </c>
-      <c r="E376" s="15" t="s">
+      <c r="E376" s="12" t="s">
         <v>890</v>
       </c>
-      <c r="F376" s="15" t="s">
+      <c r="F376" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="G376" s="15" t="s">
+      <c r="G376" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="H376" s="15">
+      <c r="H376" s="12">
         <v>2012.0</v>
       </c>
-      <c r="I376" s="15">
+      <c r="I376" s="12">
         <v>2018.0</v>
       </c>
-      <c r="J376" s="15" t="s">
+      <c r="J376" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="K376" s="15" t="s">
+      <c r="K376" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="L376" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="M376" s="15" t="s">
+      <c r="L376" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M376" s="12" t="s">
         <v>41</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="8">
+        <v>45734.90535626157</v>
+      </c>
+      <c r="B377" s="9" t="s">
+        <v>891</v>
+      </c>
+      <c r="C377" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D377" s="9">
+        <v>2.0243532E7</v>
+      </c>
+      <c r="E377" s="9" t="s">
+        <v>892</v>
+      </c>
+      <c r="F377" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G377" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H377" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I377" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J377" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K377" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L377" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M377" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="11">
+        <v>45734.91131415509</v>
+      </c>
+      <c r="B378" s="12" t="s">
+        <v>893</v>
+      </c>
+      <c r="C378" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D378" s="12">
+        <v>2.0246605E7</v>
+      </c>
+      <c r="E378" s="12" t="s">
+        <v>894</v>
+      </c>
+      <c r="F378" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G378" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H378" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I378" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J378" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K378" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L378" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N378" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="8">
+        <v>45734.95933416666</v>
+      </c>
+      <c r="B379" s="9" t="s">
+        <v>895</v>
+      </c>
+      <c r="C379" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D379" s="9">
+        <v>2.0246941E7</v>
+      </c>
+      <c r="E379" s="9" t="s">
+        <v>896</v>
+      </c>
+      <c r="F379" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G379" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H379" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I379" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J379" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K379" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L379" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N379" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="11">
+        <v>45735.01871495371</v>
+      </c>
+      <c r="B380" s="12" t="s">
+        <v>897</v>
+      </c>
+      <c r="C380" s="12" t="s">
+        <v>898</v>
+      </c>
+      <c r="D380" s="12">
+        <v>2.0233705E7</v>
+      </c>
+      <c r="E380" s="12" t="s">
+        <v>899</v>
+      </c>
+      <c r="F380" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G380" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H380" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I380" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J380" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K380" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L380" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M380" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="8">
+        <v>45735.38278980324</v>
+      </c>
+      <c r="B381" s="9" t="s">
+        <v>900</v>
+      </c>
+      <c r="C381" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D381" s="9">
+        <v>2.0246208E7</v>
+      </c>
+      <c r="E381" s="9" t="s">
+        <v>901</v>
+      </c>
+      <c r="F381" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G381" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H381" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I381" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J381" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K381" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L381" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N381" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="11">
+        <v>45735.477221168985</v>
+      </c>
+      <c r="B382" s="12" t="s">
+        <v>902</v>
+      </c>
+      <c r="C382" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D382" s="12">
+        <v>2.0232941E7</v>
+      </c>
+      <c r="E382" s="12" t="s">
+        <v>903</v>
+      </c>
+      <c r="F382" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G382" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H382" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I382" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J382" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K382" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L382" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M382" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="8">
+        <v>45735.478677534724</v>
+      </c>
+      <c r="B383" s="9" t="s">
+        <v>904</v>
+      </c>
+      <c r="C383" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D383" s="9">
+        <v>2.0242223E7</v>
+      </c>
+      <c r="E383" s="9" t="s">
+        <v>905</v>
+      </c>
+      <c r="F383" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G383" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H383" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I383" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J383" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K383" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L383" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N383" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="11">
+        <v>45735.514177986115</v>
+      </c>
+      <c r="B384" s="12" t="s">
+        <v>906</v>
+      </c>
+      <c r="C384" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D384" s="12">
+        <v>2.024264E7</v>
+      </c>
+      <c r="E384" s="12" t="s">
+        <v>907</v>
+      </c>
+      <c r="F384" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G384" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H384" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I384" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J384" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K384" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L384" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M384" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="8">
+        <v>45735.62479659722</v>
+      </c>
+      <c r="B385" s="9" t="s">
+        <v>908</v>
+      </c>
+      <c r="C385" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D385" s="9">
+        <v>2.0243406E7</v>
+      </c>
+      <c r="E385" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="F385" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G385" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H385" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I385" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J385" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K385" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L385" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M385" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="11">
+        <v>45735.643252222224</v>
+      </c>
+      <c r="B386" s="12" t="s">
+        <v>910</v>
+      </c>
+      <c r="C386" s="12" t="s">
+        <v>911</v>
+      </c>
+      <c r="D386" s="12">
+        <v>2.025394E7</v>
+      </c>
+      <c r="E386" s="12" t="s">
+        <v>912</v>
+      </c>
+      <c r="F386" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G386" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H386" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I386" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J386" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K386" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L386" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N386" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="8">
+        <v>45735.68780185185</v>
+      </c>
+      <c r="B387" s="9" t="s">
+        <v>913</v>
+      </c>
+      <c r="C387" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="D387" s="9">
+        <v>2.0241217E7</v>
+      </c>
+      <c r="E387" s="9" t="s">
+        <v>914</v>
+      </c>
+      <c r="F387" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G387" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H387" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I387" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J387" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K387" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L387" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M387" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="11">
+        <v>45735.69196215278</v>
+      </c>
+      <c r="B388" s="12" t="s">
+        <v>915</v>
+      </c>
+      <c r="C388" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D388" s="12">
+        <v>2.0243427E7</v>
+      </c>
+      <c r="E388" s="12" t="s">
+        <v>916</v>
+      </c>
+      <c r="F388" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G388" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H388" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I388" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J388" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K388" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L388" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M388" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="8">
+        <v>45735.69530965278</v>
+      </c>
+      <c r="B389" s="9" t="s">
+        <v>917</v>
+      </c>
+      <c r="C389" s="9" t="s">
+        <v>918</v>
+      </c>
+      <c r="D389" s="9">
+        <v>2.0241202E7</v>
+      </c>
+      <c r="E389" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="F389" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G389" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H389" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I389" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J389" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K389" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L389" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M389" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="11">
+        <v>45735.71868121528</v>
+      </c>
+      <c r="B390" s="12" t="s">
+        <v>919</v>
+      </c>
+      <c r="C390" s="12" t="s">
+        <v>920</v>
+      </c>
+      <c r="D390" s="12">
+        <v>2.0216712E7</v>
+      </c>
+      <c r="E390" s="12" t="s">
+        <v>921</v>
+      </c>
+      <c r="F390" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G390" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H390" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I390" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J390" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K390" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L390" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M390" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="8">
+        <v>45735.73491850695</v>
+      </c>
+      <c r="B391" s="9" t="s">
+        <v>922</v>
+      </c>
+      <c r="C391" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D391" s="9">
+        <v>2.024691E7</v>
+      </c>
+      <c r="E391" s="9" t="s">
+        <v>923</v>
+      </c>
+      <c r="F391" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G391" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H391" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I391" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J391" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K391" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L391" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M391" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="11">
+        <v>45735.76529509259</v>
+      </c>
+      <c r="B392" s="12" t="s">
+        <v>924</v>
+      </c>
+      <c r="C392" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="D392" s="12">
+        <v>2.0243604E7</v>
+      </c>
+      <c r="E392" s="12" t="s">
+        <v>925</v>
+      </c>
+      <c r="F392" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G392" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H392" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I392" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J392" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K392" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L392" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M392" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="8">
+        <v>45735.79069498843</v>
+      </c>
+      <c r="B393" s="9" t="s">
+        <v>926</v>
+      </c>
+      <c r="C393" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D393" s="9">
+        <v>2.0243009E7</v>
+      </c>
+      <c r="E393" s="9" t="s">
+        <v>927</v>
+      </c>
+      <c r="F393" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G393" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H393" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I393" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J393" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K393" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L393" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N393" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="11">
+        <v>45735.802345324075</v>
+      </c>
+      <c r="B394" s="12" t="s">
+        <v>928</v>
+      </c>
+      <c r="C394" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="D394" s="12">
+        <v>2.0253236E7</v>
+      </c>
+      <c r="E394" s="12" t="s">
+        <v>929</v>
+      </c>
+      <c r="F394" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G394" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H394" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I394" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J394" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K394" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L394" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M394" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="8">
+        <v>45735.91570798611</v>
+      </c>
+      <c r="B395" s="9" t="s">
+        <v>930</v>
+      </c>
+      <c r="C395" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="D395" s="9">
+        <v>2.0232517E7</v>
+      </c>
+      <c r="E395" s="9" t="s">
+        <v>931</v>
+      </c>
+      <c r="F395" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G395" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H395" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I395" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J395" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K395" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L395" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N395" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="11">
+        <v>45735.928216458335</v>
+      </c>
+      <c r="B396" s="12" t="s">
+        <v>932</v>
+      </c>
+      <c r="C396" s="12" t="s">
+        <v>933</v>
+      </c>
+      <c r="D396" s="12">
+        <v>2.0243331E7</v>
+      </c>
+      <c r="E396" s="12" t="s">
+        <v>934</v>
+      </c>
+      <c r="F396" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G396" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H396" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I396" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J396" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K396" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L396" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M396" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="8">
+        <v>45735.93048876157</v>
+      </c>
+      <c r="B397" s="9" t="s">
+        <v>935</v>
+      </c>
+      <c r="C397" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D397" s="9">
+        <v>2.024393E7</v>
+      </c>
+      <c r="E397" s="9" t="s">
+        <v>936</v>
+      </c>
+      <c r="F397" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G397" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H397" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I397" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J397" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K397" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L397" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N397" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="11">
+        <v>45736.00639065972</v>
+      </c>
+      <c r="B398" s="12" t="s">
+        <v>937</v>
+      </c>
+      <c r="C398" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="D398" s="12">
+        <v>2.0241091E7</v>
+      </c>
+      <c r="E398" s="12" t="s">
+        <v>938</v>
+      </c>
+      <c r="F398" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G398" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H398" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I398" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J398" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K398" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L398" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M398" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="8">
+        <v>45736.12511731482</v>
+      </c>
+      <c r="B399" s="9" t="s">
+        <v>939</v>
+      </c>
+      <c r="C399" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D399" s="9">
+        <v>2.0243935E7</v>
+      </c>
+      <c r="E399" s="9" t="s">
+        <v>940</v>
+      </c>
+      <c r="F399" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G399" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H399" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I399" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J399" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K399" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L399" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M399" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="11">
+        <v>45736.41091364583</v>
+      </c>
+      <c r="B400" s="12" t="s">
+        <v>941</v>
+      </c>
+      <c r="C400" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D400" s="12">
+        <v>2.0214109E7</v>
+      </c>
+      <c r="E400" s="12" t="s">
+        <v>942</v>
+      </c>
+      <c r="F400" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G400" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H400" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I400" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J400" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K400" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L400" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M400" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="8">
+        <v>45736.4683015162</v>
+      </c>
+      <c r="B401" s="9" t="s">
+        <v>943</v>
+      </c>
+      <c r="C401" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D401" s="9">
+        <v>2.0246272E7</v>
+      </c>
+      <c r="E401" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F401" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G401" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H401" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I401" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J401" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K401" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L401" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M401" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="11">
+        <v>45736.51959512732</v>
+      </c>
+      <c r="B402" s="12" t="s">
+        <v>944</v>
+      </c>
+      <c r="C402" s="12" t="s">
+        <v>945</v>
+      </c>
+      <c r="D402" s="12">
+        <v>2.0243326E7</v>
+      </c>
+      <c r="E402" s="12" t="s">
+        <v>946</v>
+      </c>
+      <c r="F402" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G402" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H402" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I402" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J402" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K402" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L402" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N402" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="8">
+        <v>45736.62125819444</v>
+      </c>
+      <c r="B403" s="9" t="s">
+        <v>947</v>
+      </c>
+      <c r="C403" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="D403" s="9">
+        <v>2.0246923E7</v>
+      </c>
+      <c r="E403" s="9" t="s">
+        <v>948</v>
+      </c>
+      <c r="F403" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G403" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H403" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I403" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J403" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K403" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L403" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M403" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="11">
+        <v>45736.67999174769</v>
+      </c>
+      <c r="B404" s="12" t="s">
+        <v>949</v>
+      </c>
+      <c r="C404" s="12" t="s">
+        <v>950</v>
+      </c>
+      <c r="D404" s="12">
+        <v>2.024524E7</v>
+      </c>
+      <c r="E404" s="12" t="s">
+        <v>951</v>
+      </c>
+      <c r="F404" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G404" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H404" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I404" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J404" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K404" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L404" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N404" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="8">
+        <v>45736.8696159838</v>
+      </c>
+      <c r="B405" s="9" t="s">
+        <v>952</v>
+      </c>
+      <c r="C405" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D405" s="9">
+        <v>2.0242949E7</v>
+      </c>
+      <c r="E405" s="9" t="s">
+        <v>953</v>
+      </c>
+      <c r="F405" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G405" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H405" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I405" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J405" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K405" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L405" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M405" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="11">
+        <v>45736.90950487269</v>
+      </c>
+      <c r="B406" s="12" t="s">
+        <v>954</v>
+      </c>
+      <c r="C406" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D406" s="12">
+        <v>2.0206612E7</v>
+      </c>
+      <c r="E406" s="12" t="s">
+        <v>955</v>
+      </c>
+      <c r="F406" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G406" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H406" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I406" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J406" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K406" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L406" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N406" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="8">
+        <v>45737.008254976856</v>
+      </c>
+      <c r="B407" s="9" t="s">
+        <v>956</v>
+      </c>
+      <c r="C407" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D407" s="9">
+        <v>2.0203921E7</v>
+      </c>
+      <c r="E407" s="9" t="s">
+        <v>957</v>
+      </c>
+      <c r="F407" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G407" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H407" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I407" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J407" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K407" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L407" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N407" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="11">
+        <v>45737.54389634259</v>
+      </c>
+      <c r="B408" s="12" t="s">
+        <v>958</v>
+      </c>
+      <c r="C408" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D408" s="12">
+        <v>2.0196405E7</v>
+      </c>
+      <c r="E408" s="12" t="s">
+        <v>959</v>
+      </c>
+      <c r="F408" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G408" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H408" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I408" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J408" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K408" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L408" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N408" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="8">
+        <v>45737.55770434027</v>
+      </c>
+      <c r="B409" s="9" t="s">
+        <v>960</v>
+      </c>
+      <c r="C409" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D409" s="9">
+        <v>2.0242917E7</v>
+      </c>
+      <c r="E409" s="9" t="s">
+        <v>961</v>
+      </c>
+      <c r="F409" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G409" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H409" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I409" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J409" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K409" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L409" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M409" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="11">
+        <v>45737.6055834838</v>
+      </c>
+      <c r="B410" s="12" t="s">
+        <v>962</v>
+      </c>
+      <c r="C410" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="D410" s="12">
+        <v>2.0242345E7</v>
+      </c>
+      <c r="E410" s="12" t="s">
+        <v>963</v>
+      </c>
+      <c r="F410" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G410" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H410" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I410" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J410" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K410" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L410" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N410" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="8">
+        <v>45737.61058483797</v>
+      </c>
+      <c r="B411" s="9" t="s">
+        <v>964</v>
+      </c>
+      <c r="C411" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D411" s="9">
+        <v>2.0243545E7</v>
+      </c>
+      <c r="E411" s="9" t="s">
+        <v>965</v>
+      </c>
+      <c r="F411" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G411" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H411" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I411" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J411" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="K411" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L411" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M411" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="11">
+        <v>45737.64609895833</v>
+      </c>
+      <c r="B412" s="12" t="s">
+        <v>966</v>
+      </c>
+      <c r="C412" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="D412" s="12">
+        <v>2.024253E7</v>
+      </c>
+      <c r="E412" s="12" t="s">
+        <v>967</v>
+      </c>
+      <c r="F412" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G412" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H412" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I412" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J412" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K412" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L412" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M412" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="8">
+        <v>45737.66977314815</v>
+      </c>
+      <c r="B413" s="9" t="s">
+        <v>968</v>
+      </c>
+      <c r="C413" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D413" s="9">
+        <v>2.024271E7</v>
+      </c>
+      <c r="E413" s="9" t="s">
+        <v>969</v>
+      </c>
+      <c r="F413" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G413" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H413" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I413" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J413" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K413" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L413" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N413" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="11">
+        <v>45737.67798299769</v>
+      </c>
+      <c r="B414" s="12" t="s">
+        <v>970</v>
+      </c>
+      <c r="C414" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D414" s="12">
+        <v>2.0243525E7</v>
+      </c>
+      <c r="E414" s="12" t="s">
+        <v>971</v>
+      </c>
+      <c r="F414" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G414" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H414" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I414" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J414" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K414" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L414" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N414" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="8">
+        <v>45737.690100162035</v>
+      </c>
+      <c r="B415" s="9" t="s">
+        <v>972</v>
+      </c>
+      <c r="C415" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D415" s="9">
+        <v>2.024231E7</v>
+      </c>
+      <c r="E415" s="9" t="s">
+        <v>973</v>
+      </c>
+      <c r="F415" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G415" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H415" s="9">
+        <v>2027.0</v>
+      </c>
+      <c r="I415" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J415" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K415" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L415" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N415" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="11">
+        <v>45737.69630836806</v>
+      </c>
+      <c r="B416" s="12" t="s">
+        <v>974</v>
+      </c>
+      <c r="C416" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D416" s="12">
+        <v>2.024629E7</v>
+      </c>
+      <c r="E416" s="12" t="s">
+        <v>975</v>
+      </c>
+      <c r="F416" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G416" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H416" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I416" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J416" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K416" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L416" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N416" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="8">
+        <v>45737.71975903935</v>
+      </c>
+      <c r="B417" s="9" t="s">
+        <v>976</v>
+      </c>
+      <c r="C417" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D417" s="9">
+        <v>2.0246231E7</v>
+      </c>
+      <c r="E417" s="9" t="s">
+        <v>977</v>
+      </c>
+      <c r="F417" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G417" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H417" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I417" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J417" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K417" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L417" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N417" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="11">
+        <v>45737.7455812963</v>
+      </c>
+      <c r="B418" s="12" t="s">
+        <v>978</v>
+      </c>
+      <c r="C418" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D418" s="12">
+        <v>2.0243515E7</v>
+      </c>
+      <c r="E418" s="12" t="s">
+        <v>979</v>
+      </c>
+      <c r="F418" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G418" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H418" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I418" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J418" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K418" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L418" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M418" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="8">
+        <v>45737.748357881945</v>
+      </c>
+      <c r="B419" s="9" t="s">
+        <v>980</v>
+      </c>
+      <c r="C419" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D419" s="9">
+        <v>2.0183242E7</v>
+      </c>
+      <c r="E419" s="9" t="s">
+        <v>981</v>
+      </c>
+      <c r="F419" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G419" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H419" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I419" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J419" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K419" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L419" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N419" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="11">
+        <v>45737.77171185185</v>
+      </c>
+      <c r="B420" s="12" t="s">
+        <v>982</v>
+      </c>
+      <c r="C420" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D420" s="12">
+        <v>2.024292E7</v>
+      </c>
+      <c r="E420" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="F420" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G420" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H420" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I420" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J420" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K420" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L420" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M420" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="8">
+        <v>45737.772644780096</v>
+      </c>
+      <c r="B421" s="9" t="s">
+        <v>984</v>
+      </c>
+      <c r="C421" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D421" s="9">
+        <v>2.0242315E7</v>
+      </c>
+      <c r="E421" s="9" t="s">
+        <v>985</v>
+      </c>
+      <c r="F421" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G421" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H421" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I421" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J421" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K421" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L421" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M421" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="11">
+        <v>45737.883628703705</v>
+      </c>
+      <c r="B422" s="12" t="s">
+        <v>986</v>
+      </c>
+      <c r="C422" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D422" s="12">
+        <v>2.0242203E7</v>
+      </c>
+      <c r="E422" s="12" t="s">
+        <v>987</v>
+      </c>
+      <c r="F422" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G422" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H422" s="12">
+        <v>2027.0</v>
+      </c>
+      <c r="I422" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J422" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K422" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L422" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M422" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="8">
+        <v>45737.89002680556</v>
+      </c>
+      <c r="B423" s="9" t="s">
+        <v>988</v>
+      </c>
+      <c r="C423" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D423" s="9">
+        <v>2.0193716E7</v>
+      </c>
+      <c r="E423" s="9" t="s">
+        <v>989</v>
+      </c>
+      <c r="F423" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G423" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H423" s="9">
+        <v>2027.0</v>
+      </c>
+      <c r="I423" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J423" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K423" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L423" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N423" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="11">
+        <v>45737.92919309028</v>
+      </c>
+      <c r="B424" s="12" t="s">
+        <v>990</v>
+      </c>
+      <c r="C424" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D424" s="12">
+        <v>2.025384E7</v>
+      </c>
+      <c r="E424" s="12" t="s">
+        <v>991</v>
+      </c>
+      <c r="F424" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G424" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H424" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I424" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J424" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K424" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L424" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M424" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="8">
+        <v>45737.96478895833</v>
+      </c>
+      <c r="B425" s="9" t="s">
+        <v>992</v>
+      </c>
+      <c r="C425" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="D425" s="9">
+        <v>2.0256773E7</v>
+      </c>
+      <c r="E425" s="9" t="s">
+        <v>993</v>
+      </c>
+      <c r="F425" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G425" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H425" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I425" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J425" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K425" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L425" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M425" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="11">
+        <v>45737.986018125</v>
+      </c>
+      <c r="B426" s="12" t="s">
+        <v>994</v>
+      </c>
+      <c r="C426" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D426" s="12">
+        <v>2.0203048E7</v>
+      </c>
+      <c r="E426" s="12" t="s">
+        <v>995</v>
+      </c>
+      <c r="F426" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G426" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H426" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I426" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J426" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K426" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L426" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N426" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="8">
+        <v>45738.005089212966</v>
+      </c>
+      <c r="B427" s="9" t="s">
+        <v>996</v>
+      </c>
+      <c r="C427" s="9" t="s">
+        <v>997</v>
+      </c>
+      <c r="D427" s="9">
+        <v>2.0242967E7</v>
+      </c>
+      <c r="E427" s="9" t="s">
+        <v>998</v>
+      </c>
+      <c r="F427" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G427" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H427" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I427" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J427" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K427" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L427" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M427" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="11">
+        <v>45738.020397835644</v>
+      </c>
+      <c r="B428" s="12" t="s">
+        <v>999</v>
+      </c>
+      <c r="C428" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D428" s="12">
+        <v>2.0222326E7</v>
+      </c>
+      <c r="E428" s="12" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F428" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G428" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H428" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I428" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J428" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K428" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L428" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N428" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="8">
+        <v>45738.03885945602</v>
+      </c>
+      <c r="B429" s="9" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C429" s="9" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D429" s="9">
+        <v>2.0246606E7</v>
+      </c>
+      <c r="E429" s="9" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F429" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G429" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H429" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I429" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J429" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K429" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L429" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M429" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="11">
+        <v>45738.07795813658</v>
+      </c>
+      <c r="B430" s="12" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C430" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="D430" s="12">
+        <v>2.0216739E7</v>
+      </c>
+      <c r="E430" s="12" t="s">
+        <v>1005</v>
+      </c>
+      <c r="F430" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G430" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H430" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I430" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J430" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K430" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L430" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M430" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="8">
+        <v>45738.083548333336</v>
+      </c>
+      <c r="B431" s="9" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C431" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D431" s="9">
+        <v>2.0203021E7</v>
+      </c>
+      <c r="E431" s="9" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F431" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G431" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H431" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I431" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J431" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K431" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L431" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N431" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="11">
+        <v>45738.55034715278</v>
+      </c>
+      <c r="B432" s="12" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C432" s="12" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D432" s="12">
+        <v>2.0246607E7</v>
+      </c>
+      <c r="E432" s="12" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F432" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="G432" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H432" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I432" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J432" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K432" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L432" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M432" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="8">
+        <v>45738.56752491898</v>
+      </c>
+      <c r="B433" s="9" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C433" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D433" s="9">
+        <v>2.0246226E7</v>
+      </c>
+      <c r="E433" s="9" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F433" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G433" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H433" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I433" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J433" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K433" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L433" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N433" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="11">
+        <v>45738.5749559838</v>
+      </c>
+      <c r="B434" s="12" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C434" s="12" t="s">
+        <v>1014</v>
+      </c>
+      <c r="D434" s="12">
+        <v>2.0243208E7</v>
+      </c>
+      <c r="E434" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="F434" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G434" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H434" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I434" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J434" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K434" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L434" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M434" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="8">
+        <v>45738.60489283565</v>
+      </c>
+      <c r="B435" s="9" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C435" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D435" s="9">
+        <v>2.0243701E7</v>
+      </c>
+      <c r="E435" s="9" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F435" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G435" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H435" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I435" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J435" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K435" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L435" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M435" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="11">
+        <v>45738.64325866898</v>
+      </c>
+      <c r="B436" s="12" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C436" s="12" t="s">
+        <v>309</v>
+      </c>
+      <c r="D436" s="12">
+        <v>2.0231039E7</v>
+      </c>
+      <c r="E436" s="12" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F436" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G436" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H436" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I436" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J436" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K436" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L436" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N436" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="8">
+        <v>45738.64413863426</v>
+      </c>
+      <c r="B437" s="9" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C437" s="9" t="s">
+        <v>662</v>
+      </c>
+      <c r="D437" s="9">
+        <v>2.024255E7</v>
+      </c>
+      <c r="E437" s="9" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F437" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G437" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H437" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I437" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J437" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K437" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L437" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M437" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="11">
+        <v>45738.667445046296</v>
+      </c>
+      <c r="B438" s="12" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C438" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="D438" s="12">
+        <v>2.0243954E7</v>
+      </c>
+      <c r="E438" s="12" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F438" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G438" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H438" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I438" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J438" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K438" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L438" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N438" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="8">
+        <v>45738.71973546296</v>
+      </c>
+      <c r="B439" s="9" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C439" s="9" t="s">
+        <v>1024</v>
+      </c>
+      <c r="D439" s="9">
+        <v>2.0227161E7</v>
+      </c>
+      <c r="E439" s="9" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F439" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G439" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H439" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I439" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J439" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K439" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L439" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N439" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="11">
+        <v>45738.75501896991</v>
+      </c>
+      <c r="B440" s="12" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C440" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D440" s="12">
+        <v>2.0225108E7</v>
+      </c>
+      <c r="E440" s="12" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F440" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G440" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H440" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I440" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J440" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K440" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L440" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M440" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="8">
+        <v>45738.77960703704</v>
+      </c>
+      <c r="B441" s="9" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C441" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D441" s="9">
+        <v>2.0236228E7</v>
+      </c>
+      <c r="E441" s="9" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F441" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G441" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H441" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I441" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J441" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K441" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L441" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M441" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="11">
+        <v>45738.80513517361</v>
+      </c>
+      <c r="B442" s="12" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C442" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D442" s="12">
+        <v>2.0253006E7</v>
+      </c>
+      <c r="E442" s="12" t="s">
+        <v>802</v>
+      </c>
+      <c r="F442" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G442" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H442" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I442" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J442" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K442" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L442" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M442" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="8">
+        <v>45738.815496041665</v>
+      </c>
+      <c r="B443" s="9" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C443" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D443" s="9">
+        <v>2.0243039E7</v>
+      </c>
+      <c r="E443" s="9" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F443" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G443" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="H443" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I443" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J443" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K443" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L443" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N443" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="11">
+        <v>45738.83892807871</v>
+      </c>
+      <c r="B444" s="12" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C444" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D444" s="12">
+        <v>2.0242838E7</v>
+      </c>
+      <c r="E444" s="12" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F444" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G444" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H444" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I444" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J444" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K444" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L444" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M444" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="8">
+        <v>45738.84235392361</v>
+      </c>
+      <c r="B445" s="9" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C445" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D445" s="9">
+        <v>2.0245212E7</v>
+      </c>
+      <c r="E445" s="9" t="s">
+        <v>573</v>
+      </c>
+      <c r="F445" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G445" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H445" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I445" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J445" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K445" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L445" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M445" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="11">
+        <v>45738.8453138426</v>
+      </c>
+      <c r="B446" s="12" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C446" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D446" s="12">
+        <v>2.0246212E7</v>
+      </c>
+      <c r="E446" s="12" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F446" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G446" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H446" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I446" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J446" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K446" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L446" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N446" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="8">
+        <v>45738.858608090275</v>
+      </c>
+      <c r="B447" s="9" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C447" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="D447" s="9">
+        <v>2.0243226E7</v>
+      </c>
+      <c r="E447" s="9" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F447" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G447" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H447" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I447" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J447" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K447" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L447" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M447" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="11">
+        <v>45738.87446627315</v>
+      </c>
+      <c r="B448" s="12" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C448" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="D448" s="12">
+        <v>2.0241015E7</v>
+      </c>
+      <c r="E448" s="12" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F448" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G448" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H448" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I448" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J448" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K448" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L448" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M448" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="8">
+        <v>45738.91968060185</v>
+      </c>
+      <c r="B449" s="9" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C449" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D449" s="9">
+        <v>2.0244144E7</v>
+      </c>
+      <c r="E449" s="9" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F449" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G449" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H449" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I449" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J449" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="K449" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L449" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M449" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="11">
+        <v>45738.92431320602</v>
+      </c>
+      <c r="B450" s="12" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C450" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="D450" s="12">
+        <v>2.0255273E7</v>
+      </c>
+      <c r="E450" s="12" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F450" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G450" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H450" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I450" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J450" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K450" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L450" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M450" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="8">
+        <v>45738.93063569444</v>
+      </c>
+      <c r="B451" s="9" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C451" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D451" s="9">
+        <v>2.0243708E7</v>
+      </c>
+      <c r="E451" s="9" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F451" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G451" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H451" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I451" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J451" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K451" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L451" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N451" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="11">
+        <v>45738.94717818287</v>
+      </c>
+      <c r="B452" s="12" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C452" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="D452" s="12">
+        <v>2.0225119E7</v>
+      </c>
+      <c r="E452" s="12" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F452" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G452" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H452" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I452" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J452" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K452" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L452" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N452" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="8">
+        <v>45738.95290228009</v>
+      </c>
+      <c r="B453" s="9" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C453" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="D453" s="9">
+        <v>2.0225268E7</v>
+      </c>
+      <c r="E453" s="9" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F453" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G453" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H453" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I453" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J453" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K453" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L453" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M453" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="11">
+        <v>45738.992538819446</v>
+      </c>
+      <c r="B454" s="12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C454" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D454" s="12">
+        <v>2.0243817E7</v>
+      </c>
+      <c r="E454" s="12" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F454" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G454" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H454" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I454" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J454" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K454" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L454" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N454" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="8">
+        <v>45739.02464650463</v>
+      </c>
+      <c r="B455" s="9" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C455" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="D455" s="9">
+        <v>2.024662E7</v>
+      </c>
+      <c r="E455" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="F455" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G455" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H455" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I455" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J455" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K455" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L455" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N455" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="11">
+        <v>45739.03769892361</v>
+      </c>
+      <c r="B456" s="12" t="s">
+        <v>1055</v>
+      </c>
+      <c r="C456" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="D456" s="12">
+        <v>2.0245245E7</v>
+      </c>
+      <c r="E456" s="12" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F456" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G456" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H456" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I456" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J456" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K456" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L456" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N456" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="8">
+        <v>45739.05891299769</v>
+      </c>
+      <c r="B457" s="9" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C457" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D457" s="9">
+        <v>2.024272E7</v>
+      </c>
+      <c r="E457" s="9" t="s">
+        <v>1058</v>
+      </c>
+      <c r="F457" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G457" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="H457" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I457" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J457" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K457" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L457" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N457" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="11">
+        <v>45739.31440292824</v>
+      </c>
+      <c r="B458" s="12" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C458" s="12" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D458" s="12">
+        <v>2.0215135E7</v>
+      </c>
+      <c r="E458" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="F458" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G458" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H458" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I458" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J458" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K458" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L458" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N458" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="8">
+        <v>45739.32693894676</v>
+      </c>
+      <c r="B459" s="9" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C459" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="D459" s="9">
+        <v>2.0243837E7</v>
+      </c>
+      <c r="E459" s="9" t="s">
+        <v>1062</v>
+      </c>
+      <c r="F459" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G459" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H459" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I459" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J459" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K459" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L459" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N459" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="11">
+        <v>45739.350158402776</v>
+      </c>
+      <c r="B460" s="12" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C460" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="D460" s="12">
+        <v>2.0192844E7</v>
+      </c>
+      <c r="E460" s="12" t="s">
+        <v>1064</v>
+      </c>
+      <c r="F460" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G460" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H460" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I460" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J460" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K460" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L460" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N460" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="8">
+        <v>45739.38682668981</v>
+      </c>
+      <c r="B461" s="9" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C461" s="9" t="s">
+        <v>1066</v>
+      </c>
+      <c r="D461" s="9">
+        <v>2.0318005E7</v>
+      </c>
+      <c r="E461" s="9" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F461" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G461" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H461" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I461" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J461" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K461" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L461" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M461" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="11">
+        <v>45739.38995119213</v>
+      </c>
+      <c r="B462" s="12" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C462" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D462" s="12">
+        <v>2.0232323E7</v>
+      </c>
+      <c r="E462" s="12" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F462" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G462" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H462" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I462" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J462" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K462" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L462" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N462" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="8">
+        <v>45739.401763229165</v>
+      </c>
+      <c r="B463" s="9" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C463" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="D463" s="9">
+        <v>2.0235218E7</v>
+      </c>
+      <c r="E463" s="9" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F463" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G463" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H463" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I463" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J463" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K463" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L463" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N463" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="11">
+        <v>45739.41441888889</v>
+      </c>
+      <c r="B464" s="12" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C464" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D464" s="12">
+        <v>2.0231618E7</v>
+      </c>
+      <c r="E464" s="12" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F464" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G464" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H464" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I464" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J464" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K464" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L464" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M464" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="8">
+        <v>45739.43949658565</v>
+      </c>
+      <c r="B465" s="9" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C465" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="D465" s="9">
+        <v>2.0241711E7</v>
+      </c>
+      <c r="E465" s="9" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F465" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G465" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H465" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I465" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J465" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K465" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L465" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N465" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="11">
+        <v>45739.44700349537</v>
+      </c>
+      <c r="B466" s="12" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C466" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D466" s="12">
+        <v>2.023297E7</v>
+      </c>
+      <c r="E466" s="12" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F466" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G466" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H466" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I466" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J466" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K466" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L466" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N466" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="8">
+        <v>45739.450955196764</v>
+      </c>
+      <c r="B467" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C467" s="9" t="s">
+        <v>303</v>
+      </c>
+      <c r="D467" s="9">
+        <v>2.0202905E7</v>
+      </c>
+      <c r="E467" s="9" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F467" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G467" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H467" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I467" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J467" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K467" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L467" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M467" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="11">
+        <v>45739.48547189815</v>
+      </c>
+      <c r="B468" s="12" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C468" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D468" s="12">
+        <v>2.0252225E7</v>
+      </c>
+      <c r="E468" s="12" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F468" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="G468" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H468" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I468" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J468" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K468" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L468" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N468" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="8">
+        <v>45739.49298319445</v>
+      </c>
+      <c r="B469" s="9" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C469" s="9" t="s">
+        <v>242</v>
+      </c>
+      <c r="D469" s="9">
+        <v>2.0243906E7</v>
+      </c>
+      <c r="E469" s="9" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F469" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G469" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H469" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I469" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J469" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K469" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L469" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N469" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="11">
+        <v>45739.49416236111</v>
+      </c>
+      <c r="B470" s="12" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C470" s="12" t="s">
+        <v>1085</v>
+      </c>
+      <c r="D470" s="12">
+        <v>2.0242585E7</v>
+      </c>
+      <c r="E470" s="12" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F470" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G470" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H470" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I470" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J470" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K470" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L470" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N470" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="8">
+        <v>45739.512649212964</v>
+      </c>
+      <c r="B471" s="9" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C471" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D471" s="9">
+        <v>2.0195226E7</v>
+      </c>
+      <c r="E471" s="9" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F471" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G471" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H471" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I471" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J471" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K471" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L471" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N471" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="11">
+        <v>45739.51593084491</v>
+      </c>
+      <c r="B472" s="12" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C472" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D472" s="12">
+        <v>2.0212976E7</v>
+      </c>
+      <c r="E472" s="12" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F472" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G472" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H472" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I472" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J472" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K472" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L472" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N472" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="8">
+        <v>45739.517069814814</v>
+      </c>
+      <c r="B473" s="9" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C473" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D473" s="9">
+        <v>2.0242214E7</v>
+      </c>
+      <c r="E473" s="9" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F473" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G473" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H473" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I473" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J473" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K473" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L473" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M473" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="11">
+        <v>45739.55242732639</v>
+      </c>
+      <c r="B474" s="12" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C474" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="D474" s="12">
+        <v>2.0202531E7</v>
+      </c>
+      <c r="E474" s="12" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F474" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G474" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H474" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I474" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J474" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K474" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L474" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M474" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="8">
+        <v>45739.569009363426</v>
+      </c>
+      <c r="B475" s="9" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C475" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D475" s="9">
+        <v>2.0246703E7</v>
+      </c>
+      <c r="E475" s="9" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F475" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G475" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H475" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I475" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J475" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K475" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L475" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N475" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="11">
+        <v>45739.57040456019</v>
+      </c>
+      <c r="B476" s="12" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C476" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D476" s="12">
+        <v>2.0207106E7</v>
+      </c>
+      <c r="E476" s="12" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F476" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G476" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H476" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I476" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J476" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K476" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L476" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M476" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="8">
+        <v>45739.57242640047</v>
+      </c>
+      <c r="B477" s="9" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C477" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="D477" s="9">
+        <v>2.0202362E7</v>
+      </c>
+      <c r="E477" s="9" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F477" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G477" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H477" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I477" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J477" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K477" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L477" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M477" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="11">
+        <v>45739.58205261574</v>
+      </c>
+      <c r="B478" s="12" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C478" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D478" s="12">
+        <v>2.0211537E7</v>
+      </c>
+      <c r="E478" s="12" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F478" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G478" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H478" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I478" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J478" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="K478" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L478" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M478" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="8">
+        <v>45739.595550405094</v>
+      </c>
+      <c r="B479" s="9" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C479" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="D479" s="9">
+        <v>2.0241704E7</v>
+      </c>
+      <c r="E479" s="9" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F479" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G479" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H479" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I479" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J479" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K479" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L479" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M479" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="11">
+        <v>45739.597322500005</v>
+      </c>
+      <c r="B480" s="12" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C480" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D480" s="12">
+        <v>2.0232128E7</v>
+      </c>
+      <c r="E480" s="12" t="s">
+        <v>927</v>
+      </c>
+      <c r="F480" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G480" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H480" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I480" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J480" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K480" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L480" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N480" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="8">
+        <v>45739.598253993056</v>
+      </c>
+      <c r="B481" s="9" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C481" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="D481" s="9">
+        <v>2.0212527E7</v>
+      </c>
+      <c r="E481" s="9" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F481" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G481" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H481" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I481" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J481" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K481" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L481" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M481" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="11">
+        <v>45739.60219990741</v>
+      </c>
+      <c r="B482" s="12" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C482" s="12" t="s">
+        <v>662</v>
+      </c>
+      <c r="D482" s="12">
+        <v>2.0227042E7</v>
+      </c>
+      <c r="E482" s="12" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F482" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G482" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H482" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I482" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J482" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K482" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L482" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M482" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="8">
+        <v>45739.602649444445</v>
+      </c>
+      <c r="B483" s="9" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C483" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D483" s="9">
+        <v>2.0243513E7</v>
+      </c>
+      <c r="E483" s="9" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F483" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G483" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H483" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I483" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J483" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K483" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L483" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M483" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="11">
+        <v>45739.60991846064</v>
+      </c>
+      <c r="B484" s="12" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C484" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D484" s="12">
+        <v>2.0202939E7</v>
+      </c>
+      <c r="E484" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F484" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G484" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H484" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I484" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J484" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K484" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L484" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N484" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="8">
+        <v>45739.62472417824</v>
+      </c>
+      <c r="B485" s="9" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C485" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="D485" s="9">
+        <v>2.0241235E7</v>
+      </c>
+      <c r="E485" s="9" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F485" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G485" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H485" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I485" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J485" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K485" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L485" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N485" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="11">
+        <v>45739.648818483794</v>
+      </c>
+      <c r="B486" s="12" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C486" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="D486" s="12">
+        <v>2.0202215E7</v>
+      </c>
+      <c r="E486" s="12" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F486" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G486" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H486" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I486" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J486" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K486" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L486" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M486" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="8">
+        <v>45739.65660453704</v>
+      </c>
+      <c r="B487" s="9" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C487" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D487" s="9">
+        <v>2.0212997E7</v>
+      </c>
+      <c r="E487" s="9" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F487" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G487" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H487" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I487" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J487" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K487" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L487" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N487" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="11">
+        <v>45739.665195</v>
+      </c>
+      <c r="B488" s="12" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C488" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="D488" s="12">
+        <v>2.0213639E7</v>
+      </c>
+      <c r="E488" s="12" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F488" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G488" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H488" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I488" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J488" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K488" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L488" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M488" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="8">
+        <v>45739.665395856486</v>
+      </c>
+      <c r="B489" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C489" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="D489" s="9">
+        <v>2.0203726E7</v>
+      </c>
+      <c r="E489" s="9" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F489" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G489" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H489" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I489" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J489" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K489" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L489" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M489" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="11">
+        <v>45739.66588122685</v>
+      </c>
+      <c r="B490" s="12" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C490" s="12" t="s">
+        <v>320</v>
+      </c>
+      <c r="D490" s="12">
+        <v>2.0205117E7</v>
+      </c>
+      <c r="E490" s="12" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F490" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G490" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H490" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I490" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J490" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K490" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L490" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M490" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="8">
+        <v>45739.66620527778</v>
+      </c>
+      <c r="B491" s="9" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C491" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="D491" s="9">
+        <v>2.024109E7</v>
+      </c>
+      <c r="E491" s="9" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F491" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G491" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H491" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I491" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J491" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K491" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L491" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N491" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="11">
+        <v>45739.66840601852</v>
+      </c>
+      <c r="B492" s="12" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C492" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="D492" s="12">
+        <v>2.0231101E7</v>
+      </c>
+      <c r="E492" s="12" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F492" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G492" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H492" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I492" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J492" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K492" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L492" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N492" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="8">
+        <v>45739.66844016204</v>
+      </c>
+      <c r="B493" s="9" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C493" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="D493" s="9">
+        <v>2.0231062E7</v>
+      </c>
+      <c r="E493" s="9" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F493" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G493" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H493" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I493" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J493" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K493" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L493" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N493" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="11">
+        <v>45739.672849131945</v>
+      </c>
+      <c r="B494" s="12" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C494" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D494" s="12">
+        <v>2.024627E7</v>
+      </c>
+      <c r="E494" s="12" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F494" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G494" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H494" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I494" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J494" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K494" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L494" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M494" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="8">
+        <v>45739.68118079861</v>
+      </c>
+      <c r="B495" s="9" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C495" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D495" s="9">
+        <v>2.0246236E7</v>
+      </c>
+      <c r="E495" s="9" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F495" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G495" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H495" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I495" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J495" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K495" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L495" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M495" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="11">
+        <v>45739.68397219907</v>
+      </c>
+      <c r="B496" s="12" t="s">
+        <v>1136</v>
+      </c>
+      <c r="C496" s="12" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D496" s="12">
+        <v>2.0233214E7</v>
+      </c>
+      <c r="E496" s="12" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F496" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G496" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H496" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I496" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J496" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K496" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L496" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N496" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="8">
+        <v>45739.68439009259</v>
+      </c>
+      <c r="B497" s="9" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C497" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D497" s="9">
+        <v>2.0223529E7</v>
+      </c>
+      <c r="E497" s="9" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F497" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G497" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H497" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I497" s="9">
+        <v>2018.0</v>
+      </c>
+      <c r="J497" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K497" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L497" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M497" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="11">
+        <v>45739.68559710648</v>
+      </c>
+      <c r="B498" s="12" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C498" s="12" t="s">
+        <v>306</v>
+      </c>
+      <c r="D498" s="12">
+        <v>2.0241226E7</v>
+      </c>
+      <c r="E498" s="12" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F498" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G498" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H498" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I498" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J498" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K498" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L498" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M498" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="8">
+        <v>45739.68773738426</v>
+      </c>
+      <c r="B499" s="9" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C499" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D499" s="9">
+        <v>2.0243623E7</v>
+      </c>
+      <c r="E499" s="9" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F499" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G499" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H499" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I499" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J499" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K499" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L499" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M499" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="11">
+        <v>45739.69169585648</v>
+      </c>
+      <c r="B500" s="12" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C500" s="12" t="s">
+        <v>429</v>
+      </c>
+      <c r="D500" s="12">
+        <v>2.0241018E7</v>
+      </c>
+      <c r="E500" s="12" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F500" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G500" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H500" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I500" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J500" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K500" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L500" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M500" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="8">
+        <v>45739.69183797453</v>
+      </c>
+      <c r="B501" s="9" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C501" s="9" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D501" s="9">
+        <v>2.0191615E7</v>
+      </c>
+      <c r="E501" s="9" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F501" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G501" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H501" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I501" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J501" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K501" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L501" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N501" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="11">
+        <v>45739.69610052083</v>
+      </c>
+      <c r="B502" s="12" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C502" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D502" s="12">
+        <v>2.0223824E7</v>
+      </c>
+      <c r="E502" s="12" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F502" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G502" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H502" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I502" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J502" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K502" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L502" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N502" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="8">
+        <v>45739.70890346065</v>
+      </c>
+      <c r="B503" s="9" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C503" s="9" t="s">
+        <v>557</v>
+      </c>
+      <c r="D503" s="9">
+        <v>2.0242566E7</v>
+      </c>
+      <c r="E503" s="9" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F503" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G503" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H503" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I503" s="9">
+        <v>2021.0</v>
+      </c>
+      <c r="J503" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K503" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L503" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M503" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="11">
+        <v>45739.708913298615</v>
+      </c>
+      <c r="B504" s="12" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C504" s="12" t="s">
+        <v>163</v>
+      </c>
+      <c r="D504" s="12">
+        <v>2.0242715E7</v>
+      </c>
+      <c r="E504" s="12" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F504" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G504" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H504" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I504" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J504" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K504" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L504" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N504" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="8">
+        <v>45739.70991664352</v>
+      </c>
+      <c r="B505" s="9" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C505" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="D505" s="9">
+        <v>2.0243429E7</v>
+      </c>
+      <c r="E505" s="9" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F505" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G505" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H505" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I505" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J505" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K505" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L505" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N505" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="11">
+        <v>45739.71170569444</v>
+      </c>
+      <c r="B506" s="12" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C506" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D506" s="12">
+        <v>2.024342E7</v>
+      </c>
+      <c r="E506" s="12" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F506" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G506" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H506" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I506" s="12">
+        <v>2021.0</v>
+      </c>
+      <c r="J506" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K506" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L506" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N506" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="8">
+        <v>45739.7125408912</v>
+      </c>
+      <c r="B507" s="9" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C507" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D507" s="9">
+        <v>2.0232722E7</v>
+      </c>
+      <c r="E507" s="9" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F507" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G507" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H507" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I507" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J507" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K507" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L507" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N507" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="11">
+        <v>45739.71343508102</v>
+      </c>
+      <c r="B508" s="12" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C508" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="D508" s="12">
+        <v>2.024108E7</v>
+      </c>
+      <c r="E508" s="12" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F508" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G508" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H508" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I508" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J508" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K508" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L508" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N508" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="8">
+        <v>45739.72034579861</v>
+      </c>
+      <c r="B509" s="9" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C509" s="9" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D509" s="9">
+        <v>2.0212503E7</v>
+      </c>
+      <c r="E509" s="9" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F509" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G509" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H509" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I509" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J509" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K509" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L509" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N509" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="11">
+        <v>45739.721377546295</v>
+      </c>
+      <c r="B510" s="12" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C510" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D510" s="12">
+        <v>2.0233433E7</v>
+      </c>
+      <c r="E510" s="12" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F510" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G510" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H510" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I510" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J510" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K510" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L510" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M510" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="8">
+        <v>45739.731801539354</v>
+      </c>
+      <c r="B511" s="9" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C511" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D511" s="9">
+        <v>2.0192742E7</v>
+      </c>
+      <c r="E511" s="9" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F511" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G511" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H511" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I511" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J511" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K511" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L511" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M511" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="11">
+        <v>45739.73726576389</v>
+      </c>
+      <c r="B512" s="12" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C512" s="12" t="s">
+        <v>667</v>
+      </c>
+      <c r="D512" s="12">
+        <v>2.0236637E7</v>
+      </c>
+      <c r="E512" s="12" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F512" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G512" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H512" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I512" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J512" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K512" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L512" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M512" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="8">
+        <v>45739.74478583333</v>
+      </c>
+      <c r="B513" s="9" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C513" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D513" s="9">
+        <v>2.0223617E7</v>
+      </c>
+      <c r="E513" s="9" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F513" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G513" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H513" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I513" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J513" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K513" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L513" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N513" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="11">
+        <v>45739.75046248843</v>
+      </c>
+      <c r="B514" s="12" t="s">
+        <v>1174</v>
+      </c>
+      <c r="C514" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="D514" s="12">
+        <v>2.0243818E7</v>
+      </c>
+      <c r="E514" s="12" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F514" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G514" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H514" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I514" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J514" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K514" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L514" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N514" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="8">
+        <v>45739.752822511575</v>
+      </c>
+      <c r="B515" s="9" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C515" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D515" s="9">
+        <v>2.0242717E7</v>
+      </c>
+      <c r="E515" s="9" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F515" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G515" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H515" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I515" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J515" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K515" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L515" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M515" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="11">
+        <v>45739.75450818287</v>
+      </c>
+      <c r="B516" s="12" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C516" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D516" s="12">
+        <v>2.0246275E7</v>
+      </c>
+      <c r="E516" s="12" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F516" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G516" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="H516" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I516" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J516" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K516" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L516" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N516" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="8">
+        <v>45739.75609384259</v>
+      </c>
+      <c r="B517" s="9" t="s">
+        <v>1180</v>
+      </c>
+      <c r="C517" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D517" s="9">
+        <v>2.0242716E7</v>
+      </c>
+      <c r="E517" s="9" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F517" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G517" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H517" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I517" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J517" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K517" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L517" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N517" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="11">
+        <v>45739.76282207176</v>
+      </c>
+      <c r="B518" s="12" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C518" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D518" s="12">
+        <v>2.0203308E7</v>
+      </c>
+      <c r="E518" s="12" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F518" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G518" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H518" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I518" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J518" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K518" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L518" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M518" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="8">
+        <v>45739.76477458334</v>
+      </c>
+      <c r="B519" s="9" t="s">
+        <v>1184</v>
+      </c>
+      <c r="C519" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D519" s="9">
+        <v>2.0226424E7</v>
+      </c>
+      <c r="E519" s="9" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F519" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G519" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H519" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I519" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J519" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K519" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L519" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M519" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="11">
+        <v>45739.766772083334</v>
+      </c>
+      <c r="B520" s="12" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C520" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="D520" s="12">
+        <v>2.0215238E7</v>
+      </c>
+      <c r="E520" s="12" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F520" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G520" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H520" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I520" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J520" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K520" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L520" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N520" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="8">
+        <v>45739.77007849537</v>
+      </c>
+      <c r="B521" s="9" t="s">
+        <v>1188</v>
+      </c>
+      <c r="C521" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D521" s="9">
+        <v>2.0243023E7</v>
+      </c>
+      <c r="E521" s="9" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F521" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G521" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H521" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I521" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J521" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K521" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L521" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M521" s="9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="11">
+        <v>45739.771195208334</v>
+      </c>
+      <c r="B522" s="12" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C522" s="12" t="s">
+        <v>1191</v>
+      </c>
+      <c r="D522" s="12">
+        <v>2.0215202E7</v>
+      </c>
+      <c r="E522" s="12" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F522" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G522" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H522" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I522" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J522" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K522" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L522" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M522" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="8">
+        <v>45739.78805106481</v>
+      </c>
+      <c r="B523" s="9" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C523" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="D523" s="9">
+        <v>2.0231716E7</v>
+      </c>
+      <c r="E523" s="9" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F523" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G523" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H523" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I523" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J523" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K523" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L523" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M523" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="11">
+        <v>45739.792339479165</v>
+      </c>
+      <c r="B524" s="12" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C524" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D524" s="12">
+        <v>2.0243407E7</v>
+      </c>
+      <c r="E524" s="12" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F524" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G524" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H524" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I524" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J524" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K524" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L524" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N524" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="8">
+        <v>45739.79631143519</v>
+      </c>
+      <c r="B525" s="9" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C525" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="D525" s="9">
+        <v>2.0243042E7</v>
+      </c>
+      <c r="E525" s="9" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F525" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G525" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H525" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I525" s="9">
+        <v>2021.0</v>
+      </c>
+      <c r="J525" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K525" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L525" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N525" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="11">
+        <v>45739.80562724537</v>
+      </c>
+      <c r="B526" s="12" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C526" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D526" s="12">
+        <v>2.0243531E7</v>
+      </c>
+      <c r="E526" s="12" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F526" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G526" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H526" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I526" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J526" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K526" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L526" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N526" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="8">
+        <v>45739.81307751157</v>
+      </c>
+      <c r="B527" s="9" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C527" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="D527" s="9">
+        <v>2.0253244E7</v>
+      </c>
+      <c r="E527" s="9" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F527" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G527" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H527" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I527" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J527" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K527" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L527" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M527" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="11">
+        <v>45739.81321280093</v>
+      </c>
+      <c r="B528" s="12" t="s">
+        <v>1203</v>
+      </c>
+      <c r="C528" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="D528" s="12">
+        <v>2.0243533E7</v>
+      </c>
+      <c r="E528" s="12" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F528" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G528" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H528" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I528" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J528" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K528" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L528" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N528" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="8">
+        <v>45739.819354189814</v>
+      </c>
+      <c r="B529" s="9" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C529" s="9" t="s">
+        <v>484</v>
+      </c>
+      <c r="D529" s="9">
+        <v>2.0201731E7</v>
+      </c>
+      <c r="E529" s="9" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F529" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G529" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H529" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I529" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J529" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K529" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L529" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N529" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="11">
+        <v>45739.82272487268</v>
+      </c>
+      <c r="B530" s="12" t="s">
+        <v>1207</v>
+      </c>
+      <c r="C530" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D530" s="12">
+        <v>2.0193262E7</v>
+      </c>
+      <c r="E530" s="12" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F530" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G530" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H530" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I530" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J530" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K530" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L530" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M530" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="8">
+        <v>45739.823763900466</v>
+      </c>
+      <c r="B531" s="9" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C531" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D531" s="9">
+        <v>2.0215152E7</v>
+      </c>
+      <c r="E531" s="9" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F531" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G531" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H531" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I531" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J531" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K531" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L531" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N531" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="11">
+        <v>45739.82596545139</v>
+      </c>
+      <c r="B532" s="12" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C532" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D532" s="12">
+        <v>2.0227056E7</v>
+      </c>
+      <c r="E532" s="12" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F532" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G532" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H532" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I532" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J532" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K532" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L532" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N532" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="8">
+        <v>45739.826041099535</v>
+      </c>
+      <c r="B533" s="9" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C533" s="9" t="s">
+        <v>1213</v>
+      </c>
+      <c r="D533" s="9">
+        <v>2.024106E7</v>
+      </c>
+      <c r="E533" s="9" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F533" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G533" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H533" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I533" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J533" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K533" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L533" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N533" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="11">
+        <v>45739.82896271991</v>
+      </c>
+      <c r="B534" s="12" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C534" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D534" s="12">
+        <v>2.0227107E7</v>
+      </c>
+      <c r="E534" s="12" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F534" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G534" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H534" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I534" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J534" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K534" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L534" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N534" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="8">
+        <v>45739.8307834375</v>
+      </c>
+      <c r="B535" s="9" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C535" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="D535" s="9">
+        <v>2.0242207E7</v>
+      </c>
+      <c r="E535" s="9" t="s">
+        <v>537</v>
+      </c>
+      <c r="F535" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G535" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H535" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I535" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J535" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K535" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L535" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M535" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="11">
+        <v>45739.832616238426</v>
+      </c>
+      <c r="B536" s="12" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C536" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D536" s="12">
+        <v>2.0242537E7</v>
+      </c>
+      <c r="E536" s="12" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F536" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G536" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H536" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I536" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J536" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K536" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L536" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M536" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="8">
+        <v>45739.833549999996</v>
+      </c>
+      <c r="B537" s="9" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C537" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D537" s="9">
+        <v>2.024354E7</v>
+      </c>
+      <c r="E537" s="9" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F537" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G537" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H537" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I537" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J537" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K537" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L537" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N537" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="11">
+        <v>45739.83593239583</v>
+      </c>
+      <c r="B538" s="12" t="s">
+        <v>1222</v>
+      </c>
+      <c r="C538" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D538" s="12">
+        <v>2.0222116E7</v>
+      </c>
+      <c r="E538" s="12" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F538" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="G538" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H538" s="12">
+        <v>2012.0</v>
+      </c>
+      <c r="I538" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J538" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K538" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L538" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M538" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="8">
+        <v>45739.83775832176</v>
+      </c>
+      <c r="B539" s="9" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C539" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D539" s="9">
+        <v>2.0242546E7</v>
+      </c>
+      <c r="E539" s="9" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F539" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G539" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H539" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I539" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J539" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K539" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="L539" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N539" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="11">
+        <v>45739.83805658565</v>
+      </c>
+      <c r="B540" s="12" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C540" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D540" s="12">
+        <v>2.0242969E7</v>
+      </c>
+      <c r="E540" s="12" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F540" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G540" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H540" s="12">
+        <v>2022.0</v>
+      </c>
+      <c r="I540" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J540" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K540" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L540" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M540" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="8">
+        <v>45739.83809174769</v>
+      </c>
+      <c r="B541" s="9" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C541" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="D541" s="9">
+        <v>2.0243633E7</v>
+      </c>
+      <c r="E541" s="9" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F541" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G541" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H541" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I541" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J541" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K541" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L541" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N541" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="11">
+        <v>45739.839833923616</v>
+      </c>
+      <c r="B542" s="12" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C542" s="12" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D542" s="12">
+        <v>2.0213228E7</v>
+      </c>
+      <c r="E542" s="12" t="s">
+        <v>1232</v>
+      </c>
+      <c r="F542" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G542" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H542" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I542" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J542" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K542" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L542" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M542" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="8">
+        <v>45739.84185362268</v>
+      </c>
+      <c r="B543" s="9" t="s">
+        <v>1233</v>
+      </c>
+      <c r="C543" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="D543" s="9">
+        <v>2.0246403E7</v>
+      </c>
+      <c r="E543" s="9" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F543" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G543" s="9" t="s">
+        <v>569</v>
+      </c>
+      <c r="H543" s="9">
+        <v>2022.0</v>
+      </c>
+      <c r="I543" s="9">
+        <v>2019.0</v>
+      </c>
+      <c r="J543" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="K543" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L543" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N543" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="11">
+        <v>45739.84226773148</v>
+      </c>
+      <c r="B544" s="12" t="s">
+        <v>1235</v>
+      </c>
+      <c r="C544" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="D544" s="12">
+        <v>2.0241714E7</v>
+      </c>
+      <c r="E544" s="12" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F544" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G544" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="H544" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I544" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J544" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K544" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L544" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M544" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="8">
+        <v>45739.84474865741</v>
+      </c>
+      <c r="B545" s="9" t="s">
+        <v>1237</v>
+      </c>
+      <c r="C545" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D545" s="9">
+        <v>2.0203056E7</v>
+      </c>
+      <c r="E545" s="9" t="s">
+        <v>1238</v>
+      </c>
+      <c r="F545" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G545" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H545" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I545" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J545" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K545" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L545" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M545" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="11">
+        <v>45739.8450655787</v>
+      </c>
+      <c r="B546" s="12" t="s">
+        <v>1239</v>
+      </c>
+      <c r="C546" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D546" s="12">
+        <v>2.0202133E7</v>
+      </c>
+      <c r="E546" s="12" t="s">
+        <v>1240</v>
+      </c>
+      <c r="F546" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G546" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H546" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I546" s="12">
+        <v>2019.0</v>
+      </c>
+      <c r="J546" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K546" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L546" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M546" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="8">
+        <v>45739.84613917824</v>
+      </c>
+      <c r="B547" s="9" t="s">
+        <v>1241</v>
+      </c>
+      <c r="C547" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D547" s="9">
+        <v>2.0243522E7</v>
+      </c>
+      <c r="E547" s="9" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F547" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G547" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H547" s="9">
+        <v>2012.0</v>
+      </c>
+      <c r="I547" s="9">
+        <v>2021.0</v>
+      </c>
+      <c r="J547" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K547" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L547" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M547" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="11">
+        <v>45739.847289722224</v>
+      </c>
+      <c r="B548" s="12" t="s">
+        <v>1243</v>
+      </c>
+      <c r="C548" s="12" t="s">
+        <v>1244</v>
+      </c>
+      <c r="D548" s="12">
+        <v>2.0221108E7</v>
+      </c>
+      <c r="E548" s="12" t="s">
+        <v>1245</v>
+      </c>
+      <c r="F548" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G548" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H548" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I548" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J548" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K548" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L548" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M548" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="8">
+        <v>45739.85275346065</v>
+      </c>
+      <c r="B549" s="9" t="s">
+        <v>1246</v>
+      </c>
+      <c r="C549" s="9" t="s">
+        <v>317</v>
+      </c>
+      <c r="D549" s="9">
+        <v>2.0241012E7</v>
+      </c>
+      <c r="E549" s="9" t="s">
+        <v>909</v>
+      </c>
+      <c r="F549" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G549" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H549" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I549" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J549" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K549" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L549" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M549" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="11">
+        <v>45739.8535012963</v>
+      </c>
+      <c r="B550" s="12" t="s">
+        <v>1247</v>
+      </c>
+      <c r="C550" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D550" s="12">
+        <v>2.0222999E7</v>
+      </c>
+      <c r="E550" s="12" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F550" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G550" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H550" s="12">
+        <v>2027.0</v>
+      </c>
+      <c r="I550" s="12">
+        <v>2018.0</v>
+      </c>
+      <c r="J550" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K550" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L550" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N550" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="8">
+        <v>45739.85851855324</v>
+      </c>
+      <c r="B551" s="9" t="s">
+        <v>1249</v>
+      </c>
+      <c r="C551" s="9" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D551" s="9">
+        <v>2.020162E7</v>
+      </c>
+      <c r="E551" s="9" t="s">
+        <v>1251</v>
+      </c>
+      <c r="F551" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G551" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H551" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I551" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J551" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K551" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L551" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M551" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="11">
+        <v>45739.85910391204</v>
+      </c>
+      <c r="B552" s="12" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C552" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D552" s="12">
+        <v>2.0214102E7</v>
+      </c>
+      <c r="E552" s="12" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F552" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G552" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H552" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I552" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J552" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K552" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L552" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N552" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="8">
+        <v>45739.87083418982</v>
+      </c>
+      <c r="B553" s="9" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C553" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="D553" s="9">
+        <v>2.0241611E7</v>
+      </c>
+      <c r="E553" s="9" t="s">
+        <v>1255</v>
+      </c>
+      <c r="F553" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G553" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H553" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I553" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J553" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K553" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L553" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N553" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="11">
+        <v>45739.87877951389</v>
+      </c>
+      <c r="B554" s="12" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C554" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="D554" s="12">
+        <v>2.0242516E7</v>
+      </c>
+      <c r="E554" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="F554" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G554" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="H554" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I554" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J554" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K554" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L554" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N554" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="8">
+        <v>45739.87985938658</v>
+      </c>
+      <c r="B555" s="9" t="s">
+        <v>1257</v>
+      </c>
+      <c r="C555" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="D555" s="9">
+        <v>2.0215255E7</v>
+      </c>
+      <c r="E555" s="9" t="s">
+        <v>1258</v>
+      </c>
+      <c r="F555" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G555" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H555" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I555" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J555" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K555" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L555" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N555" s="10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="11">
+        <v>45739.888228587966</v>
+      </c>
+      <c r="B556" s="12" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C556" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="D556" s="12">
+        <v>2.0243403E7</v>
+      </c>
+      <c r="E556" s="12" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F556" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G556" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H556" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I556" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J556" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K556" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L556" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M556" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="8">
+        <v>45739.89210545139</v>
+      </c>
+      <c r="B557" s="9" t="s">
+        <v>1261</v>
+      </c>
+      <c r="C557" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D557" s="9">
+        <v>2.0227146E7</v>
+      </c>
+      <c r="E557" s="9" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F557" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G557" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H557" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I557" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J557" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K557" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L557" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="N557" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="11">
+        <v>45739.89327905093</v>
+      </c>
+      <c r="B558" s="12" t="s">
+        <v>1263</v>
+      </c>
+      <c r="C558" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="D558" s="12">
+        <v>2.0201603E7</v>
+      </c>
+      <c r="E558" s="12" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F558" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G558" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H558" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I558" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J558" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K558" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L558" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="M558" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="8">
+        <v>45739.895879386575</v>
+      </c>
+      <c r="B559" s="9" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C559" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="D559" s="9">
+        <v>2.0212105E7</v>
+      </c>
+      <c r="E559" s="9" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F559" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="G559" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H559" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I559" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J559" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K559" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="L559" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M559" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="11">
+        <v>45739.8968159375</v>
+      </c>
+      <c r="B560" s="12" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C560" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D560" s="12">
+        <v>2.0227026E7</v>
+      </c>
+      <c r="E560" s="12" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F560" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G560" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H560" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I560" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J560" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K560" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="L560" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N560" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="8">
+        <v>45739.8974654051</v>
+      </c>
+      <c r="B561" s="9" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C561" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D561" s="9">
+        <v>2.0243029E7</v>
+      </c>
+      <c r="E561" s="9" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F561" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G561" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H561" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I561" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J561" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K561" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="L561" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M561" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="11">
+        <v>45739.897950162034</v>
+      </c>
+      <c r="B562" s="12" t="s">
+        <v>1271</v>
+      </c>
+      <c r="C562" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="D562" s="12">
+        <v>2.021515E7</v>
+      </c>
+      <c r="E562" s="12" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F562" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G562" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H562" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I562" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J562" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K562" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="L562" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N562" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="8">
+        <v>45739.89857240741</v>
+      </c>
+      <c r="B563" s="9" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C563" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D563" s="9">
+        <v>2.0243012E7</v>
+      </c>
+      <c r="E563" s="9" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F563" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G563" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H563" s="9">
+        <v>2017.0</v>
+      </c>
+      <c r="I563" s="9">
+        <v>2020.0</v>
+      </c>
+      <c r="J563" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="K563" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L563" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M563" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="11">
+        <v>45739.90506113426</v>
+      </c>
+      <c r="B564" s="12" t="s">
+        <v>1275</v>
+      </c>
+      <c r="C564" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D564" s="12">
+        <v>2.0242508E7</v>
+      </c>
+      <c r="E564" s="12" t="s">
+        <v>1276</v>
+      </c>
+      <c r="F564" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="G564" s="12" t="s">
+        <v>569</v>
+      </c>
+      <c r="H564" s="12">
+        <v>2017.0</v>
+      </c>
+      <c r="I564" s="12">
+        <v>2020.0</v>
+      </c>
+      <c r="J564" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K564" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="L564" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="N564" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="14">
+        <v>45739.91096954861</v>
+      </c>
+      <c r="B565" s="15" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C565" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="D565" s="15">
+        <v>2.0223232E7</v>
+      </c>
+      <c r="E565" s="15" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F565" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G565" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H565" s="15">
+        <v>2022.0</v>
+      </c>
+      <c r="I565" s="15">
+        <v>2020.0</v>
+      </c>
+      <c r="J565" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="K565" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="L565" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="M565" s="15" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
